--- a/docs/3DSB_Acompanhamento_CampusApp.xlsx
+++ b/docs/3DSB_Acompanhamento_CampusApp.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\.github\docs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4358CB75-1EE7-41AF-9C5D-B005A9A4FC2F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3979694D-AB44-4DAE-86D6-A00F1D5FE839}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-16320" windowWidth="29040" windowHeight="15720" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-16320" windowWidth="29040" windowHeight="15720" tabRatio="500" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Dashboard" sheetId="1" r:id="rId1"/>
@@ -51,7 +51,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1263" uniqueCount="557">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1257" uniqueCount="551">
   <si>
     <t>Desenvolvimento de Dispositivos Móveis · IFTM Campus Uberlândia · Prof. Edson Angoti Júnior</t>
   </si>
@@ -89,37 +89,19 @@
     <t>Radar Neurodivergente</t>
   </si>
   <si>
-    <t>Ana Beatriz Ramos Del Padre (+ equipe)</t>
-  </si>
-  <si>
     <t>E Agora, Adulto?</t>
   </si>
   <si>
-    <t>Felipe, Gabriel, Heitor, Philipe, Vitor Hugo</t>
-  </si>
-  <si>
     <t>Sincronize</t>
   </si>
   <si>
-    <t>Alexandre, Giovana, Lara, M. Eduarda, Matheus, Rian</t>
-  </si>
-  <si>
     <t>Anbylize</t>
   </si>
   <si>
-    <t>Luiza Brandão Nunes (+ equipe)</t>
-  </si>
-  <si>
     <t>Monitorizador</t>
   </si>
   <si>
-    <t>Miguel Antonio Alves Gontijo (+ equipe)</t>
-  </si>
-  <si>
     <t>FlowUp</t>
-  </si>
-  <si>
-    <t>Rafael Costa Fernandes (+ equipe)</t>
   </si>
   <si>
     <t>TOTAL DA TURMA</t>
@@ -2324,7 +2306,7 @@
   <sheetData>
     <row r="2" spans="2:11" ht="21" x14ac:dyDescent="0.4">
       <c r="B2" s="1" t="s">
-        <v>528</v>
+        <v>522</v>
       </c>
     </row>
     <row r="3" spans="2:11" x14ac:dyDescent="0.3">
@@ -2364,12 +2346,20 @@
         <v>10</v>
       </c>
     </row>
-    <row r="6" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="6" spans="2:11" ht="40.200000000000003" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B6" s="4" t="s">
         <v>11</v>
       </c>
-      <c r="C6" s="5" t="s">
-        <v>12</v>
+      <c r="C6" s="5" t="str">
+        <f>_xlfn.TEXTJOIN(", ", TRUE,
+  IFERROR(LEFT(_xlfn.XLOOKUP(B6, Equipes!A$2:A$7, Equipes!B$2:B$7), SEARCH(" ", _xlfn.XLOOKUP(B6, Equipes!A$2:A$7, Equipes!B$2:B$7), SEARCH(" ", _xlfn.XLOOKUP(B6, Equipes!A$2:A$7, Equipes!B$2:B$7)) + 1) - 1), _xlfn.XLOOKUP(B6, Equipes!A$2:A$7, Equipes!B$2:B$7)),
+  IFERROR(LEFT(_xlfn.XLOOKUP(B6, Equipes!A$2:A$7, Equipes!C$2:C$7), SEARCH(" ", _xlfn.XLOOKUP(B6, Equipes!A$2:A$7, Equipes!C$2:C$7), SEARCH(" ", _xlfn.XLOOKUP(B6, Equipes!A$2:A$7, Equipes!C$2:C$7)) + 1) - 1), _xlfn.XLOOKUP(B6, Equipes!A$2:A$7, Equipes!C$2:C$7)),
+  IFERROR(LEFT(_xlfn.XLOOKUP(B6, Equipes!A$2:A$7, Equipes!D$2:D$7), SEARCH(" ", _xlfn.XLOOKUP(B6, Equipes!A$2:A$7, Equipes!D$2:D$7), SEARCH(" ", _xlfn.XLOOKUP(B6, Equipes!A$2:A$7, Equipes!D$2:D$7)) + 1) - 1), _xlfn.XLOOKUP(B6, Equipes!A$2:A$7, Equipes!D$2:D$7)),
+  IFERROR(LEFT(_xlfn.XLOOKUP(B6, Equipes!A$2:A$7, Equipes!E$2:E$7), SEARCH(" ", _xlfn.XLOOKUP(B6, Equipes!A$2:A$7, Equipes!E$2:E$7), SEARCH(" ", _xlfn.XLOOKUP(B6, Equipes!A$2:A$7, Equipes!E$2:E$7)) + 1) - 1), _xlfn.XLOOKUP(B6, Equipes!A$2:A$7, Equipes!E$2:E$7)),
+  IFERROR(LEFT(_xlfn.XLOOKUP(B6, Equipes!A$2:A$7, Equipes!F$2:F$7), SEARCH(" ", _xlfn.XLOOKUP(B6, Equipes!A$2:A$7, Equipes!F$2:F$7), SEARCH(" ", _xlfn.XLOOKUP(B6, Equipes!A$2:A$7, Equipes!F$2:F$7)) + 1) - 1), _xlfn.XLOOKUP(B6, Equipes!A$2:A$7, Equipes!F$2:F$7)),
+  IFERROR(LEFT(_xlfn.XLOOKUP(B6, Equipes!A$2:A$7, Equipes!G$2:G$7), SEARCH(" ", _xlfn.XLOOKUP(B6, Equipes!A$2:A$7, Equipes!G$2:G$7), SEARCH(" ", _xlfn.XLOOKUP(B6, Equipes!A$2:A$7, Equipes!G$2:G$7)) + 1) - 1), _xlfn.XLOOKUP(B6, Equipes!A$2:A$7, Equipes!G$2:G$7))
+)</f>
+        <v>Ana Beatriz, João Victor, Maria Paula, Sarah Hevelyn</v>
       </c>
       <c r="D6" s="6">
         <f>COUNTA(RadarNeuro!A2:A45)</f>
@@ -2404,12 +2394,20 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="7" spans="2:11" ht="40.200000000000003" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B7" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="C7" s="9" t="s">
-        <v>14</v>
+        <v>12</v>
+      </c>
+      <c r="C7" s="5" t="str">
+        <f>_xlfn.TEXTJOIN(", ", TRUE,
+  IFERROR(LEFT(_xlfn.XLOOKUP(B7, Equipes!A$2:A$7, Equipes!B$2:B$7), SEARCH(" ", _xlfn.XLOOKUP(B7, Equipes!A$2:A$7, Equipes!B$2:B$7), SEARCH(" ", _xlfn.XLOOKUP(B7, Equipes!A$2:A$7, Equipes!B$2:B$7)) + 1) - 1), _xlfn.XLOOKUP(B7, Equipes!A$2:A$7, Equipes!B$2:B$7)),
+  IFERROR(LEFT(_xlfn.XLOOKUP(B7, Equipes!A$2:A$7, Equipes!C$2:C$7), SEARCH(" ", _xlfn.XLOOKUP(B7, Equipes!A$2:A$7, Equipes!C$2:C$7), SEARCH(" ", _xlfn.XLOOKUP(B7, Equipes!A$2:A$7, Equipes!C$2:C$7)) + 1) - 1), _xlfn.XLOOKUP(B7, Equipes!A$2:A$7, Equipes!C$2:C$7)),
+  IFERROR(LEFT(_xlfn.XLOOKUP(B7, Equipes!A$2:A$7, Equipes!D$2:D$7), SEARCH(" ", _xlfn.XLOOKUP(B7, Equipes!A$2:A$7, Equipes!D$2:D$7), SEARCH(" ", _xlfn.XLOOKUP(B7, Equipes!A$2:A$7, Equipes!D$2:D$7)) + 1) - 1), _xlfn.XLOOKUP(B7, Equipes!A$2:A$7, Equipes!D$2:D$7)),
+  IFERROR(LEFT(_xlfn.XLOOKUP(B7, Equipes!A$2:A$7, Equipes!E$2:E$7), SEARCH(" ", _xlfn.XLOOKUP(B7, Equipes!A$2:A$7, Equipes!E$2:E$7), SEARCH(" ", _xlfn.XLOOKUP(B7, Equipes!A$2:A$7, Equipes!E$2:E$7)) + 1) - 1), _xlfn.XLOOKUP(B7, Equipes!A$2:A$7, Equipes!E$2:E$7)),
+  IFERROR(LEFT(_xlfn.XLOOKUP(B7, Equipes!A$2:A$7, Equipes!F$2:F$7), SEARCH(" ", _xlfn.XLOOKUP(B7, Equipes!A$2:A$7, Equipes!F$2:F$7), SEARCH(" ", _xlfn.XLOOKUP(B7, Equipes!A$2:A$7, Equipes!F$2:F$7)) + 1) - 1), _xlfn.XLOOKUP(B7, Equipes!A$2:A$7, Equipes!F$2:F$7)),
+  IFERROR(LEFT(_xlfn.XLOOKUP(B7, Equipes!A$2:A$7, Equipes!G$2:G$7), SEARCH(" ", _xlfn.XLOOKUP(B7, Equipes!A$2:A$7, Equipes!G$2:G$7), SEARCH(" ", _xlfn.XLOOKUP(B7, Equipes!A$2:A$7, Equipes!G$2:G$7)) + 1) - 1), _xlfn.XLOOKUP(B7, Equipes!A$2:A$7, Equipes!G$2:G$7))
+)</f>
+        <v>Felipe Augusto, Gabriel Souza, Heitor Calegari, Philipe Medeiros, Vitor Hugo</v>
       </c>
       <c r="D7" s="10">
         <f>COUNTA(EAgoraAdulto!A2:A40)</f>
@@ -2444,12 +2442,20 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="2:11" ht="26.4" x14ac:dyDescent="0.3">
+    <row r="8" spans="2:11" ht="40.200000000000003" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B8" s="12" t="s">
-        <v>15</v>
-      </c>
-      <c r="C8" s="5" t="s">
-        <v>16</v>
+        <v>13</v>
+      </c>
+      <c r="C8" s="5" t="str">
+        <f>_xlfn.TEXTJOIN(", ", TRUE,
+  IFERROR(LEFT(_xlfn.XLOOKUP(B8, Equipes!A$2:A$7, Equipes!B$2:B$7), SEARCH(" ", _xlfn.XLOOKUP(B8, Equipes!A$2:A$7, Equipes!B$2:B$7), SEARCH(" ", _xlfn.XLOOKUP(B8, Equipes!A$2:A$7, Equipes!B$2:B$7)) + 1) - 1), _xlfn.XLOOKUP(B8, Equipes!A$2:A$7, Equipes!B$2:B$7)),
+  IFERROR(LEFT(_xlfn.XLOOKUP(B8, Equipes!A$2:A$7, Equipes!C$2:C$7), SEARCH(" ", _xlfn.XLOOKUP(B8, Equipes!A$2:A$7, Equipes!C$2:C$7), SEARCH(" ", _xlfn.XLOOKUP(B8, Equipes!A$2:A$7, Equipes!C$2:C$7)) + 1) - 1), _xlfn.XLOOKUP(B8, Equipes!A$2:A$7, Equipes!C$2:C$7)),
+  IFERROR(LEFT(_xlfn.XLOOKUP(B8, Equipes!A$2:A$7, Equipes!D$2:D$7), SEARCH(" ", _xlfn.XLOOKUP(B8, Equipes!A$2:A$7, Equipes!D$2:D$7), SEARCH(" ", _xlfn.XLOOKUP(B8, Equipes!A$2:A$7, Equipes!D$2:D$7)) + 1) - 1), _xlfn.XLOOKUP(B8, Equipes!A$2:A$7, Equipes!D$2:D$7)),
+  IFERROR(LEFT(_xlfn.XLOOKUP(B8, Equipes!A$2:A$7, Equipes!E$2:E$7), SEARCH(" ", _xlfn.XLOOKUP(B8, Equipes!A$2:A$7, Equipes!E$2:E$7), SEARCH(" ", _xlfn.XLOOKUP(B8, Equipes!A$2:A$7, Equipes!E$2:E$7)) + 1) - 1), _xlfn.XLOOKUP(B8, Equipes!A$2:A$7, Equipes!E$2:E$7)),
+  IFERROR(LEFT(_xlfn.XLOOKUP(B8, Equipes!A$2:A$7, Equipes!F$2:F$7), SEARCH(" ", _xlfn.XLOOKUP(B8, Equipes!A$2:A$7, Equipes!F$2:F$7), SEARCH(" ", _xlfn.XLOOKUP(B8, Equipes!A$2:A$7, Equipes!F$2:F$7)) + 1) - 1), _xlfn.XLOOKUP(B8, Equipes!A$2:A$7, Equipes!F$2:F$7)),
+  IFERROR(LEFT(_xlfn.XLOOKUP(B8, Equipes!A$2:A$7, Equipes!G$2:G$7), SEARCH(" ", _xlfn.XLOOKUP(B8, Equipes!A$2:A$7, Equipes!G$2:G$7), SEARCH(" ", _xlfn.XLOOKUP(B8, Equipes!A$2:A$7, Equipes!G$2:G$7)) + 1) - 1), _xlfn.XLOOKUP(B8, Equipes!A$2:A$7, Equipes!G$2:G$7))
+)</f>
+        <v>Alexandre Hiratsuka, Giovana Cunha, Lara Campos, Maria Eduarda, Matheus Cardoso, Rian Cristian</v>
       </c>
       <c r="D8" s="6">
         <f>COUNTA(Sincronize!A2:A39)</f>
@@ -2484,12 +2490,20 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="9" spans="2:11" ht="40.200000000000003" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B9" s="13" t="s">
-        <v>17</v>
-      </c>
-      <c r="C9" s="9" t="s">
-        <v>18</v>
+        <v>14</v>
+      </c>
+      <c r="C9" s="5" t="str">
+        <f>_xlfn.TEXTJOIN(", ", TRUE,
+  IFERROR(LEFT(_xlfn.XLOOKUP(B9, Equipes!A$2:A$7, Equipes!B$2:B$7), SEARCH(" ", _xlfn.XLOOKUP(B9, Equipes!A$2:A$7, Equipes!B$2:B$7), SEARCH(" ", _xlfn.XLOOKUP(B9, Equipes!A$2:A$7, Equipes!B$2:B$7)) + 1) - 1), _xlfn.XLOOKUP(B9, Equipes!A$2:A$7, Equipes!B$2:B$7)),
+  IFERROR(LEFT(_xlfn.XLOOKUP(B9, Equipes!A$2:A$7, Equipes!C$2:C$7), SEARCH(" ", _xlfn.XLOOKUP(B9, Equipes!A$2:A$7, Equipes!C$2:C$7), SEARCH(" ", _xlfn.XLOOKUP(B9, Equipes!A$2:A$7, Equipes!C$2:C$7)) + 1) - 1), _xlfn.XLOOKUP(B9, Equipes!A$2:A$7, Equipes!C$2:C$7)),
+  IFERROR(LEFT(_xlfn.XLOOKUP(B9, Equipes!A$2:A$7, Equipes!D$2:D$7), SEARCH(" ", _xlfn.XLOOKUP(B9, Equipes!A$2:A$7, Equipes!D$2:D$7), SEARCH(" ", _xlfn.XLOOKUP(B9, Equipes!A$2:A$7, Equipes!D$2:D$7)) + 1) - 1), _xlfn.XLOOKUP(B9, Equipes!A$2:A$7, Equipes!D$2:D$7)),
+  IFERROR(LEFT(_xlfn.XLOOKUP(B9, Equipes!A$2:A$7, Equipes!E$2:E$7), SEARCH(" ", _xlfn.XLOOKUP(B9, Equipes!A$2:A$7, Equipes!E$2:E$7), SEARCH(" ", _xlfn.XLOOKUP(B9, Equipes!A$2:A$7, Equipes!E$2:E$7)) + 1) - 1), _xlfn.XLOOKUP(B9, Equipes!A$2:A$7, Equipes!E$2:E$7)),
+  IFERROR(LEFT(_xlfn.XLOOKUP(B9, Equipes!A$2:A$7, Equipes!F$2:F$7), SEARCH(" ", _xlfn.XLOOKUP(B9, Equipes!A$2:A$7, Equipes!F$2:F$7), SEARCH(" ", _xlfn.XLOOKUP(B9, Equipes!A$2:A$7, Equipes!F$2:F$7)) + 1) - 1), _xlfn.XLOOKUP(B9, Equipes!A$2:A$7, Equipes!F$2:F$7)),
+  IFERROR(LEFT(_xlfn.XLOOKUP(B9, Equipes!A$2:A$7, Equipes!G$2:G$7), SEARCH(" ", _xlfn.XLOOKUP(B9, Equipes!A$2:A$7, Equipes!G$2:G$7), SEARCH(" ", _xlfn.XLOOKUP(B9, Equipes!A$2:A$7, Equipes!G$2:G$7)) + 1) - 1), _xlfn.XLOOKUP(B9, Equipes!A$2:A$7, Equipes!G$2:G$7))
+)</f>
+        <v>Luiza Brandão, Andressa Marques, Byanca Gonçalves, Manuella Serafim</v>
       </c>
       <c r="D9" s="10">
         <f>COUNTA(Anbylize!A2:A37)</f>
@@ -2524,12 +2538,20 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="10" spans="2:11" ht="40.200000000000003" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B10" s="14" t="s">
-        <v>19</v>
-      </c>
-      <c r="C10" s="5" t="s">
-        <v>20</v>
+        <v>15</v>
+      </c>
+      <c r="C10" s="5" t="str">
+        <f>_xlfn.TEXTJOIN(", ", TRUE,
+  IFERROR(LEFT(_xlfn.XLOOKUP(B10, Equipes!A$2:A$7, Equipes!B$2:B$7), SEARCH(" ", _xlfn.XLOOKUP(B10, Equipes!A$2:A$7, Equipes!B$2:B$7), SEARCH(" ", _xlfn.XLOOKUP(B10, Equipes!A$2:A$7, Equipes!B$2:B$7)) + 1) - 1), _xlfn.XLOOKUP(B10, Equipes!A$2:A$7, Equipes!B$2:B$7)),
+  IFERROR(LEFT(_xlfn.XLOOKUP(B10, Equipes!A$2:A$7, Equipes!C$2:C$7), SEARCH(" ", _xlfn.XLOOKUP(B10, Equipes!A$2:A$7, Equipes!C$2:C$7), SEARCH(" ", _xlfn.XLOOKUP(B10, Equipes!A$2:A$7, Equipes!C$2:C$7)) + 1) - 1), _xlfn.XLOOKUP(B10, Equipes!A$2:A$7, Equipes!C$2:C$7)),
+  IFERROR(LEFT(_xlfn.XLOOKUP(B10, Equipes!A$2:A$7, Equipes!D$2:D$7), SEARCH(" ", _xlfn.XLOOKUP(B10, Equipes!A$2:A$7, Equipes!D$2:D$7), SEARCH(" ", _xlfn.XLOOKUP(B10, Equipes!A$2:A$7, Equipes!D$2:D$7)) + 1) - 1), _xlfn.XLOOKUP(B10, Equipes!A$2:A$7, Equipes!D$2:D$7)),
+  IFERROR(LEFT(_xlfn.XLOOKUP(B10, Equipes!A$2:A$7, Equipes!E$2:E$7), SEARCH(" ", _xlfn.XLOOKUP(B10, Equipes!A$2:A$7, Equipes!E$2:E$7), SEARCH(" ", _xlfn.XLOOKUP(B10, Equipes!A$2:A$7, Equipes!E$2:E$7)) + 1) - 1), _xlfn.XLOOKUP(B10, Equipes!A$2:A$7, Equipes!E$2:E$7)),
+  IFERROR(LEFT(_xlfn.XLOOKUP(B10, Equipes!A$2:A$7, Equipes!F$2:F$7), SEARCH(" ", _xlfn.XLOOKUP(B10, Equipes!A$2:A$7, Equipes!F$2:F$7), SEARCH(" ", _xlfn.XLOOKUP(B10, Equipes!A$2:A$7, Equipes!F$2:F$7)) + 1) - 1), _xlfn.XLOOKUP(B10, Equipes!A$2:A$7, Equipes!F$2:F$7)),
+  IFERROR(LEFT(_xlfn.XLOOKUP(B10, Equipes!A$2:A$7, Equipes!G$2:G$7), SEARCH(" ", _xlfn.XLOOKUP(B10, Equipes!A$2:A$7, Equipes!G$2:G$7), SEARCH(" ", _xlfn.XLOOKUP(B10, Equipes!A$2:A$7, Equipes!G$2:G$7)) + 1) - 1), _xlfn.XLOOKUP(B10, Equipes!A$2:A$7, Equipes!G$2:G$7))
+)</f>
+        <v>Miguel Antonio, Erik Mourão, Kaique Eduardo, Muryel Afonso</v>
       </c>
       <c r="D10" s="6">
         <f>COUNTA(Monitorizador!A2:A35)</f>
@@ -2564,12 +2586,20 @@
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="11" spans="2:11" ht="40.200000000000003" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B11" s="15" t="s">
-        <v>21</v>
-      </c>
-      <c r="C11" s="9" t="s">
-        <v>22</v>
+        <v>16</v>
+      </c>
+      <c r="C11" s="5" t="str">
+        <f>_xlfn.TEXTJOIN(", ", TRUE,
+  IFERROR(LEFT(_xlfn.XLOOKUP(B11, Equipes!A$2:A$7, Equipes!B$2:B$7), SEARCH(" ", _xlfn.XLOOKUP(B11, Equipes!A$2:A$7, Equipes!B$2:B$7), SEARCH(" ", _xlfn.XLOOKUP(B11, Equipes!A$2:A$7, Equipes!B$2:B$7)) + 1) - 1), _xlfn.XLOOKUP(B11, Equipes!A$2:A$7, Equipes!B$2:B$7)),
+  IFERROR(LEFT(_xlfn.XLOOKUP(B11, Equipes!A$2:A$7, Equipes!C$2:C$7), SEARCH(" ", _xlfn.XLOOKUP(B11, Equipes!A$2:A$7, Equipes!C$2:C$7), SEARCH(" ", _xlfn.XLOOKUP(B11, Equipes!A$2:A$7, Equipes!C$2:C$7)) + 1) - 1), _xlfn.XLOOKUP(B11, Equipes!A$2:A$7, Equipes!C$2:C$7)),
+  IFERROR(LEFT(_xlfn.XLOOKUP(B11, Equipes!A$2:A$7, Equipes!D$2:D$7), SEARCH(" ", _xlfn.XLOOKUP(B11, Equipes!A$2:A$7, Equipes!D$2:D$7), SEARCH(" ", _xlfn.XLOOKUP(B11, Equipes!A$2:A$7, Equipes!D$2:D$7)) + 1) - 1), _xlfn.XLOOKUP(B11, Equipes!A$2:A$7, Equipes!D$2:D$7)),
+  IFERROR(LEFT(_xlfn.XLOOKUP(B11, Equipes!A$2:A$7, Equipes!E$2:E$7), SEARCH(" ", _xlfn.XLOOKUP(B11, Equipes!A$2:A$7, Equipes!E$2:E$7), SEARCH(" ", _xlfn.XLOOKUP(B11, Equipes!A$2:A$7, Equipes!E$2:E$7)) + 1) - 1), _xlfn.XLOOKUP(B11, Equipes!A$2:A$7, Equipes!E$2:E$7)),
+  IFERROR(LEFT(_xlfn.XLOOKUP(B11, Equipes!A$2:A$7, Equipes!F$2:F$7), SEARCH(" ", _xlfn.XLOOKUP(B11, Equipes!A$2:A$7, Equipes!F$2:F$7), SEARCH(" ", _xlfn.XLOOKUP(B11, Equipes!A$2:A$7, Equipes!F$2:F$7)) + 1) - 1), _xlfn.XLOOKUP(B11, Equipes!A$2:A$7, Equipes!F$2:F$7)),
+  IFERROR(LEFT(_xlfn.XLOOKUP(B11, Equipes!A$2:A$7, Equipes!G$2:G$7), SEARCH(" ", _xlfn.XLOOKUP(B11, Equipes!A$2:A$7, Equipes!G$2:G$7), SEARCH(" ", _xlfn.XLOOKUP(B11, Equipes!A$2:A$7, Equipes!G$2:G$7)) + 1) - 1), _xlfn.XLOOKUP(B11, Equipes!A$2:A$7, Equipes!G$2:G$7))
+)</f>
+        <v>Rafael Costa, Guilherme Ferreira, Luiz Gustavo, Murilo Portes, Túlio Rodrigues</v>
       </c>
       <c r="D11" s="10">
         <f>COUNTA(FlowUp!A2:A35)</f>
@@ -2606,7 +2636,7 @@
     </row>
     <row r="12" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B12" s="16" t="s">
-        <v>23</v>
+        <v>17</v>
       </c>
       <c r="C12" s="17"/>
       <c r="D12" s="3">
@@ -2644,32 +2674,32 @@
     </row>
     <row r="14" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B14" s="19" t="s">
-        <v>24</v>
+        <v>18</v>
       </c>
     </row>
     <row r="15" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B15" s="20" t="s">
-        <v>25</v>
+        <v>19</v>
       </c>
     </row>
     <row r="16" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B16" s="20" t="s">
-        <v>26</v>
+        <v>20</v>
       </c>
     </row>
     <row r="17" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B17" s="20" t="s">
-        <v>27</v>
+        <v>21</v>
       </c>
     </row>
     <row r="18" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B18" s="20" t="s">
-        <v>28</v>
+        <v>22</v>
       </c>
     </row>
     <row r="19" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B19" s="20" t="s">
-        <v>29</v>
+        <v>23</v>
       </c>
     </row>
   </sheetData>
@@ -2715,120 +2745,120 @@
         <v>11</v>
       </c>
       <c r="B2" s="5" t="s">
-        <v>529</v>
+        <v>523</v>
       </c>
       <c r="C2" s="5" t="s">
-        <v>530</v>
+        <v>524</v>
       </c>
       <c r="D2" s="5" t="s">
-        <v>531</v>
+        <v>525</v>
       </c>
       <c r="E2" s="5" t="s">
-        <v>532</v>
+        <v>526</v>
       </c>
       <c r="F2" s="34"/>
       <c r="G2" s="34"/>
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A3" s="8" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B3" s="9" t="s">
-        <v>533</v>
+        <v>527</v>
       </c>
       <c r="C3" s="9" t="s">
-        <v>534</v>
+        <v>528</v>
       </c>
       <c r="D3" s="9" t="s">
-        <v>535</v>
+        <v>529</v>
       </c>
       <c r="E3" s="9" t="s">
-        <v>536</v>
+        <v>530</v>
       </c>
       <c r="F3" s="9" t="s">
-        <v>537</v>
+        <v>531</v>
       </c>
       <c r="G3" s="34"/>
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A4" s="12" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="B4" s="5" t="s">
-        <v>552</v>
+        <v>546</v>
       </c>
       <c r="C4" s="5" t="s">
-        <v>538</v>
+        <v>532</v>
       </c>
       <c r="D4" s="5" t="s">
-        <v>539</v>
+        <v>533</v>
       </c>
       <c r="E4" s="5" t="s">
-        <v>540</v>
+        <v>534</v>
       </c>
       <c r="F4" s="5" t="s">
-        <v>541</v>
+        <v>535</v>
       </c>
       <c r="G4" s="5" t="s">
-        <v>542</v>
+        <v>536</v>
       </c>
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A5" s="13" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="B5" s="9" t="s">
-        <v>543</v>
+        <v>537</v>
       </c>
       <c r="C5" s="9" t="s">
-        <v>544</v>
+        <v>538</v>
       </c>
       <c r="D5" s="9" t="s">
-        <v>545</v>
+        <v>539</v>
       </c>
       <c r="E5" s="9" t="s">
-        <v>546</v>
+        <v>540</v>
       </c>
       <c r="F5" s="34"/>
       <c r="G5" s="34"/>
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A6" s="14" t="s">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="B6" s="5" t="s">
-        <v>547</v>
+        <v>541</v>
       </c>
       <c r="C6" s="5" t="s">
-        <v>548</v>
+        <v>542</v>
       </c>
       <c r="D6" s="5" t="s">
-        <v>549</v>
+        <v>543</v>
       </c>
       <c r="E6" s="5" t="s">
-        <v>550</v>
+        <v>544</v>
       </c>
       <c r="F6" s="34"/>
       <c r="G6" s="34"/>
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A7" s="15" t="s">
-        <v>21</v>
+        <v>16</v>
       </c>
       <c r="B7" s="9" t="s">
-        <v>551</v>
+        <v>545</v>
       </c>
       <c r="C7" s="9" t="s">
-        <v>553</v>
+        <v>547</v>
       </c>
       <c r="D7" s="9" t="s">
-        <v>554</v>
+        <v>548</v>
       </c>
       <c r="E7" s="9" t="s">
-        <v>555</v>
+        <v>549</v>
       </c>
       <c r="F7" s="9" t="s">
-        <v>556</v>
+        <v>550</v>
       </c>
       <c r="G7" s="34"/>
     </row>
@@ -2855,45 +2885,45 @@
   <sheetData>
     <row r="1" spans="1:9" ht="26.4" x14ac:dyDescent="0.3">
       <c r="A1" s="21" t="s">
+        <v>24</v>
+      </c>
+      <c r="B1" s="21" t="s">
+        <v>25</v>
+      </c>
+      <c r="C1" s="21" t="s">
+        <v>26</v>
+      </c>
+      <c r="D1" s="21" t="s">
+        <v>27</v>
+      </c>
+      <c r="E1" s="21" t="s">
+        <v>28</v>
+      </c>
+      <c r="F1" s="21" t="s">
+        <v>29</v>
+      </c>
+      <c r="G1" s="21" t="s">
         <v>30</v>
       </c>
-      <c r="B1" s="21" t="s">
+      <c r="H1" s="21" t="s">
         <v>31</v>
       </c>
-      <c r="C1" s="21" t="s">
+      <c r="I1" s="21" t="s">
         <v>32</v>
-      </c>
-      <c r="D1" s="21" t="s">
-        <v>33</v>
-      </c>
-      <c r="E1" s="21" t="s">
-        <v>34</v>
-      </c>
-      <c r="F1" s="21" t="s">
-        <v>35</v>
-      </c>
-      <c r="G1" s="21" t="s">
-        <v>36</v>
-      </c>
-      <c r="H1" s="21" t="s">
-        <v>37</v>
-      </c>
-      <c r="I1" s="21" t="s">
-        <v>38</v>
       </c>
     </row>
     <row r="2" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A2" s="22" t="s">
-        <v>39</v>
+        <v>33</v>
       </c>
       <c r="B2" s="23" t="s">
-        <v>40</v>
+        <v>34</v>
       </c>
       <c r="C2" s="5" t="s">
-        <v>41</v>
+        <v>35</v>
       </c>
       <c r="D2" s="24" t="s">
-        <v>42</v>
+        <v>36</v>
       </c>
       <c r="E2" s="6">
         <v>1</v>
@@ -2902,23 +2932,23 @@
         <v>0.5</v>
       </c>
       <c r="G2" s="6" t="s">
-        <v>43</v>
+        <v>37</v>
       </c>
       <c r="H2" s="5"/>
       <c r="I2" s="5"/>
     </row>
     <row r="3" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A3" s="15" t="s">
-        <v>44</v>
+        <v>38</v>
       </c>
       <c r="B3" s="25" t="s">
-        <v>40</v>
+        <v>34</v>
       </c>
       <c r="C3" s="9" t="s">
-        <v>45</v>
+        <v>39</v>
       </c>
       <c r="D3" s="24" t="s">
-        <v>42</v>
+        <v>36</v>
       </c>
       <c r="E3" s="10">
         <v>1</v>
@@ -2927,23 +2957,23 @@
         <v>0.5</v>
       </c>
       <c r="G3" s="10" t="s">
-        <v>43</v>
+        <v>37</v>
       </c>
       <c r="H3" s="9"/>
       <c r="I3" s="9"/>
     </row>
     <row r="4" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A4" s="22" t="s">
-        <v>46</v>
+        <v>40</v>
       </c>
       <c r="B4" s="23" t="s">
-        <v>40</v>
+        <v>34</v>
       </c>
       <c r="C4" s="5" t="s">
-        <v>47</v>
+        <v>41</v>
       </c>
       <c r="D4" s="24" t="s">
-        <v>42</v>
+        <v>36</v>
       </c>
       <c r="E4" s="6">
         <v>1</v>
@@ -2952,23 +2982,23 @@
         <v>1</v>
       </c>
       <c r="G4" s="6" t="s">
-        <v>43</v>
+        <v>37</v>
       </c>
       <c r="H4" s="5"/>
       <c r="I4" s="5"/>
     </row>
     <row r="5" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A5" s="15" t="s">
-        <v>48</v>
+        <v>42</v>
       </c>
       <c r="B5" s="25" t="s">
-        <v>40</v>
+        <v>34</v>
       </c>
       <c r="C5" s="9" t="s">
-        <v>49</v>
+        <v>43</v>
       </c>
       <c r="D5" s="24" t="s">
-        <v>42</v>
+        <v>36</v>
       </c>
       <c r="E5" s="10">
         <v>1</v>
@@ -2977,23 +3007,23 @@
         <v>1</v>
       </c>
       <c r="G5" s="10" t="s">
-        <v>43</v>
+        <v>37</v>
       </c>
       <c r="H5" s="9"/>
       <c r="I5" s="9"/>
     </row>
     <row r="6" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A6" s="22" t="s">
-        <v>50</v>
+        <v>44</v>
       </c>
       <c r="B6" s="23" t="s">
-        <v>40</v>
+        <v>34</v>
       </c>
       <c r="C6" s="5" t="s">
-        <v>51</v>
+        <v>45</v>
       </c>
       <c r="D6" s="24" t="s">
-        <v>42</v>
+        <v>36</v>
       </c>
       <c r="E6" s="6">
         <v>1</v>
@@ -3002,23 +3032,23 @@
         <v>1</v>
       </c>
       <c r="G6" s="6" t="s">
-        <v>43</v>
+        <v>37</v>
       </c>
       <c r="H6" s="5"/>
       <c r="I6" s="5"/>
     </row>
     <row r="7" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A7" s="15" t="s">
-        <v>52</v>
+        <v>46</v>
       </c>
       <c r="B7" s="25" t="s">
-        <v>40</v>
+        <v>34</v>
       </c>
       <c r="C7" s="9" t="s">
-        <v>53</v>
+        <v>47</v>
       </c>
       <c r="D7" s="24" t="s">
-        <v>42</v>
+        <v>36</v>
       </c>
       <c r="E7" s="10">
         <v>1</v>
@@ -3027,23 +3057,23 @@
         <v>1</v>
       </c>
       <c r="G7" s="10" t="s">
-        <v>43</v>
+        <v>37</v>
       </c>
       <c r="H7" s="9"/>
       <c r="I7" s="9"/>
     </row>
     <row r="8" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A8" s="22" t="s">
-        <v>54</v>
+        <v>48</v>
       </c>
       <c r="B8" s="23" t="s">
-        <v>40</v>
+        <v>34</v>
       </c>
       <c r="C8" s="5" t="s">
-        <v>55</v>
+        <v>49</v>
       </c>
       <c r="D8" s="24" t="s">
-        <v>42</v>
+        <v>36</v>
       </c>
       <c r="E8" s="6">
         <v>1</v>
@@ -3052,23 +3082,23 @@
         <v>0.5</v>
       </c>
       <c r="G8" s="6" t="s">
-        <v>43</v>
+        <v>37</v>
       </c>
       <c r="H8" s="5"/>
       <c r="I8" s="5"/>
     </row>
     <row r="9" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A9" s="15" t="s">
-        <v>56</v>
+        <v>50</v>
       </c>
       <c r="B9" s="25" t="s">
-        <v>57</v>
+        <v>51</v>
       </c>
       <c r="C9" s="9" t="s">
-        <v>58</v>
+        <v>52</v>
       </c>
       <c r="D9" s="24" t="s">
-        <v>42</v>
+        <v>36</v>
       </c>
       <c r="E9" s="10">
         <v>1</v>
@@ -3077,23 +3107,23 @@
         <v>1</v>
       </c>
       <c r="G9" s="10" t="s">
-        <v>43</v>
+        <v>37</v>
       </c>
       <c r="H9" s="9"/>
       <c r="I9" s="9"/>
     </row>
     <row r="10" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A10" s="22" t="s">
-        <v>59</v>
+        <v>53</v>
       </c>
       <c r="B10" s="23" t="s">
-        <v>57</v>
+        <v>51</v>
       </c>
       <c r="C10" s="5" t="s">
-        <v>60</v>
+        <v>54</v>
       </c>
       <c r="D10" s="24" t="s">
-        <v>42</v>
+        <v>36</v>
       </c>
       <c r="E10" s="6">
         <v>1</v>
@@ -3102,23 +3132,23 @@
         <v>1</v>
       </c>
       <c r="G10" s="6" t="s">
-        <v>43</v>
+        <v>37</v>
       </c>
       <c r="H10" s="5"/>
       <c r="I10" s="5"/>
     </row>
     <row r="11" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A11" s="15" t="s">
-        <v>61</v>
+        <v>55</v>
       </c>
       <c r="B11" s="25" t="s">
-        <v>57</v>
+        <v>51</v>
       </c>
       <c r="C11" s="9" t="s">
-        <v>62</v>
+        <v>56</v>
       </c>
       <c r="D11" s="24" t="s">
-        <v>42</v>
+        <v>36</v>
       </c>
       <c r="E11" s="10">
         <v>1</v>
@@ -3127,23 +3157,23 @@
         <v>1</v>
       </c>
       <c r="G11" s="10" t="s">
-        <v>43</v>
+        <v>37</v>
       </c>
       <c r="H11" s="9"/>
       <c r="I11" s="9"/>
     </row>
     <row r="12" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A12" s="22" t="s">
-        <v>63</v>
+        <v>57</v>
       </c>
       <c r="B12" s="23" t="s">
-        <v>57</v>
+        <v>51</v>
       </c>
       <c r="C12" s="5" t="s">
-        <v>64</v>
+        <v>58</v>
       </c>
       <c r="D12" s="24" t="s">
-        <v>42</v>
+        <v>36</v>
       </c>
       <c r="E12" s="6">
         <v>1</v>
@@ -3152,23 +3182,23 @@
         <v>0.5</v>
       </c>
       <c r="G12" s="6" t="s">
-        <v>43</v>
+        <v>37</v>
       </c>
       <c r="H12" s="5"/>
       <c r="I12" s="5"/>
     </row>
     <row r="13" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A13" s="15" t="s">
-        <v>65</v>
+        <v>59</v>
       </c>
       <c r="B13" s="25" t="s">
-        <v>66</v>
+        <v>60</v>
       </c>
       <c r="C13" s="9" t="s">
-        <v>67</v>
+        <v>61</v>
       </c>
       <c r="D13" s="24" t="s">
-        <v>42</v>
+        <v>36</v>
       </c>
       <c r="E13" s="10">
         <v>1</v>
@@ -3177,23 +3207,23 @@
         <v>1</v>
       </c>
       <c r="G13" s="10" t="s">
-        <v>43</v>
+        <v>37</v>
       </c>
       <c r="H13" s="9"/>
       <c r="I13" s="9"/>
     </row>
     <row r="14" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A14" s="22" t="s">
-        <v>68</v>
+        <v>62</v>
       </c>
       <c r="B14" s="23" t="s">
-        <v>66</v>
+        <v>60</v>
       </c>
       <c r="C14" s="5" t="s">
-        <v>69</v>
+        <v>63</v>
       </c>
       <c r="D14" s="24" t="s">
-        <v>42</v>
+        <v>36</v>
       </c>
       <c r="E14" s="6">
         <v>1</v>
@@ -3202,23 +3232,23 @@
         <v>1</v>
       </c>
       <c r="G14" s="6" t="s">
-        <v>43</v>
+        <v>37</v>
       </c>
       <c r="H14" s="5"/>
       <c r="I14" s="5"/>
     </row>
     <row r="15" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A15" s="15" t="s">
-        <v>70</v>
+        <v>64</v>
       </c>
       <c r="B15" s="25" t="s">
-        <v>66</v>
+        <v>60</v>
       </c>
       <c r="C15" s="9" t="s">
-        <v>71</v>
+        <v>65</v>
       </c>
       <c r="D15" s="24" t="s">
-        <v>42</v>
+        <v>36</v>
       </c>
       <c r="E15" s="10">
         <v>1</v>
@@ -3227,23 +3257,23 @@
         <v>0.5</v>
       </c>
       <c r="G15" s="10" t="s">
-        <v>43</v>
+        <v>37</v>
       </c>
       <c r="H15" s="9"/>
       <c r="I15" s="9"/>
     </row>
     <row r="16" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A16" s="22" t="s">
-        <v>72</v>
+        <v>66</v>
       </c>
       <c r="B16" s="23" t="s">
-        <v>66</v>
+        <v>60</v>
       </c>
       <c r="C16" s="5" t="s">
-        <v>73</v>
+        <v>67</v>
       </c>
       <c r="D16" s="24" t="s">
-        <v>42</v>
+        <v>36</v>
       </c>
       <c r="E16" s="6">
         <v>1</v>
@@ -3252,23 +3282,23 @@
         <v>1</v>
       </c>
       <c r="G16" s="6" t="s">
-        <v>43</v>
+        <v>37</v>
       </c>
       <c r="H16" s="5"/>
       <c r="I16" s="5"/>
     </row>
     <row r="17" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A17" s="15" t="s">
-        <v>74</v>
+        <v>68</v>
       </c>
       <c r="B17" s="25" t="s">
-        <v>75</v>
+        <v>69</v>
       </c>
       <c r="C17" s="9" t="s">
-        <v>76</v>
+        <v>70</v>
       </c>
       <c r="D17" s="24" t="s">
-        <v>42</v>
+        <v>36</v>
       </c>
       <c r="E17" s="10">
         <v>2</v>
@@ -3277,23 +3307,23 @@
         <v>1</v>
       </c>
       <c r="G17" s="10" t="s">
-        <v>77</v>
+        <v>71</v>
       </c>
       <c r="H17" s="9"/>
       <c r="I17" s="9"/>
     </row>
     <row r="18" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A18" s="22" t="s">
-        <v>78</v>
+        <v>72</v>
       </c>
       <c r="B18" s="23" t="s">
-        <v>75</v>
+        <v>69</v>
       </c>
       <c r="C18" s="5" t="s">
-        <v>79</v>
+        <v>73</v>
       </c>
       <c r="D18" s="24" t="s">
-        <v>42</v>
+        <v>36</v>
       </c>
       <c r="E18" s="6">
         <v>2</v>
@@ -3302,23 +3332,23 @@
         <v>1</v>
       </c>
       <c r="G18" s="6" t="s">
-        <v>77</v>
+        <v>71</v>
       </c>
       <c r="H18" s="5"/>
       <c r="I18" s="5"/>
     </row>
     <row r="19" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A19" s="15" t="s">
-        <v>80</v>
+        <v>74</v>
       </c>
       <c r="B19" s="25" t="s">
+        <v>69</v>
+      </c>
+      <c r="C19" s="9" t="s">
         <v>75</v>
       </c>
-      <c r="C19" s="9" t="s">
-        <v>81</v>
-      </c>
       <c r="D19" s="24" t="s">
-        <v>42</v>
+        <v>36</v>
       </c>
       <c r="E19" s="10">
         <v>2</v>
@@ -3327,23 +3357,23 @@
         <v>1</v>
       </c>
       <c r="G19" s="10" t="s">
-        <v>77</v>
+        <v>71</v>
       </c>
       <c r="H19" s="9"/>
       <c r="I19" s="9"/>
     </row>
     <row r="20" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A20" s="22" t="s">
-        <v>82</v>
+        <v>76</v>
       </c>
       <c r="B20" s="23" t="s">
-        <v>75</v>
+        <v>69</v>
       </c>
       <c r="C20" s="5" t="s">
-        <v>83</v>
+        <v>77</v>
       </c>
       <c r="D20" s="24" t="s">
-        <v>42</v>
+        <v>36</v>
       </c>
       <c r="E20" s="6">
         <v>2</v>
@@ -3352,23 +3382,23 @@
         <v>0.5</v>
       </c>
       <c r="G20" s="6" t="s">
-        <v>77</v>
+        <v>71</v>
       </c>
       <c r="H20" s="5"/>
       <c r="I20" s="5"/>
     </row>
     <row r="21" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A21" s="15" t="s">
-        <v>84</v>
+        <v>78</v>
       </c>
       <c r="B21" s="25" t="s">
-        <v>75</v>
+        <v>69</v>
       </c>
       <c r="C21" s="9" t="s">
-        <v>85</v>
+        <v>79</v>
       </c>
       <c r="D21" s="24" t="s">
-        <v>42</v>
+        <v>36</v>
       </c>
       <c r="E21" s="10">
         <v>2</v>
@@ -3377,23 +3407,23 @@
         <v>0.5</v>
       </c>
       <c r="G21" s="10" t="s">
-        <v>77</v>
+        <v>71</v>
       </c>
       <c r="H21" s="9"/>
       <c r="I21" s="9"/>
     </row>
     <row r="22" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A22" s="22" t="s">
-        <v>86</v>
+        <v>80</v>
       </c>
       <c r="B22" s="23" t="s">
-        <v>87</v>
+        <v>81</v>
       </c>
       <c r="C22" s="5" t="s">
-        <v>88</v>
+        <v>82</v>
       </c>
       <c r="D22" s="24" t="s">
-        <v>42</v>
+        <v>36</v>
       </c>
       <c r="E22" s="6">
         <v>2</v>
@@ -3402,23 +3432,23 @@
         <v>1</v>
       </c>
       <c r="G22" s="6" t="s">
-        <v>77</v>
+        <v>71</v>
       </c>
       <c r="H22" s="5"/>
       <c r="I22" s="5"/>
     </row>
     <row r="23" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A23" s="15" t="s">
-        <v>89</v>
+        <v>83</v>
       </c>
       <c r="B23" s="25" t="s">
-        <v>87</v>
+        <v>81</v>
       </c>
       <c r="C23" s="9" t="s">
-        <v>90</v>
+        <v>84</v>
       </c>
       <c r="D23" s="24" t="s">
-        <v>42</v>
+        <v>36</v>
       </c>
       <c r="E23" s="10">
         <v>2</v>
@@ -3427,23 +3457,23 @@
         <v>1</v>
       </c>
       <c r="G23" s="10" t="s">
-        <v>77</v>
+        <v>71</v>
       </c>
       <c r="H23" s="9"/>
       <c r="I23" s="9"/>
     </row>
     <row r="24" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A24" s="22" t="s">
-        <v>91</v>
+        <v>85</v>
       </c>
       <c r="B24" s="23" t="s">
-        <v>87</v>
+        <v>81</v>
       </c>
       <c r="C24" s="5" t="s">
-        <v>92</v>
+        <v>86</v>
       </c>
       <c r="D24" s="24" t="s">
-        <v>42</v>
+        <v>36</v>
       </c>
       <c r="E24" s="6">
         <v>2</v>
@@ -3452,23 +3482,23 @@
         <v>0.5</v>
       </c>
       <c r="G24" s="6" t="s">
-        <v>77</v>
+        <v>71</v>
       </c>
       <c r="H24" s="5"/>
       <c r="I24" s="5"/>
     </row>
     <row r="25" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A25" s="15" t="s">
-        <v>93</v>
+        <v>87</v>
       </c>
       <c r="B25" s="25" t="s">
-        <v>87</v>
+        <v>81</v>
       </c>
       <c r="C25" s="9" t="s">
-        <v>94</v>
+        <v>88</v>
       </c>
       <c r="D25" s="24" t="s">
-        <v>42</v>
+        <v>36</v>
       </c>
       <c r="E25" s="10">
         <v>2</v>
@@ -3477,23 +3507,23 @@
         <v>1</v>
       </c>
       <c r="G25" s="10" t="s">
-        <v>77</v>
+        <v>71</v>
       </c>
       <c r="H25" s="9"/>
       <c r="I25" s="9"/>
     </row>
     <row r="26" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A26" s="22" t="s">
-        <v>95</v>
+        <v>89</v>
       </c>
       <c r="B26" s="23" t="s">
-        <v>87</v>
+        <v>81</v>
       </c>
       <c r="C26" s="5" t="s">
-        <v>96</v>
+        <v>90</v>
       </c>
       <c r="D26" s="24" t="s">
-        <v>42</v>
+        <v>36</v>
       </c>
       <c r="E26" s="6">
         <v>2</v>
@@ -3502,23 +3532,23 @@
         <v>0.5</v>
       </c>
       <c r="G26" s="6" t="s">
-        <v>77</v>
+        <v>71</v>
       </c>
       <c r="H26" s="5"/>
       <c r="I26" s="5"/>
     </row>
     <row r="27" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A27" s="15" t="s">
-        <v>97</v>
+        <v>91</v>
       </c>
       <c r="B27" s="25" t="s">
-        <v>98</v>
+        <v>92</v>
       </c>
       <c r="C27" s="9" t="s">
-        <v>99</v>
+        <v>93</v>
       </c>
       <c r="D27" s="24" t="s">
-        <v>42</v>
+        <v>36</v>
       </c>
       <c r="E27" s="10">
         <v>2</v>
@@ -3527,23 +3557,23 @@
         <v>1</v>
       </c>
       <c r="G27" s="10" t="s">
-        <v>77</v>
+        <v>71</v>
       </c>
       <c r="H27" s="9"/>
       <c r="I27" s="9"/>
     </row>
     <row r="28" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A28" s="22" t="s">
-        <v>100</v>
+        <v>94</v>
       </c>
       <c r="B28" s="23" t="s">
-        <v>98</v>
+        <v>92</v>
       </c>
       <c r="C28" s="5" t="s">
-        <v>101</v>
+        <v>95</v>
       </c>
       <c r="D28" s="24" t="s">
-        <v>42</v>
+        <v>36</v>
       </c>
       <c r="E28" s="6">
         <v>2</v>
@@ -3552,23 +3582,23 @@
         <v>1</v>
       </c>
       <c r="G28" s="6" t="s">
-        <v>77</v>
+        <v>71</v>
       </c>
       <c r="H28" s="5"/>
       <c r="I28" s="5"/>
     </row>
     <row r="29" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A29" s="15" t="s">
-        <v>102</v>
+        <v>96</v>
       </c>
       <c r="B29" s="25" t="s">
-        <v>98</v>
+        <v>92</v>
       </c>
       <c r="C29" s="9" t="s">
-        <v>103</v>
+        <v>97</v>
       </c>
       <c r="D29" s="24" t="s">
-        <v>42</v>
+        <v>36</v>
       </c>
       <c r="E29" s="10">
         <v>2</v>
@@ -3577,23 +3607,23 @@
         <v>1.5</v>
       </c>
       <c r="G29" s="10" t="s">
-        <v>77</v>
+        <v>71</v>
       </c>
       <c r="H29" s="9"/>
       <c r="I29" s="9"/>
     </row>
     <row r="30" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A30" s="22" t="s">
-        <v>104</v>
+        <v>98</v>
       </c>
       <c r="B30" s="23" t="s">
-        <v>98</v>
+        <v>92</v>
       </c>
       <c r="C30" s="5" t="s">
-        <v>105</v>
+        <v>99</v>
       </c>
       <c r="D30" s="24" t="s">
-        <v>42</v>
+        <v>36</v>
       </c>
       <c r="E30" s="6">
         <v>2</v>
@@ -3602,23 +3632,23 @@
         <v>1</v>
       </c>
       <c r="G30" s="6" t="s">
-        <v>77</v>
+        <v>71</v>
       </c>
       <c r="H30" s="5"/>
       <c r="I30" s="5"/>
     </row>
     <row r="31" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A31" s="15" t="s">
-        <v>106</v>
+        <v>100</v>
       </c>
       <c r="B31" s="25" t="s">
-        <v>107</v>
+        <v>101</v>
       </c>
       <c r="C31" s="9" t="s">
-        <v>108</v>
+        <v>102</v>
       </c>
       <c r="D31" s="24" t="s">
-        <v>42</v>
+        <v>36</v>
       </c>
       <c r="E31" s="10">
         <v>2</v>
@@ -3627,23 +3657,23 @@
         <v>1</v>
       </c>
       <c r="G31" s="10" t="s">
-        <v>77</v>
+        <v>71</v>
       </c>
       <c r="H31" s="9"/>
       <c r="I31" s="9"/>
     </row>
     <row r="32" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A32" s="22" t="s">
-        <v>109</v>
+        <v>103</v>
       </c>
       <c r="B32" s="23" t="s">
-        <v>107</v>
+        <v>101</v>
       </c>
       <c r="C32" s="5" t="s">
-        <v>110</v>
+        <v>104</v>
       </c>
       <c r="D32" s="24" t="s">
-        <v>42</v>
+        <v>36</v>
       </c>
       <c r="E32" s="6">
         <v>2</v>
@@ -3652,23 +3682,23 @@
         <v>1.5</v>
       </c>
       <c r="G32" s="6" t="s">
-        <v>77</v>
+        <v>71</v>
       </c>
       <c r="H32" s="5"/>
       <c r="I32" s="5"/>
     </row>
     <row r="33" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A33" s="15" t="s">
-        <v>111</v>
+        <v>105</v>
       </c>
       <c r="B33" s="25" t="s">
-        <v>107</v>
+        <v>101</v>
       </c>
       <c r="C33" s="9" t="s">
-        <v>112</v>
+        <v>106</v>
       </c>
       <c r="D33" s="24" t="s">
-        <v>42</v>
+        <v>36</v>
       </c>
       <c r="E33" s="10">
         <v>2</v>
@@ -3677,23 +3707,23 @@
         <v>1</v>
       </c>
       <c r="G33" s="10" t="s">
-        <v>77</v>
+        <v>71</v>
       </c>
       <c r="H33" s="9"/>
       <c r="I33" s="9"/>
     </row>
     <row r="34" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A34" s="22" t="s">
-        <v>113</v>
+        <v>107</v>
       </c>
       <c r="B34" s="23" t="s">
-        <v>107</v>
+        <v>101</v>
       </c>
       <c r="C34" s="5" t="s">
-        <v>114</v>
+        <v>108</v>
       </c>
       <c r="D34" s="24" t="s">
-        <v>42</v>
+        <v>36</v>
       </c>
       <c r="E34" s="6">
         <v>2</v>
@@ -3702,23 +3732,23 @@
         <v>1</v>
       </c>
       <c r="G34" s="6" t="s">
-        <v>77</v>
+        <v>71</v>
       </c>
       <c r="H34" s="5"/>
       <c r="I34" s="5"/>
     </row>
     <row r="35" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A35" s="15" t="s">
-        <v>115</v>
+        <v>109</v>
       </c>
       <c r="B35" s="25" t="s">
-        <v>116</v>
+        <v>110</v>
       </c>
       <c r="C35" s="9" t="s">
-        <v>117</v>
+        <v>111</v>
       </c>
       <c r="D35" s="26" t="s">
-        <v>118</v>
+        <v>112</v>
       </c>
       <c r="E35" s="10">
         <v>3</v>
@@ -3727,23 +3757,23 @@
         <v>1</v>
       </c>
       <c r="G35" s="10" t="s">
-        <v>77</v>
+        <v>71</v>
       </c>
       <c r="H35" s="9"/>
       <c r="I35" s="9"/>
     </row>
     <row r="36" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A36" s="22" t="s">
-        <v>119</v>
+        <v>113</v>
       </c>
       <c r="B36" s="23" t="s">
-        <v>116</v>
+        <v>110</v>
       </c>
       <c r="C36" s="5" t="s">
-        <v>120</v>
+        <v>114</v>
       </c>
       <c r="D36" s="26" t="s">
-        <v>118</v>
+        <v>112</v>
       </c>
       <c r="E36" s="6">
         <v>3</v>
@@ -3752,23 +3782,23 @@
         <v>1</v>
       </c>
       <c r="G36" s="6" t="s">
-        <v>77</v>
+        <v>71</v>
       </c>
       <c r="H36" s="5"/>
       <c r="I36" s="5"/>
     </row>
     <row r="37" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A37" s="15" t="s">
-        <v>121</v>
+        <v>115</v>
       </c>
       <c r="B37" s="25" t="s">
+        <v>110</v>
+      </c>
+      <c r="C37" s="9" t="s">
         <v>116</v>
       </c>
-      <c r="C37" s="9" t="s">
-        <v>122</v>
-      </c>
       <c r="D37" s="26" t="s">
-        <v>118</v>
+        <v>112</v>
       </c>
       <c r="E37" s="10">
         <v>3</v>
@@ -3777,23 +3807,23 @@
         <v>1</v>
       </c>
       <c r="G37" s="10" t="s">
-        <v>77</v>
+        <v>71</v>
       </c>
       <c r="H37" s="9"/>
       <c r="I37" s="9"/>
     </row>
     <row r="38" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A38" s="22" t="s">
-        <v>123</v>
+        <v>117</v>
       </c>
       <c r="B38" s="23" t="s">
-        <v>124</v>
+        <v>118</v>
       </c>
       <c r="C38" s="5" t="s">
-        <v>125</v>
+        <v>119</v>
       </c>
       <c r="D38" s="26" t="s">
-        <v>118</v>
+        <v>112</v>
       </c>
       <c r="E38" s="6">
         <v>3</v>
@@ -3802,23 +3832,23 @@
         <v>1</v>
       </c>
       <c r="G38" s="6" t="s">
-        <v>77</v>
+        <v>71</v>
       </c>
       <c r="H38" s="5"/>
       <c r="I38" s="5"/>
     </row>
     <row r="39" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A39" s="15" t="s">
-        <v>126</v>
+        <v>120</v>
       </c>
       <c r="B39" s="25" t="s">
-        <v>124</v>
+        <v>118</v>
       </c>
       <c r="C39" s="9" t="s">
-        <v>127</v>
+        <v>121</v>
       </c>
       <c r="D39" s="26" t="s">
-        <v>118</v>
+        <v>112</v>
       </c>
       <c r="E39" s="10">
         <v>3</v>
@@ -3827,23 +3857,23 @@
         <v>0.5</v>
       </c>
       <c r="G39" s="10" t="s">
-        <v>77</v>
+        <v>71</v>
       </c>
       <c r="H39" s="9"/>
       <c r="I39" s="9"/>
     </row>
     <row r="40" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A40" s="22" t="s">
-        <v>128</v>
+        <v>122</v>
       </c>
       <c r="B40" s="23" t="s">
-        <v>124</v>
+        <v>118</v>
       </c>
       <c r="C40" s="5" t="s">
-        <v>129</v>
+        <v>123</v>
       </c>
       <c r="D40" s="26" t="s">
-        <v>118</v>
+        <v>112</v>
       </c>
       <c r="E40" s="6">
         <v>3</v>
@@ -3852,23 +3882,23 @@
         <v>1</v>
       </c>
       <c r="G40" s="6" t="s">
-        <v>77</v>
+        <v>71</v>
       </c>
       <c r="H40" s="5"/>
       <c r="I40" s="5"/>
     </row>
     <row r="41" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A41" s="15" t="s">
-        <v>130</v>
+        <v>124</v>
       </c>
       <c r="B41" s="25" t="s">
-        <v>131</v>
+        <v>125</v>
       </c>
       <c r="C41" s="9" t="s">
-        <v>132</v>
+        <v>126</v>
       </c>
       <c r="D41" s="24" t="s">
-        <v>42</v>
+        <v>36</v>
       </c>
       <c r="E41" s="10">
         <v>3</v>
@@ -3877,23 +3907,23 @@
         <v>1</v>
       </c>
       <c r="G41" s="10" t="s">
-        <v>77</v>
+        <v>71</v>
       </c>
       <c r="H41" s="9"/>
       <c r="I41" s="9"/>
     </row>
     <row r="42" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A42" s="22" t="s">
-        <v>133</v>
+        <v>127</v>
       </c>
       <c r="B42" s="23" t="s">
-        <v>131</v>
+        <v>125</v>
       </c>
       <c r="C42" s="5" t="s">
-        <v>134</v>
+        <v>128</v>
       </c>
       <c r="D42" s="24" t="s">
-        <v>42</v>
+        <v>36</v>
       </c>
       <c r="E42" s="6">
         <v>3</v>
@@ -3902,23 +3932,23 @@
         <v>0.5</v>
       </c>
       <c r="G42" s="6" t="s">
-        <v>77</v>
+        <v>71</v>
       </c>
       <c r="H42" s="5"/>
       <c r="I42" s="5"/>
     </row>
     <row r="43" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A43" s="15" t="s">
-        <v>135</v>
+        <v>129</v>
       </c>
       <c r="B43" s="25" t="s">
-        <v>136</v>
+        <v>130</v>
       </c>
       <c r="C43" s="9" t="s">
-        <v>137</v>
+        <v>131</v>
       </c>
       <c r="D43" s="24" t="s">
-        <v>42</v>
+        <v>36</v>
       </c>
       <c r="E43" s="10">
         <v>3</v>
@@ -3927,23 +3957,23 @@
         <v>1</v>
       </c>
       <c r="G43" s="10" t="s">
-        <v>77</v>
+        <v>71</v>
       </c>
       <c r="H43" s="9"/>
       <c r="I43" s="9"/>
     </row>
     <row r="44" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A44" s="22" t="s">
-        <v>138</v>
+        <v>132</v>
       </c>
       <c r="B44" s="23" t="s">
-        <v>136</v>
+        <v>130</v>
       </c>
       <c r="C44" s="5" t="s">
-        <v>139</v>
+        <v>133</v>
       </c>
       <c r="D44" s="24" t="s">
-        <v>42</v>
+        <v>36</v>
       </c>
       <c r="E44" s="6">
         <v>3</v>
@@ -3952,23 +3982,23 @@
         <v>2</v>
       </c>
       <c r="G44" s="6" t="s">
-        <v>77</v>
+        <v>71</v>
       </c>
       <c r="H44" s="5"/>
       <c r="I44" s="5"/>
     </row>
     <row r="45" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A45" s="15" t="s">
-        <v>140</v>
+        <v>134</v>
       </c>
       <c r="B45" s="25" t="s">
-        <v>136</v>
+        <v>130</v>
       </c>
       <c r="C45" s="9" t="s">
-        <v>141</v>
+        <v>135</v>
       </c>
       <c r="D45" s="24" t="s">
-        <v>42</v>
+        <v>36</v>
       </c>
       <c r="E45" s="10">
         <v>3</v>
@@ -3977,14 +4007,14 @@
         <v>1</v>
       </c>
       <c r="G45" s="10" t="s">
-        <v>77</v>
+        <v>71</v>
       </c>
       <c r="H45" s="9"/>
       <c r="I45" s="9"/>
     </row>
     <row r="47" spans="1:9" x14ac:dyDescent="0.3">
       <c r="C47" s="27" t="s">
-        <v>142</v>
+        <v>136</v>
       </c>
       <c r="F47" s="28">
         <f>SUM(F2:F45)</f>
@@ -3993,7 +4023,7 @@
     </row>
     <row r="48" spans="1:9" x14ac:dyDescent="0.3">
       <c r="C48" s="27" t="s">
-        <v>143</v>
+        <v>137</v>
       </c>
       <c r="F48" s="28">
         <f>SUMIF(G2:G45,"Feito",F2:F45)</f>
@@ -4010,6 +4040,18 @@
   </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{CCE6A557-97BC-4b89-ADB6-D9C93CAAB3DF}">
+      <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" count="1">
+        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{675B0BE3-E490-4D87-ADC0-8146D9EEBB4D}">
+          <x14:formula1>
+            <xm:f>Equipes!$B$2:$E$2</xm:f>
+          </x14:formula1>
+          <xm:sqref>H2:H45</xm:sqref>
+        </x14:dataValidation>
+      </x14:dataValidations>
+    </ext>
+  </extLst>
 </worksheet>
 </file>
 
@@ -4031,45 +4073,45 @@
   <sheetData>
     <row r="1" spans="1:9" ht="26.4" x14ac:dyDescent="0.3">
       <c r="A1" s="29" t="s">
+        <v>24</v>
+      </c>
+      <c r="B1" s="29" t="s">
+        <v>25</v>
+      </c>
+      <c r="C1" s="29" t="s">
+        <v>26</v>
+      </c>
+      <c r="D1" s="29" t="s">
+        <v>27</v>
+      </c>
+      <c r="E1" s="29" t="s">
+        <v>28</v>
+      </c>
+      <c r="F1" s="29" t="s">
+        <v>29</v>
+      </c>
+      <c r="G1" s="29" t="s">
         <v>30</v>
       </c>
-      <c r="B1" s="29" t="s">
+      <c r="H1" s="29" t="s">
         <v>31</v>
       </c>
-      <c r="C1" s="29" t="s">
+      <c r="I1" s="29" t="s">
         <v>32</v>
-      </c>
-      <c r="D1" s="29" t="s">
-        <v>33</v>
-      </c>
-      <c r="E1" s="29" t="s">
-        <v>34</v>
-      </c>
-      <c r="F1" s="29" t="s">
-        <v>35</v>
-      </c>
-      <c r="G1" s="29" t="s">
-        <v>36</v>
-      </c>
-      <c r="H1" s="29" t="s">
-        <v>37</v>
-      </c>
-      <c r="I1" s="29" t="s">
-        <v>38</v>
       </c>
     </row>
     <row r="2" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A2" s="22" t="s">
-        <v>144</v>
+        <v>138</v>
       </c>
       <c r="B2" s="23" t="s">
-        <v>145</v>
+        <v>139</v>
       </c>
       <c r="C2" s="5" t="s">
-        <v>146</v>
+        <v>140</v>
       </c>
       <c r="D2" s="24" t="s">
-        <v>42</v>
+        <v>36</v>
       </c>
       <c r="E2" s="6">
         <v>1</v>
@@ -4078,23 +4120,23 @@
         <v>0.5</v>
       </c>
       <c r="G2" s="6" t="s">
-        <v>43</v>
+        <v>37</v>
       </c>
       <c r="H2" s="5"/>
       <c r="I2" s="5"/>
     </row>
     <row r="3" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A3" s="15" t="s">
-        <v>147</v>
+        <v>141</v>
       </c>
       <c r="B3" s="25" t="s">
-        <v>145</v>
+        <v>139</v>
       </c>
       <c r="C3" s="9" t="s">
-        <v>148</v>
+        <v>142</v>
       </c>
       <c r="D3" s="24" t="s">
-        <v>42</v>
+        <v>36</v>
       </c>
       <c r="E3" s="10">
         <v>1</v>
@@ -4103,23 +4145,23 @@
         <v>1.5</v>
       </c>
       <c r="G3" s="10" t="s">
-        <v>43</v>
+        <v>37</v>
       </c>
       <c r="H3" s="9"/>
       <c r="I3" s="9"/>
     </row>
     <row r="4" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A4" s="22" t="s">
-        <v>149</v>
+        <v>143</v>
       </c>
       <c r="B4" s="23" t="s">
-        <v>145</v>
+        <v>139</v>
       </c>
       <c r="C4" s="5" t="s">
-        <v>150</v>
+        <v>144</v>
       </c>
       <c r="D4" s="24" t="s">
-        <v>42</v>
+        <v>36</v>
       </c>
       <c r="E4" s="6">
         <v>1</v>
@@ -4128,23 +4170,23 @@
         <v>1</v>
       </c>
       <c r="G4" s="6" t="s">
-        <v>43</v>
+        <v>37</v>
       </c>
       <c r="H4" s="5"/>
       <c r="I4" s="5"/>
     </row>
     <row r="5" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A5" s="15" t="s">
-        <v>151</v>
+        <v>145</v>
       </c>
       <c r="B5" s="25" t="s">
-        <v>145</v>
+        <v>139</v>
       </c>
       <c r="C5" s="9" t="s">
-        <v>152</v>
+        <v>146</v>
       </c>
       <c r="D5" s="24" t="s">
-        <v>42</v>
+        <v>36</v>
       </c>
       <c r="E5" s="10">
         <v>1</v>
@@ -4153,23 +4195,23 @@
         <v>1</v>
       </c>
       <c r="G5" s="10" t="s">
-        <v>43</v>
+        <v>37</v>
       </c>
       <c r="H5" s="9"/>
       <c r="I5" s="9"/>
     </row>
     <row r="6" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A6" s="22" t="s">
-        <v>153</v>
+        <v>147</v>
       </c>
       <c r="B6" s="23" t="s">
-        <v>145</v>
+        <v>139</v>
       </c>
       <c r="C6" s="5" t="s">
-        <v>154</v>
+        <v>148</v>
       </c>
       <c r="D6" s="24" t="s">
-        <v>42</v>
+        <v>36</v>
       </c>
       <c r="E6" s="6">
         <v>1</v>
@@ -4178,23 +4220,23 @@
         <v>1</v>
       </c>
       <c r="G6" s="6" t="s">
-        <v>43</v>
+        <v>37</v>
       </c>
       <c r="H6" s="5"/>
       <c r="I6" s="5"/>
     </row>
     <row r="7" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A7" s="15" t="s">
-        <v>155</v>
+        <v>149</v>
       </c>
       <c r="B7" s="25" t="s">
-        <v>156</v>
+        <v>150</v>
       </c>
       <c r="C7" s="9" t="s">
-        <v>157</v>
+        <v>151</v>
       </c>
       <c r="D7" s="24" t="s">
-        <v>42</v>
+        <v>36</v>
       </c>
       <c r="E7" s="10">
         <v>1</v>
@@ -4203,23 +4245,23 @@
         <v>0.5</v>
       </c>
       <c r="G7" s="10" t="s">
-        <v>43</v>
+        <v>37</v>
       </c>
       <c r="H7" s="9"/>
       <c r="I7" s="9"/>
     </row>
     <row r="8" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A8" s="22" t="s">
-        <v>158</v>
+        <v>152</v>
       </c>
       <c r="B8" s="23" t="s">
-        <v>156</v>
+        <v>150</v>
       </c>
       <c r="C8" s="5" t="s">
-        <v>159</v>
+        <v>153</v>
       </c>
       <c r="D8" s="24" t="s">
-        <v>42</v>
+        <v>36</v>
       </c>
       <c r="E8" s="6">
         <v>1</v>
@@ -4228,23 +4270,23 @@
         <v>1</v>
       </c>
       <c r="G8" s="6" t="s">
-        <v>43</v>
+        <v>37</v>
       </c>
       <c r="H8" s="5"/>
       <c r="I8" s="5"/>
     </row>
     <row r="9" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A9" s="15" t="s">
-        <v>160</v>
+        <v>154</v>
       </c>
       <c r="B9" s="25" t="s">
-        <v>156</v>
+        <v>150</v>
       </c>
       <c r="C9" s="9" t="s">
-        <v>161</v>
+        <v>155</v>
       </c>
       <c r="D9" s="24" t="s">
-        <v>42</v>
+        <v>36</v>
       </c>
       <c r="E9" s="10">
         <v>1</v>
@@ -4253,23 +4295,23 @@
         <v>1.5</v>
       </c>
       <c r="G9" s="10" t="s">
-        <v>43</v>
+        <v>37</v>
       </c>
       <c r="H9" s="9"/>
       <c r="I9" s="9"/>
     </row>
     <row r="10" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A10" s="22" t="s">
-        <v>162</v>
+        <v>156</v>
       </c>
       <c r="B10" s="23" t="s">
-        <v>156</v>
+        <v>150</v>
       </c>
       <c r="C10" s="5" t="s">
-        <v>163</v>
+        <v>157</v>
       </c>
       <c r="D10" s="24" t="s">
-        <v>42</v>
+        <v>36</v>
       </c>
       <c r="E10" s="6">
         <v>1</v>
@@ -4278,23 +4320,23 @@
         <v>0.5</v>
       </c>
       <c r="G10" s="6" t="s">
-        <v>43</v>
+        <v>37</v>
       </c>
       <c r="H10" s="5"/>
       <c r="I10" s="5"/>
     </row>
     <row r="11" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A11" s="15" t="s">
-        <v>164</v>
+        <v>158</v>
       </c>
       <c r="B11" s="25" t="s">
-        <v>165</v>
+        <v>159</v>
       </c>
       <c r="C11" s="9" t="s">
-        <v>166</v>
+        <v>160</v>
       </c>
       <c r="D11" s="24" t="s">
-        <v>42</v>
+        <v>36</v>
       </c>
       <c r="E11" s="10">
         <v>1</v>
@@ -4303,23 +4345,23 @@
         <v>1</v>
       </c>
       <c r="G11" s="10" t="s">
-        <v>43</v>
+        <v>37</v>
       </c>
       <c r="H11" s="9"/>
       <c r="I11" s="9"/>
     </row>
     <row r="12" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A12" s="22" t="s">
-        <v>167</v>
+        <v>161</v>
       </c>
       <c r="B12" s="23" t="s">
-        <v>165</v>
+        <v>159</v>
       </c>
       <c r="C12" s="5" t="s">
-        <v>168</v>
+        <v>162</v>
       </c>
       <c r="D12" s="24" t="s">
-        <v>42</v>
+        <v>36</v>
       </c>
       <c r="E12" s="6">
         <v>1</v>
@@ -4328,23 +4370,23 @@
         <v>2</v>
       </c>
       <c r="G12" s="6" t="s">
-        <v>43</v>
+        <v>37</v>
       </c>
       <c r="H12" s="5"/>
       <c r="I12" s="5"/>
     </row>
     <row r="13" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A13" s="15" t="s">
-        <v>169</v>
+        <v>163</v>
       </c>
       <c r="B13" s="25" t="s">
-        <v>165</v>
+        <v>159</v>
       </c>
       <c r="C13" s="9" t="s">
-        <v>170</v>
+        <v>164</v>
       </c>
       <c r="D13" s="24" t="s">
-        <v>42</v>
+        <v>36</v>
       </c>
       <c r="E13" s="10">
         <v>1</v>
@@ -4353,23 +4395,23 @@
         <v>2</v>
       </c>
       <c r="G13" s="10" t="s">
-        <v>43</v>
+        <v>37</v>
       </c>
       <c r="H13" s="9"/>
       <c r="I13" s="9"/>
     </row>
     <row r="14" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A14" s="22" t="s">
-        <v>171</v>
+        <v>165</v>
       </c>
       <c r="B14" s="23" t="s">
-        <v>165</v>
+        <v>159</v>
       </c>
       <c r="C14" s="5" t="s">
-        <v>172</v>
+        <v>166</v>
       </c>
       <c r="D14" s="24" t="s">
-        <v>42</v>
+        <v>36</v>
       </c>
       <c r="E14" s="6">
         <v>1</v>
@@ -4378,23 +4420,23 @@
         <v>2</v>
       </c>
       <c r="G14" s="6" t="s">
-        <v>43</v>
+        <v>37</v>
       </c>
       <c r="H14" s="5"/>
       <c r="I14" s="5"/>
     </row>
     <row r="15" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A15" s="15" t="s">
-        <v>173</v>
+        <v>167</v>
       </c>
       <c r="B15" s="25" t="s">
-        <v>165</v>
+        <v>159</v>
       </c>
       <c r="C15" s="9" t="s">
-        <v>174</v>
+        <v>168</v>
       </c>
       <c r="D15" s="24" t="s">
-        <v>42</v>
+        <v>36</v>
       </c>
       <c r="E15" s="10">
         <v>1</v>
@@ -4403,23 +4445,23 @@
         <v>1</v>
       </c>
       <c r="G15" s="10" t="s">
-        <v>43</v>
+        <v>37</v>
       </c>
       <c r="H15" s="9"/>
       <c r="I15" s="9"/>
     </row>
     <row r="16" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A16" s="22" t="s">
-        <v>175</v>
+        <v>169</v>
       </c>
       <c r="B16" s="23" t="s">
-        <v>165</v>
+        <v>159</v>
       </c>
       <c r="C16" s="5" t="s">
-        <v>176</v>
+        <v>170</v>
       </c>
       <c r="D16" s="24" t="s">
-        <v>42</v>
+        <v>36</v>
       </c>
       <c r="E16" s="6">
         <v>1</v>
@@ -4428,23 +4470,23 @@
         <v>1</v>
       </c>
       <c r="G16" s="6" t="s">
-        <v>43</v>
+        <v>37</v>
       </c>
       <c r="H16" s="5"/>
       <c r="I16" s="5"/>
     </row>
     <row r="17" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A17" s="15" t="s">
-        <v>177</v>
+        <v>171</v>
       </c>
       <c r="B17" s="25" t="s">
-        <v>178</v>
+        <v>172</v>
       </c>
       <c r="C17" s="9" t="s">
-        <v>179</v>
+        <v>173</v>
       </c>
       <c r="D17" s="24" t="s">
-        <v>42</v>
+        <v>36</v>
       </c>
       <c r="E17" s="10">
         <v>2</v>
@@ -4453,23 +4495,23 @@
         <v>1</v>
       </c>
       <c r="G17" s="10" t="s">
-        <v>77</v>
+        <v>71</v>
       </c>
       <c r="H17" s="9"/>
       <c r="I17" s="9"/>
     </row>
     <row r="18" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A18" s="22" t="s">
-        <v>180</v>
+        <v>174</v>
       </c>
       <c r="B18" s="23" t="s">
-        <v>178</v>
+        <v>172</v>
       </c>
       <c r="C18" s="5" t="s">
-        <v>181</v>
+        <v>175</v>
       </c>
       <c r="D18" s="24" t="s">
-        <v>42</v>
+        <v>36</v>
       </c>
       <c r="E18" s="6">
         <v>2</v>
@@ -4478,23 +4520,23 @@
         <v>1.5</v>
       </c>
       <c r="G18" s="6" t="s">
-        <v>77</v>
+        <v>71</v>
       </c>
       <c r="H18" s="5"/>
       <c r="I18" s="5"/>
     </row>
     <row r="19" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A19" s="15" t="s">
-        <v>182</v>
+        <v>176</v>
       </c>
       <c r="B19" s="25" t="s">
-        <v>178</v>
+        <v>172</v>
       </c>
       <c r="C19" s="9" t="s">
-        <v>183</v>
+        <v>177</v>
       </c>
       <c r="D19" s="24" t="s">
-        <v>42</v>
+        <v>36</v>
       </c>
       <c r="E19" s="10">
         <v>2</v>
@@ -4503,23 +4545,23 @@
         <v>1</v>
       </c>
       <c r="G19" s="10" t="s">
-        <v>77</v>
+        <v>71</v>
       </c>
       <c r="H19" s="9"/>
       <c r="I19" s="9"/>
     </row>
     <row r="20" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A20" s="22" t="s">
-        <v>184</v>
+        <v>178</v>
       </c>
       <c r="B20" s="23" t="s">
-        <v>178</v>
+        <v>172</v>
       </c>
       <c r="C20" s="5" t="s">
-        <v>185</v>
+        <v>179</v>
       </c>
       <c r="D20" s="24" t="s">
-        <v>42</v>
+        <v>36</v>
       </c>
       <c r="E20" s="6">
         <v>2</v>
@@ -4528,23 +4570,23 @@
         <v>0.5</v>
       </c>
       <c r="G20" s="6" t="s">
-        <v>77</v>
+        <v>71</v>
       </c>
       <c r="H20" s="5"/>
       <c r="I20" s="5"/>
     </row>
     <row r="21" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A21" s="15" t="s">
-        <v>186</v>
+        <v>180</v>
       </c>
       <c r="B21" s="25" t="s">
-        <v>187</v>
+        <v>181</v>
       </c>
       <c r="C21" s="9" t="s">
-        <v>188</v>
+        <v>182</v>
       </c>
       <c r="D21" s="24" t="s">
-        <v>42</v>
+        <v>36</v>
       </c>
       <c r="E21" s="10">
         <v>2</v>
@@ -4553,23 +4595,23 @@
         <v>1</v>
       </c>
       <c r="G21" s="10" t="s">
-        <v>77</v>
+        <v>71</v>
       </c>
       <c r="H21" s="9"/>
       <c r="I21" s="9"/>
     </row>
     <row r="22" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A22" s="22" t="s">
-        <v>189</v>
+        <v>183</v>
       </c>
       <c r="B22" s="23" t="s">
-        <v>187</v>
+        <v>181</v>
       </c>
       <c r="C22" s="5" t="s">
-        <v>190</v>
+        <v>184</v>
       </c>
       <c r="D22" s="24" t="s">
-        <v>42</v>
+        <v>36</v>
       </c>
       <c r="E22" s="6">
         <v>2</v>
@@ -4578,23 +4620,23 @@
         <v>0.5</v>
       </c>
       <c r="G22" s="6" t="s">
-        <v>77</v>
+        <v>71</v>
       </c>
       <c r="H22" s="5"/>
       <c r="I22" s="5"/>
     </row>
     <row r="23" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A23" s="15" t="s">
-        <v>191</v>
+        <v>185</v>
       </c>
       <c r="B23" s="25" t="s">
-        <v>187</v>
+        <v>181</v>
       </c>
       <c r="C23" s="9" t="s">
-        <v>192</v>
+        <v>186</v>
       </c>
       <c r="D23" s="24" t="s">
-        <v>42</v>
+        <v>36</v>
       </c>
       <c r="E23" s="10">
         <v>2</v>
@@ -4603,23 +4645,23 @@
         <v>0.5</v>
       </c>
       <c r="G23" s="10" t="s">
-        <v>77</v>
+        <v>71</v>
       </c>
       <c r="H23" s="9"/>
       <c r="I23" s="9"/>
     </row>
     <row r="24" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A24" s="22" t="s">
-        <v>193</v>
+        <v>187</v>
       </c>
       <c r="B24" s="23" t="s">
-        <v>194</v>
+        <v>188</v>
       </c>
       <c r="C24" s="5" t="s">
-        <v>195</v>
+        <v>189</v>
       </c>
       <c r="D24" s="24" t="s">
-        <v>42</v>
+        <v>36</v>
       </c>
       <c r="E24" s="6">
         <v>2</v>
@@ -4628,23 +4670,23 @@
         <v>1</v>
       </c>
       <c r="G24" s="6" t="s">
-        <v>77</v>
+        <v>71</v>
       </c>
       <c r="H24" s="5"/>
       <c r="I24" s="5"/>
     </row>
     <row r="25" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A25" s="15" t="s">
-        <v>196</v>
+        <v>190</v>
       </c>
       <c r="B25" s="25" t="s">
-        <v>194</v>
+        <v>188</v>
       </c>
       <c r="C25" s="9" t="s">
-        <v>197</v>
+        <v>191</v>
       </c>
       <c r="D25" s="24" t="s">
-        <v>42</v>
+        <v>36</v>
       </c>
       <c r="E25" s="10">
         <v>2</v>
@@ -4653,23 +4695,23 @@
         <v>1</v>
       </c>
       <c r="G25" s="10" t="s">
-        <v>77</v>
+        <v>71</v>
       </c>
       <c r="H25" s="9"/>
       <c r="I25" s="9"/>
     </row>
     <row r="26" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A26" s="22" t="s">
-        <v>198</v>
+        <v>192</v>
       </c>
       <c r="B26" s="23" t="s">
-        <v>194</v>
+        <v>188</v>
       </c>
       <c r="C26" s="5" t="s">
-        <v>199</v>
+        <v>193</v>
       </c>
       <c r="D26" s="24" t="s">
-        <v>42</v>
+        <v>36</v>
       </c>
       <c r="E26" s="6">
         <v>2</v>
@@ -4678,23 +4720,23 @@
         <v>1</v>
       </c>
       <c r="G26" s="6" t="s">
-        <v>77</v>
+        <v>71</v>
       </c>
       <c r="H26" s="5"/>
       <c r="I26" s="5"/>
     </row>
     <row r="27" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A27" s="15" t="s">
-        <v>200</v>
+        <v>194</v>
       </c>
       <c r="B27" s="25" t="s">
-        <v>194</v>
+        <v>188</v>
       </c>
       <c r="C27" s="9" t="s">
-        <v>201</v>
+        <v>195</v>
       </c>
       <c r="D27" s="24" t="s">
-        <v>42</v>
+        <v>36</v>
       </c>
       <c r="E27" s="10">
         <v>2</v>
@@ -4703,23 +4745,23 @@
         <v>0.5</v>
       </c>
       <c r="G27" s="10" t="s">
-        <v>77</v>
+        <v>71</v>
       </c>
       <c r="H27" s="9"/>
       <c r="I27" s="9"/>
     </row>
     <row r="28" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A28" s="22" t="s">
-        <v>202</v>
+        <v>196</v>
       </c>
       <c r="B28" s="23" t="s">
-        <v>203</v>
+        <v>197</v>
       </c>
       <c r="C28" s="5" t="s">
-        <v>204</v>
+        <v>198</v>
       </c>
       <c r="D28" s="24" t="s">
-        <v>42</v>
+        <v>36</v>
       </c>
       <c r="E28" s="6">
         <v>2</v>
@@ -4728,23 +4770,23 @@
         <v>0.5</v>
       </c>
       <c r="G28" s="6" t="s">
-        <v>77</v>
+        <v>71</v>
       </c>
       <c r="H28" s="5"/>
       <c r="I28" s="5"/>
     </row>
     <row r="29" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A29" s="15" t="s">
-        <v>205</v>
+        <v>199</v>
       </c>
       <c r="B29" s="25" t="s">
-        <v>203</v>
+        <v>197</v>
       </c>
       <c r="C29" s="9" t="s">
-        <v>206</v>
+        <v>200</v>
       </c>
       <c r="D29" s="24" t="s">
-        <v>42</v>
+        <v>36</v>
       </c>
       <c r="E29" s="10">
         <v>2</v>
@@ -4753,23 +4795,23 @@
         <v>1</v>
       </c>
       <c r="G29" s="10" t="s">
-        <v>77</v>
+        <v>71</v>
       </c>
       <c r="H29" s="9"/>
       <c r="I29" s="9"/>
     </row>
     <row r="30" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A30" s="22" t="s">
-        <v>207</v>
+        <v>201</v>
       </c>
       <c r="B30" s="23" t="s">
-        <v>203</v>
+        <v>197</v>
       </c>
       <c r="C30" s="5" t="s">
-        <v>208</v>
+        <v>202</v>
       </c>
       <c r="D30" s="24" t="s">
-        <v>42</v>
+        <v>36</v>
       </c>
       <c r="E30" s="6">
         <v>2</v>
@@ -4778,23 +4820,23 @@
         <v>0.5</v>
       </c>
       <c r="G30" s="6" t="s">
-        <v>77</v>
+        <v>71</v>
       </c>
       <c r="H30" s="5"/>
       <c r="I30" s="5"/>
     </row>
     <row r="31" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A31" s="15" t="s">
-        <v>209</v>
+        <v>203</v>
       </c>
       <c r="B31" s="25" t="s">
-        <v>210</v>
+        <v>204</v>
       </c>
       <c r="C31" s="9" t="s">
-        <v>211</v>
+        <v>205</v>
       </c>
       <c r="D31" s="26" t="s">
-        <v>118</v>
+        <v>112</v>
       </c>
       <c r="E31" s="10">
         <v>3</v>
@@ -4803,23 +4845,23 @@
         <v>0.5</v>
       </c>
       <c r="G31" s="10" t="s">
-        <v>77</v>
+        <v>71</v>
       </c>
       <c r="H31" s="9"/>
       <c r="I31" s="9"/>
     </row>
     <row r="32" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A32" s="22" t="s">
-        <v>212</v>
+        <v>206</v>
       </c>
       <c r="B32" s="23" t="s">
-        <v>210</v>
+        <v>204</v>
       </c>
       <c r="C32" s="5" t="s">
-        <v>213</v>
+        <v>207</v>
       </c>
       <c r="D32" s="26" t="s">
-        <v>118</v>
+        <v>112</v>
       </c>
       <c r="E32" s="6">
         <v>3</v>
@@ -4828,23 +4870,23 @@
         <v>1</v>
       </c>
       <c r="G32" s="6" t="s">
-        <v>77</v>
+        <v>71</v>
       </c>
       <c r="H32" s="5"/>
       <c r="I32" s="5"/>
     </row>
     <row r="33" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A33" s="15" t="s">
-        <v>214</v>
+        <v>208</v>
       </c>
       <c r="B33" s="25" t="s">
-        <v>210</v>
+        <v>204</v>
       </c>
       <c r="C33" s="9" t="s">
-        <v>215</v>
+        <v>209</v>
       </c>
       <c r="D33" s="26" t="s">
-        <v>118</v>
+        <v>112</v>
       </c>
       <c r="E33" s="10">
         <v>3</v>
@@ -4853,23 +4895,23 @@
         <v>1</v>
       </c>
       <c r="G33" s="10" t="s">
-        <v>77</v>
+        <v>71</v>
       </c>
       <c r="H33" s="9"/>
       <c r="I33" s="9"/>
     </row>
     <row r="34" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A34" s="22" t="s">
-        <v>216</v>
+        <v>210</v>
       </c>
       <c r="B34" s="23" t="s">
-        <v>210</v>
+        <v>204</v>
       </c>
       <c r="C34" s="5" t="s">
-        <v>217</v>
+        <v>211</v>
       </c>
       <c r="D34" s="26" t="s">
-        <v>118</v>
+        <v>112</v>
       </c>
       <c r="E34" s="6">
         <v>3</v>
@@ -4878,23 +4920,23 @@
         <v>0.5</v>
       </c>
       <c r="G34" s="6" t="s">
-        <v>77</v>
+        <v>71</v>
       </c>
       <c r="H34" s="5"/>
       <c r="I34" s="5"/>
     </row>
     <row r="35" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A35" s="15" t="s">
-        <v>218</v>
+        <v>212</v>
       </c>
       <c r="B35" s="25" t="s">
-        <v>219</v>
+        <v>213</v>
       </c>
       <c r="C35" s="9" t="s">
-        <v>220</v>
+        <v>214</v>
       </c>
       <c r="D35" s="26" t="s">
-        <v>118</v>
+        <v>112</v>
       </c>
       <c r="E35" s="10">
         <v>3</v>
@@ -4903,23 +4945,23 @@
         <v>1</v>
       </c>
       <c r="G35" s="10" t="s">
-        <v>77</v>
+        <v>71</v>
       </c>
       <c r="H35" s="9"/>
       <c r="I35" s="9"/>
     </row>
     <row r="36" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A36" s="22" t="s">
-        <v>221</v>
+        <v>215</v>
       </c>
       <c r="B36" s="23" t="s">
-        <v>219</v>
+        <v>213</v>
       </c>
       <c r="C36" s="5" t="s">
-        <v>222</v>
+        <v>216</v>
       </c>
       <c r="D36" s="26" t="s">
-        <v>118</v>
+        <v>112</v>
       </c>
       <c r="E36" s="6">
         <v>3</v>
@@ -4928,23 +4970,23 @@
         <v>1</v>
       </c>
       <c r="G36" s="6" t="s">
-        <v>77</v>
+        <v>71</v>
       </c>
       <c r="H36" s="5"/>
       <c r="I36" s="5"/>
     </row>
     <row r="37" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A37" s="15" t="s">
-        <v>223</v>
+        <v>217</v>
       </c>
       <c r="B37" s="25" t="s">
-        <v>219</v>
+        <v>213</v>
       </c>
       <c r="C37" s="9" t="s">
-        <v>224</v>
+        <v>218</v>
       </c>
       <c r="D37" s="26" t="s">
-        <v>118</v>
+        <v>112</v>
       </c>
       <c r="E37" s="10">
         <v>3</v>
@@ -4953,23 +4995,23 @@
         <v>0.5</v>
       </c>
       <c r="G37" s="10" t="s">
-        <v>77</v>
+        <v>71</v>
       </c>
       <c r="H37" s="9"/>
       <c r="I37" s="9"/>
     </row>
     <row r="38" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A38" s="22" t="s">
-        <v>225</v>
+        <v>219</v>
       </c>
       <c r="B38" s="23" t="s">
-        <v>136</v>
+        <v>130</v>
       </c>
       <c r="C38" s="5" t="s">
-        <v>137</v>
+        <v>131</v>
       </c>
       <c r="D38" s="24" t="s">
-        <v>42</v>
+        <v>36</v>
       </c>
       <c r="E38" s="6">
         <v>3</v>
@@ -4978,23 +5020,23 @@
         <v>1</v>
       </c>
       <c r="G38" s="6" t="s">
-        <v>77</v>
+        <v>71</v>
       </c>
       <c r="H38" s="5"/>
       <c r="I38" s="5"/>
     </row>
     <row r="39" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A39" s="15" t="s">
-        <v>226</v>
+        <v>220</v>
       </c>
       <c r="B39" s="25" t="s">
-        <v>136</v>
+        <v>130</v>
       </c>
       <c r="C39" s="9" t="s">
-        <v>139</v>
+        <v>133</v>
       </c>
       <c r="D39" s="24" t="s">
-        <v>42</v>
+        <v>36</v>
       </c>
       <c r="E39" s="10">
         <v>3</v>
@@ -5003,23 +5045,23 @@
         <v>2</v>
       </c>
       <c r="G39" s="10" t="s">
-        <v>77</v>
+        <v>71</v>
       </c>
       <c r="H39" s="9"/>
       <c r="I39" s="9"/>
     </row>
     <row r="40" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A40" s="22" t="s">
-        <v>227</v>
+        <v>221</v>
       </c>
       <c r="B40" s="23" t="s">
-        <v>136</v>
+        <v>130</v>
       </c>
       <c r="C40" s="5" t="s">
-        <v>228</v>
+        <v>222</v>
       </c>
       <c r="D40" s="24" t="s">
-        <v>42</v>
+        <v>36</v>
       </c>
       <c r="E40" s="6">
         <v>3</v>
@@ -5028,14 +5070,14 @@
         <v>1.5</v>
       </c>
       <c r="G40" s="6" t="s">
-        <v>77</v>
+        <v>71</v>
       </c>
       <c r="H40" s="5"/>
       <c r="I40" s="5"/>
     </row>
     <row r="42" spans="1:9" x14ac:dyDescent="0.3">
       <c r="C42" s="27" t="s">
-        <v>142</v>
+        <v>136</v>
       </c>
       <c r="F42" s="28">
         <f>SUM(F2:F40)</f>
@@ -5044,7 +5086,7 @@
     </row>
     <row r="43" spans="1:9" x14ac:dyDescent="0.3">
       <c r="C43" s="27" t="s">
-        <v>143</v>
+        <v>137</v>
       </c>
       <c r="F43" s="28">
         <f>SUMIF(G2:G40,"Feito",F2:F40)</f>
@@ -5061,6 +5103,18 @@
   </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{CCE6A557-97BC-4b89-ADB6-D9C93CAAB3DF}">
+      <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" count="1">
+        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{1077F13B-C9E0-4585-84FF-BA8836EAFAC9}">
+          <x14:formula1>
+            <xm:f>Equipes!$B$3:$G$3</xm:f>
+          </x14:formula1>
+          <xm:sqref>H2:H40</xm:sqref>
+        </x14:dataValidation>
+      </x14:dataValidations>
+    </ext>
+  </extLst>
 </worksheet>
 </file>
 
@@ -5082,45 +5136,45 @@
   <sheetData>
     <row r="1" spans="1:9" ht="26.4" x14ac:dyDescent="0.3">
       <c r="A1" s="30" t="s">
+        <v>24</v>
+      </c>
+      <c r="B1" s="30" t="s">
+        <v>25</v>
+      </c>
+      <c r="C1" s="30" t="s">
+        <v>26</v>
+      </c>
+      <c r="D1" s="30" t="s">
+        <v>27</v>
+      </c>
+      <c r="E1" s="30" t="s">
+        <v>28</v>
+      </c>
+      <c r="F1" s="30" t="s">
+        <v>29</v>
+      </c>
+      <c r="G1" s="30" t="s">
         <v>30</v>
       </c>
-      <c r="B1" s="30" t="s">
+      <c r="H1" s="30" t="s">
         <v>31</v>
       </c>
-      <c r="C1" s="30" t="s">
+      <c r="I1" s="30" t="s">
         <v>32</v>
-      </c>
-      <c r="D1" s="30" t="s">
-        <v>33</v>
-      </c>
-      <c r="E1" s="30" t="s">
-        <v>34</v>
-      </c>
-      <c r="F1" s="30" t="s">
-        <v>35</v>
-      </c>
-      <c r="G1" s="30" t="s">
-        <v>36</v>
-      </c>
-      <c r="H1" s="30" t="s">
-        <v>37</v>
-      </c>
-      <c r="I1" s="30" t="s">
-        <v>38</v>
       </c>
     </row>
     <row r="2" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A2" s="22" t="s">
-        <v>229</v>
+        <v>223</v>
       </c>
       <c r="B2" s="23" t="s">
-        <v>230</v>
+        <v>224</v>
       </c>
       <c r="C2" s="5" t="s">
-        <v>146</v>
+        <v>140</v>
       </c>
       <c r="D2" s="24" t="s">
-        <v>42</v>
+        <v>36</v>
       </c>
       <c r="E2" s="6">
         <v>1</v>
@@ -5129,23 +5183,23 @@
         <v>0.5</v>
       </c>
       <c r="G2" s="6" t="s">
-        <v>43</v>
+        <v>37</v>
       </c>
       <c r="H2" s="5"/>
       <c r="I2" s="5"/>
     </row>
     <row r="3" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A3" s="15" t="s">
-        <v>231</v>
+        <v>225</v>
       </c>
       <c r="B3" s="25" t="s">
-        <v>230</v>
+        <v>224</v>
       </c>
       <c r="C3" s="9" t="s">
-        <v>148</v>
+        <v>142</v>
       </c>
       <c r="D3" s="24" t="s">
-        <v>42</v>
+        <v>36</v>
       </c>
       <c r="E3" s="10">
         <v>1</v>
@@ -5154,23 +5208,23 @@
         <v>1.5</v>
       </c>
       <c r="G3" s="10" t="s">
-        <v>43</v>
+        <v>37</v>
       </c>
       <c r="H3" s="9"/>
       <c r="I3" s="9"/>
     </row>
     <row r="4" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A4" s="22" t="s">
-        <v>232</v>
+        <v>226</v>
       </c>
       <c r="B4" s="23" t="s">
-        <v>230</v>
+        <v>224</v>
       </c>
       <c r="C4" s="5" t="s">
-        <v>150</v>
+        <v>144</v>
       </c>
       <c r="D4" s="24" t="s">
-        <v>42</v>
+        <v>36</v>
       </c>
       <c r="E4" s="6">
         <v>1</v>
@@ -5179,23 +5233,23 @@
         <v>1</v>
       </c>
       <c r="G4" s="6" t="s">
-        <v>43</v>
+        <v>37</v>
       </c>
       <c r="H4" s="5"/>
       <c r="I4" s="5"/>
     </row>
     <row r="5" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A5" s="15" t="s">
-        <v>233</v>
+        <v>227</v>
       </c>
       <c r="B5" s="25" t="s">
-        <v>230</v>
+        <v>224</v>
       </c>
       <c r="C5" s="9" t="s">
-        <v>234</v>
+        <v>228</v>
       </c>
       <c r="D5" s="24" t="s">
-        <v>42</v>
+        <v>36</v>
       </c>
       <c r="E5" s="10">
         <v>1</v>
@@ -5204,23 +5258,23 @@
         <v>1</v>
       </c>
       <c r="G5" s="10" t="s">
-        <v>43</v>
+        <v>37</v>
       </c>
       <c r="H5" s="9"/>
       <c r="I5" s="9"/>
     </row>
     <row r="6" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A6" s="22" t="s">
-        <v>235</v>
+        <v>229</v>
       </c>
       <c r="B6" s="23" t="s">
+        <v>224</v>
+      </c>
+      <c r="C6" s="5" t="s">
         <v>230</v>
       </c>
-      <c r="C6" s="5" t="s">
-        <v>236</v>
-      </c>
       <c r="D6" s="24" t="s">
-        <v>42</v>
+        <v>36</v>
       </c>
       <c r="E6" s="6">
         <v>1</v>
@@ -5229,23 +5283,23 @@
         <v>1.5</v>
       </c>
       <c r="G6" s="6" t="s">
-        <v>43</v>
+        <v>37</v>
       </c>
       <c r="H6" s="5"/>
       <c r="I6" s="5"/>
     </row>
     <row r="7" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A7" s="15" t="s">
-        <v>237</v>
+        <v>231</v>
       </c>
       <c r="B7" s="25" t="s">
-        <v>230</v>
+        <v>224</v>
       </c>
       <c r="C7" s="9" t="s">
-        <v>238</v>
+        <v>232</v>
       </c>
       <c r="D7" s="24" t="s">
-        <v>42</v>
+        <v>36</v>
       </c>
       <c r="E7" s="10">
         <v>1</v>
@@ -5254,23 +5308,23 @@
         <v>0.5</v>
       </c>
       <c r="G7" s="10" t="s">
-        <v>43</v>
+        <v>37</v>
       </c>
       <c r="H7" s="9"/>
       <c r="I7" s="9"/>
     </row>
     <row r="8" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A8" s="22" t="s">
-        <v>239</v>
+        <v>233</v>
       </c>
       <c r="B8" s="23" t="s">
-        <v>240</v>
+        <v>234</v>
       </c>
       <c r="C8" s="5" t="s">
-        <v>241</v>
+        <v>235</v>
       </c>
       <c r="D8" s="24" t="s">
-        <v>42</v>
+        <v>36</v>
       </c>
       <c r="E8" s="6">
         <v>2</v>
@@ -5279,23 +5333,23 @@
         <v>0.5</v>
       </c>
       <c r="G8" s="6" t="s">
-        <v>77</v>
+        <v>71</v>
       </c>
       <c r="H8" s="5"/>
       <c r="I8" s="5"/>
     </row>
     <row r="9" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A9" s="15" t="s">
-        <v>242</v>
+        <v>236</v>
       </c>
       <c r="B9" s="25" t="s">
-        <v>240</v>
+        <v>234</v>
       </c>
       <c r="C9" s="9" t="s">
-        <v>243</v>
+        <v>237</v>
       </c>
       <c r="D9" s="24" t="s">
-        <v>42</v>
+        <v>36</v>
       </c>
       <c r="E9" s="10">
         <v>2</v>
@@ -5304,23 +5358,23 @@
         <v>0.5</v>
       </c>
       <c r="G9" s="10" t="s">
-        <v>77</v>
+        <v>71</v>
       </c>
       <c r="H9" s="9"/>
       <c r="I9" s="9"/>
     </row>
     <row r="10" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A10" s="22" t="s">
-        <v>244</v>
+        <v>238</v>
       </c>
       <c r="B10" s="23" t="s">
-        <v>240</v>
+        <v>234</v>
       </c>
       <c r="C10" s="5" t="s">
-        <v>245</v>
+        <v>239</v>
       </c>
       <c r="D10" s="24" t="s">
-        <v>42</v>
+        <v>36</v>
       </c>
       <c r="E10" s="6">
         <v>2</v>
@@ -5329,23 +5383,23 @@
         <v>1</v>
       </c>
       <c r="G10" s="6" t="s">
-        <v>77</v>
+        <v>71</v>
       </c>
       <c r="H10" s="5"/>
       <c r="I10" s="5"/>
     </row>
     <row r="11" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A11" s="15" t="s">
-        <v>246</v>
+        <v>240</v>
       </c>
       <c r="B11" s="25" t="s">
-        <v>240</v>
+        <v>234</v>
       </c>
       <c r="C11" s="9" t="s">
-        <v>247</v>
+        <v>241</v>
       </c>
       <c r="D11" s="24" t="s">
-        <v>42</v>
+        <v>36</v>
       </c>
       <c r="E11" s="10">
         <v>2</v>
@@ -5354,23 +5408,23 @@
         <v>1</v>
       </c>
       <c r="G11" s="10" t="s">
-        <v>77</v>
+        <v>71</v>
       </c>
       <c r="H11" s="9"/>
       <c r="I11" s="9"/>
     </row>
     <row r="12" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A12" s="22" t="s">
-        <v>248</v>
+        <v>242</v>
       </c>
       <c r="B12" s="23" t="s">
-        <v>240</v>
+        <v>234</v>
       </c>
       <c r="C12" s="5" t="s">
-        <v>249</v>
+        <v>243</v>
       </c>
       <c r="D12" s="24" t="s">
-        <v>42</v>
+        <v>36</v>
       </c>
       <c r="E12" s="6">
         <v>2</v>
@@ -5379,23 +5433,23 @@
         <v>0.5</v>
       </c>
       <c r="G12" s="6" t="s">
-        <v>77</v>
+        <v>71</v>
       </c>
       <c r="H12" s="5"/>
       <c r="I12" s="5"/>
     </row>
     <row r="13" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A13" s="15" t="s">
-        <v>250</v>
+        <v>244</v>
       </c>
       <c r="B13" s="25" t="s">
-        <v>251</v>
+        <v>245</v>
       </c>
       <c r="C13" s="9" t="s">
-        <v>252</v>
+        <v>246</v>
       </c>
       <c r="D13" s="24" t="s">
-        <v>42</v>
+        <v>36</v>
       </c>
       <c r="E13" s="10">
         <v>2</v>
@@ -5404,23 +5458,23 @@
         <v>1</v>
       </c>
       <c r="G13" s="10" t="s">
-        <v>77</v>
+        <v>71</v>
       </c>
       <c r="H13" s="9"/>
       <c r="I13" s="9"/>
     </row>
     <row r="14" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A14" s="22" t="s">
-        <v>253</v>
+        <v>247</v>
       </c>
       <c r="B14" s="23" t="s">
-        <v>251</v>
+        <v>245</v>
       </c>
       <c r="C14" s="5" t="s">
-        <v>254</v>
+        <v>248</v>
       </c>
       <c r="D14" s="24" t="s">
-        <v>42</v>
+        <v>36</v>
       </c>
       <c r="E14" s="6">
         <v>2</v>
@@ -5429,23 +5483,23 @@
         <v>1</v>
       </c>
       <c r="G14" s="6" t="s">
-        <v>77</v>
+        <v>71</v>
       </c>
       <c r="H14" s="5"/>
       <c r="I14" s="5"/>
     </row>
     <row r="15" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A15" s="15" t="s">
-        <v>255</v>
+        <v>249</v>
       </c>
       <c r="B15" s="25" t="s">
-        <v>256</v>
+        <v>250</v>
       </c>
       <c r="C15" s="9" t="s">
-        <v>257</v>
+        <v>251</v>
       </c>
       <c r="D15" s="24" t="s">
-        <v>42</v>
+        <v>36</v>
       </c>
       <c r="E15" s="10">
         <v>2</v>
@@ -5454,23 +5508,23 @@
         <v>0.5</v>
       </c>
       <c r="G15" s="10" t="s">
-        <v>77</v>
+        <v>71</v>
       </c>
       <c r="H15" s="9"/>
       <c r="I15" s="9"/>
     </row>
     <row r="16" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A16" s="22" t="s">
-        <v>258</v>
+        <v>252</v>
       </c>
       <c r="B16" s="23" t="s">
-        <v>256</v>
+        <v>250</v>
       </c>
       <c r="C16" s="5" t="s">
-        <v>259</v>
+        <v>253</v>
       </c>
       <c r="D16" s="24" t="s">
-        <v>42</v>
+        <v>36</v>
       </c>
       <c r="E16" s="6">
         <v>2</v>
@@ -5479,23 +5533,23 @@
         <v>1</v>
       </c>
       <c r="G16" s="6" t="s">
-        <v>77</v>
+        <v>71</v>
       </c>
       <c r="H16" s="5"/>
       <c r="I16" s="5"/>
     </row>
     <row r="17" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A17" s="15" t="s">
-        <v>260</v>
+        <v>254</v>
       </c>
       <c r="B17" s="25" t="s">
-        <v>256</v>
+        <v>250</v>
       </c>
       <c r="C17" s="9" t="s">
-        <v>261</v>
+        <v>255</v>
       </c>
       <c r="D17" s="24" t="s">
-        <v>42</v>
+        <v>36</v>
       </c>
       <c r="E17" s="10">
         <v>2</v>
@@ -5504,23 +5558,23 @@
         <v>1</v>
       </c>
       <c r="G17" s="10" t="s">
-        <v>77</v>
+        <v>71</v>
       </c>
       <c r="H17" s="9"/>
       <c r="I17" s="9"/>
     </row>
     <row r="18" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A18" s="22" t="s">
-        <v>262</v>
+        <v>256</v>
       </c>
       <c r="B18" s="23" t="s">
-        <v>263</v>
+        <v>257</v>
       </c>
       <c r="C18" s="5" t="s">
-        <v>264</v>
+        <v>258</v>
       </c>
       <c r="D18" s="24" t="s">
-        <v>42</v>
+        <v>36</v>
       </c>
       <c r="E18" s="6">
         <v>2</v>
@@ -5529,23 +5583,23 @@
         <v>1</v>
       </c>
       <c r="G18" s="6" t="s">
-        <v>77</v>
+        <v>71</v>
       </c>
       <c r="H18" s="5"/>
       <c r="I18" s="5"/>
     </row>
     <row r="19" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A19" s="15" t="s">
-        <v>265</v>
+        <v>259</v>
       </c>
       <c r="B19" s="25" t="s">
-        <v>263</v>
+        <v>257</v>
       </c>
       <c r="C19" s="9" t="s">
-        <v>266</v>
+        <v>260</v>
       </c>
       <c r="D19" s="24" t="s">
-        <v>42</v>
+        <v>36</v>
       </c>
       <c r="E19" s="10">
         <v>2</v>
@@ -5554,23 +5608,23 @@
         <v>1</v>
       </c>
       <c r="G19" s="10" t="s">
-        <v>77</v>
+        <v>71</v>
       </c>
       <c r="H19" s="9"/>
       <c r="I19" s="9"/>
     </row>
     <row r="20" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A20" s="22" t="s">
-        <v>267</v>
+        <v>261</v>
       </c>
       <c r="B20" s="23" t="s">
-        <v>268</v>
+        <v>262</v>
       </c>
       <c r="C20" s="5" t="s">
-        <v>269</v>
+        <v>263</v>
       </c>
       <c r="D20" s="24" t="s">
-        <v>42</v>
+        <v>36</v>
       </c>
       <c r="E20" s="6">
         <v>2</v>
@@ -5579,23 +5633,23 @@
         <v>1</v>
       </c>
       <c r="G20" s="6" t="s">
-        <v>77</v>
+        <v>71</v>
       </c>
       <c r="H20" s="5"/>
       <c r="I20" s="5"/>
     </row>
     <row r="21" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A21" s="15" t="s">
-        <v>270</v>
+        <v>264</v>
       </c>
       <c r="B21" s="25" t="s">
-        <v>268</v>
+        <v>262</v>
       </c>
       <c r="C21" s="9" t="s">
-        <v>271</v>
+        <v>265</v>
       </c>
       <c r="D21" s="24" t="s">
-        <v>42</v>
+        <v>36</v>
       </c>
       <c r="E21" s="10">
         <v>2</v>
@@ -5604,23 +5658,23 @@
         <v>1</v>
       </c>
       <c r="G21" s="10" t="s">
-        <v>77</v>
+        <v>71</v>
       </c>
       <c r="H21" s="9"/>
       <c r="I21" s="9"/>
     </row>
     <row r="22" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A22" s="22" t="s">
-        <v>272</v>
+        <v>266</v>
       </c>
       <c r="B22" s="23" t="s">
-        <v>268</v>
+        <v>262</v>
       </c>
       <c r="C22" s="5" t="s">
-        <v>273</v>
+        <v>267</v>
       </c>
       <c r="D22" s="24" t="s">
-        <v>42</v>
+        <v>36</v>
       </c>
       <c r="E22" s="6">
         <v>2</v>
@@ -5629,23 +5683,23 @@
         <v>1</v>
       </c>
       <c r="G22" s="6" t="s">
-        <v>77</v>
+        <v>71</v>
       </c>
       <c r="H22" s="5"/>
       <c r="I22" s="5"/>
     </row>
     <row r="23" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A23" s="15" t="s">
-        <v>274</v>
+        <v>268</v>
       </c>
       <c r="B23" s="25" t="s">
-        <v>268</v>
+        <v>262</v>
       </c>
       <c r="C23" s="9" t="s">
-        <v>275</v>
+        <v>269</v>
       </c>
       <c r="D23" s="24" t="s">
-        <v>42</v>
+        <v>36</v>
       </c>
       <c r="E23" s="10">
         <v>2</v>
@@ -5654,23 +5708,23 @@
         <v>1</v>
       </c>
       <c r="G23" s="10" t="s">
-        <v>77</v>
+        <v>71</v>
       </c>
       <c r="H23" s="9"/>
       <c r="I23" s="9"/>
     </row>
     <row r="24" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A24" s="22" t="s">
-        <v>276</v>
+        <v>270</v>
       </c>
       <c r="B24" s="23" t="s">
-        <v>277</v>
+        <v>271</v>
       </c>
       <c r="C24" s="5" t="s">
-        <v>278</v>
+        <v>272</v>
       </c>
       <c r="D24" s="24" t="s">
-        <v>42</v>
+        <v>36</v>
       </c>
       <c r="E24" s="6">
         <v>2</v>
@@ -5679,23 +5733,23 @@
         <v>1</v>
       </c>
       <c r="G24" s="6" t="s">
-        <v>77</v>
+        <v>71</v>
       </c>
       <c r="H24" s="5"/>
       <c r="I24" s="5"/>
     </row>
     <row r="25" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A25" s="15" t="s">
-        <v>279</v>
+        <v>273</v>
       </c>
       <c r="B25" s="25" t="s">
-        <v>277</v>
+        <v>271</v>
       </c>
       <c r="C25" s="9" t="s">
-        <v>280</v>
+        <v>274</v>
       </c>
       <c r="D25" s="24" t="s">
-        <v>42</v>
+        <v>36</v>
       </c>
       <c r="E25" s="10">
         <v>2</v>
@@ -5704,23 +5758,23 @@
         <v>1</v>
       </c>
       <c r="G25" s="10" t="s">
-        <v>77</v>
+        <v>71</v>
       </c>
       <c r="H25" s="9"/>
       <c r="I25" s="9"/>
     </row>
     <row r="26" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A26" s="22" t="s">
-        <v>281</v>
+        <v>275</v>
       </c>
       <c r="B26" s="23" t="s">
-        <v>277</v>
+        <v>271</v>
       </c>
       <c r="C26" s="5" t="s">
-        <v>282</v>
+        <v>276</v>
       </c>
       <c r="D26" s="24" t="s">
-        <v>42</v>
+        <v>36</v>
       </c>
       <c r="E26" s="6">
         <v>2</v>
@@ -5729,23 +5783,23 @@
         <v>1</v>
       </c>
       <c r="G26" s="6" t="s">
-        <v>77</v>
+        <v>71</v>
       </c>
       <c r="H26" s="5"/>
       <c r="I26" s="5"/>
     </row>
     <row r="27" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A27" s="15" t="s">
-        <v>283</v>
+        <v>277</v>
       </c>
       <c r="B27" s="25" t="s">
-        <v>277</v>
+        <v>271</v>
       </c>
       <c r="C27" s="9" t="s">
-        <v>284</v>
+        <v>278</v>
       </c>
       <c r="D27" s="24" t="s">
-        <v>42</v>
+        <v>36</v>
       </c>
       <c r="E27" s="10">
         <v>2</v>
@@ -5754,23 +5808,23 @@
         <v>0.5</v>
       </c>
       <c r="G27" s="10" t="s">
-        <v>77</v>
+        <v>71</v>
       </c>
       <c r="H27" s="9"/>
       <c r="I27" s="9"/>
     </row>
     <row r="28" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A28" s="22" t="s">
-        <v>285</v>
+        <v>279</v>
       </c>
       <c r="B28" s="23" t="s">
-        <v>277</v>
+        <v>271</v>
       </c>
       <c r="C28" s="5" t="s">
-        <v>286</v>
+        <v>280</v>
       </c>
       <c r="D28" s="24" t="s">
-        <v>42</v>
+        <v>36</v>
       </c>
       <c r="E28" s="6">
         <v>2</v>
@@ -5779,23 +5833,23 @@
         <v>0.5</v>
       </c>
       <c r="G28" s="6" t="s">
-        <v>77</v>
+        <v>71</v>
       </c>
       <c r="H28" s="5"/>
       <c r="I28" s="5"/>
     </row>
     <row r="29" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A29" s="15" t="s">
-        <v>287</v>
+        <v>281</v>
       </c>
       <c r="B29" s="25" t="s">
-        <v>288</v>
+        <v>282</v>
       </c>
       <c r="C29" s="9" t="s">
-        <v>289</v>
+        <v>283</v>
       </c>
       <c r="D29" s="26" t="s">
-        <v>118</v>
+        <v>112</v>
       </c>
       <c r="E29" s="10">
         <v>3</v>
@@ -5804,23 +5858,23 @@
         <v>1</v>
       </c>
       <c r="G29" s="10" t="s">
-        <v>77</v>
+        <v>71</v>
       </c>
       <c r="H29" s="9"/>
       <c r="I29" s="9"/>
     </row>
     <row r="30" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A30" s="22" t="s">
-        <v>290</v>
+        <v>284</v>
       </c>
       <c r="B30" s="23" t="s">
-        <v>288</v>
+        <v>282</v>
       </c>
       <c r="C30" s="5" t="s">
-        <v>291</v>
+        <v>285</v>
       </c>
       <c r="D30" s="26" t="s">
-        <v>118</v>
+        <v>112</v>
       </c>
       <c r="E30" s="6">
         <v>3</v>
@@ -5829,23 +5883,23 @@
         <v>0.5</v>
       </c>
       <c r="G30" s="6" t="s">
-        <v>77</v>
+        <v>71</v>
       </c>
       <c r="H30" s="5"/>
       <c r="I30" s="5"/>
     </row>
     <row r="31" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A31" s="15" t="s">
-        <v>292</v>
+        <v>286</v>
       </c>
       <c r="B31" s="25" t="s">
-        <v>293</v>
+        <v>287</v>
       </c>
       <c r="C31" s="9" t="s">
-        <v>294</v>
+        <v>288</v>
       </c>
       <c r="D31" s="26" t="s">
-        <v>118</v>
+        <v>112</v>
       </c>
       <c r="E31" s="10">
         <v>3</v>
@@ -5854,23 +5908,23 @@
         <v>1</v>
       </c>
       <c r="G31" s="10" t="s">
-        <v>77</v>
+        <v>71</v>
       </c>
       <c r="H31" s="9"/>
       <c r="I31" s="9"/>
     </row>
     <row r="32" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A32" s="22" t="s">
-        <v>295</v>
+        <v>289</v>
       </c>
       <c r="B32" s="23" t="s">
-        <v>293</v>
+        <v>287</v>
       </c>
       <c r="C32" s="5" t="s">
-        <v>296</v>
+        <v>290</v>
       </c>
       <c r="D32" s="26" t="s">
-        <v>118</v>
+        <v>112</v>
       </c>
       <c r="E32" s="6">
         <v>3</v>
@@ -5879,23 +5933,23 @@
         <v>1</v>
       </c>
       <c r="G32" s="6" t="s">
-        <v>77</v>
+        <v>71</v>
       </c>
       <c r="H32" s="5"/>
       <c r="I32" s="5"/>
     </row>
     <row r="33" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A33" s="15" t="s">
-        <v>297</v>
+        <v>291</v>
       </c>
       <c r="B33" s="25" t="s">
-        <v>293</v>
+        <v>287</v>
       </c>
       <c r="C33" s="9" t="s">
-        <v>298</v>
+        <v>292</v>
       </c>
       <c r="D33" s="26" t="s">
-        <v>118</v>
+        <v>112</v>
       </c>
       <c r="E33" s="10">
         <v>3</v>
@@ -5904,23 +5958,23 @@
         <v>0.5</v>
       </c>
       <c r="G33" s="10" t="s">
-        <v>77</v>
+        <v>71</v>
       </c>
       <c r="H33" s="9"/>
       <c r="I33" s="9"/>
     </row>
     <row r="34" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A34" s="22" t="s">
-        <v>299</v>
+        <v>293</v>
       </c>
       <c r="B34" s="23" t="s">
-        <v>300</v>
+        <v>294</v>
       </c>
       <c r="C34" s="5" t="s">
-        <v>301</v>
+        <v>295</v>
       </c>
       <c r="D34" s="26" t="s">
-        <v>118</v>
+        <v>112</v>
       </c>
       <c r="E34" s="6">
         <v>3</v>
@@ -5929,23 +5983,23 @@
         <v>1</v>
       </c>
       <c r="G34" s="6" t="s">
-        <v>77</v>
+        <v>71</v>
       </c>
       <c r="H34" s="5"/>
       <c r="I34" s="5"/>
     </row>
     <row r="35" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A35" s="15" t="s">
-        <v>302</v>
+        <v>296</v>
       </c>
       <c r="B35" s="25" t="s">
-        <v>300</v>
+        <v>294</v>
       </c>
       <c r="C35" s="9" t="s">
-        <v>303</v>
+        <v>297</v>
       </c>
       <c r="D35" s="26" t="s">
-        <v>118</v>
+        <v>112</v>
       </c>
       <c r="E35" s="10">
         <v>3</v>
@@ -5954,23 +6008,23 @@
         <v>0.5</v>
       </c>
       <c r="G35" s="10" t="s">
-        <v>77</v>
+        <v>71</v>
       </c>
       <c r="H35" s="9"/>
       <c r="I35" s="9"/>
     </row>
     <row r="36" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A36" s="22" t="s">
-        <v>304</v>
+        <v>298</v>
       </c>
       <c r="B36" s="23" t="s">
-        <v>305</v>
+        <v>299</v>
       </c>
       <c r="C36" s="5" t="s">
-        <v>306</v>
+        <v>300</v>
       </c>
       <c r="D36" s="26" t="s">
-        <v>118</v>
+        <v>112</v>
       </c>
       <c r="E36" s="6">
         <v>3</v>
@@ -5979,23 +6033,23 @@
         <v>1</v>
       </c>
       <c r="G36" s="6" t="s">
-        <v>77</v>
+        <v>71</v>
       </c>
       <c r="H36" s="5"/>
       <c r="I36" s="5"/>
     </row>
     <row r="37" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A37" s="15" t="s">
-        <v>307</v>
+        <v>301</v>
       </c>
       <c r="B37" s="25" t="s">
-        <v>305</v>
+        <v>299</v>
       </c>
       <c r="C37" s="9" t="s">
-        <v>308</v>
+        <v>302</v>
       </c>
       <c r="D37" s="26" t="s">
-        <v>118</v>
+        <v>112</v>
       </c>
       <c r="E37" s="10">
         <v>3</v>
@@ -6004,23 +6058,23 @@
         <v>1</v>
       </c>
       <c r="G37" s="10" t="s">
-        <v>77</v>
+        <v>71</v>
       </c>
       <c r="H37" s="9"/>
       <c r="I37" s="9"/>
     </row>
     <row r="38" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A38" s="22" t="s">
-        <v>309</v>
+        <v>303</v>
       </c>
       <c r="B38" s="23" t="s">
-        <v>136</v>
+        <v>130</v>
       </c>
       <c r="C38" s="5" t="s">
-        <v>137</v>
+        <v>131</v>
       </c>
       <c r="D38" s="24" t="s">
-        <v>42</v>
+        <v>36</v>
       </c>
       <c r="E38" s="6">
         <v>3</v>
@@ -6029,23 +6083,23 @@
         <v>1</v>
       </c>
       <c r="G38" s="6" t="s">
-        <v>77</v>
+        <v>71</v>
       </c>
       <c r="H38" s="5"/>
       <c r="I38" s="5"/>
     </row>
     <row r="39" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A39" s="15" t="s">
-        <v>310</v>
+        <v>304</v>
       </c>
       <c r="B39" s="25" t="s">
-        <v>136</v>
+        <v>130</v>
       </c>
       <c r="C39" s="9" t="s">
-        <v>139</v>
+        <v>133</v>
       </c>
       <c r="D39" s="24" t="s">
-        <v>42</v>
+        <v>36</v>
       </c>
       <c r="E39" s="10">
         <v>3</v>
@@ -6054,14 +6108,14 @@
         <v>2</v>
       </c>
       <c r="G39" s="10" t="s">
-        <v>77</v>
+        <v>71</v>
       </c>
       <c r="H39" s="9"/>
       <c r="I39" s="9"/>
     </row>
     <row r="41" spans="1:9" x14ac:dyDescent="0.3">
       <c r="C41" s="27" t="s">
-        <v>142</v>
+        <v>136</v>
       </c>
       <c r="F41" s="28">
         <f>SUM(F2:F39)</f>
@@ -6070,7 +6124,7 @@
     </row>
     <row r="42" spans="1:9" x14ac:dyDescent="0.3">
       <c r="C42" s="27" t="s">
-        <v>143</v>
+        <v>137</v>
       </c>
       <c r="F42" s="28">
         <f>SUMIF(G2:G39,"Feito",F2:F39)</f>
@@ -6087,6 +6141,18 @@
   </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{CCE6A557-97BC-4b89-ADB6-D9C93CAAB3DF}">
+      <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" count="1">
+        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{494125DA-65EE-4932-AE2A-FFB231D06642}">
+          <x14:formula1>
+            <xm:f>Equipes!$B$4:$G$4</xm:f>
+          </x14:formula1>
+          <xm:sqref>H2:H39</xm:sqref>
+        </x14:dataValidation>
+      </x14:dataValidations>
+    </ext>
+  </extLst>
 </worksheet>
 </file>
 
@@ -6108,45 +6174,45 @@
   <sheetData>
     <row r="1" spans="1:9" ht="26.4" x14ac:dyDescent="0.3">
       <c r="A1" s="31" t="s">
+        <v>24</v>
+      </c>
+      <c r="B1" s="31" t="s">
+        <v>25</v>
+      </c>
+      <c r="C1" s="31" t="s">
+        <v>26</v>
+      </c>
+      <c r="D1" s="31" t="s">
+        <v>27</v>
+      </c>
+      <c r="E1" s="31" t="s">
+        <v>28</v>
+      </c>
+      <c r="F1" s="31" t="s">
+        <v>29</v>
+      </c>
+      <c r="G1" s="31" t="s">
         <v>30</v>
       </c>
-      <c r="B1" s="31" t="s">
+      <c r="H1" s="31" t="s">
         <v>31</v>
       </c>
-      <c r="C1" s="31" t="s">
+      <c r="I1" s="31" t="s">
         <v>32</v>
-      </c>
-      <c r="D1" s="31" t="s">
-        <v>33</v>
-      </c>
-      <c r="E1" s="31" t="s">
-        <v>34</v>
-      </c>
-      <c r="F1" s="31" t="s">
-        <v>35</v>
-      </c>
-      <c r="G1" s="31" t="s">
-        <v>36</v>
-      </c>
-      <c r="H1" s="31" t="s">
-        <v>37</v>
-      </c>
-      <c r="I1" s="31" t="s">
-        <v>38</v>
       </c>
     </row>
     <row r="2" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A2" s="22" t="s">
-        <v>311</v>
+        <v>305</v>
       </c>
       <c r="B2" s="23" t="s">
-        <v>312</v>
+        <v>306</v>
       </c>
       <c r="C2" s="5" t="s">
-        <v>313</v>
+        <v>307</v>
       </c>
       <c r="D2" s="24" t="s">
-        <v>42</v>
+        <v>36</v>
       </c>
       <c r="E2" s="6">
         <v>1</v>
@@ -6155,23 +6221,23 @@
         <v>1</v>
       </c>
       <c r="G2" s="6" t="s">
-        <v>43</v>
+        <v>37</v>
       </c>
       <c r="H2" s="5"/>
       <c r="I2" s="5"/>
     </row>
     <row r="3" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A3" s="15" t="s">
-        <v>314</v>
+        <v>308</v>
       </c>
       <c r="B3" s="25" t="s">
-        <v>312</v>
+        <v>306</v>
       </c>
       <c r="C3" s="9" t="s">
-        <v>315</v>
+        <v>309</v>
       </c>
       <c r="D3" s="24" t="s">
-        <v>42</v>
+        <v>36</v>
       </c>
       <c r="E3" s="10">
         <v>1</v>
@@ -6180,23 +6246,23 @@
         <v>1</v>
       </c>
       <c r="G3" s="10" t="s">
-        <v>43</v>
+        <v>37</v>
       </c>
       <c r="H3" s="9"/>
       <c r="I3" s="9"/>
     </row>
     <row r="4" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A4" s="22" t="s">
-        <v>316</v>
+        <v>310</v>
       </c>
       <c r="B4" s="23" t="s">
-        <v>312</v>
+        <v>306</v>
       </c>
       <c r="C4" s="5" t="s">
-        <v>317</v>
+        <v>311</v>
       </c>
       <c r="D4" s="24" t="s">
-        <v>42</v>
+        <v>36</v>
       </c>
       <c r="E4" s="6">
         <v>1</v>
@@ -6205,23 +6271,23 @@
         <v>1.5</v>
       </c>
       <c r="G4" s="6" t="s">
-        <v>43</v>
+        <v>37</v>
       </c>
       <c r="H4" s="5"/>
       <c r="I4" s="5"/>
     </row>
     <row r="5" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A5" s="15" t="s">
-        <v>318</v>
+        <v>312</v>
       </c>
       <c r="B5" s="25" t="s">
-        <v>312</v>
+        <v>306</v>
       </c>
       <c r="C5" s="9" t="s">
-        <v>319</v>
+        <v>313</v>
       </c>
       <c r="D5" s="24" t="s">
-        <v>42</v>
+        <v>36</v>
       </c>
       <c r="E5" s="10">
         <v>1</v>
@@ -6230,23 +6296,23 @@
         <v>1</v>
       </c>
       <c r="G5" s="10" t="s">
-        <v>43</v>
+        <v>37</v>
       </c>
       <c r="H5" s="9"/>
       <c r="I5" s="9"/>
     </row>
     <row r="6" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A6" s="22" t="s">
-        <v>320</v>
+        <v>314</v>
       </c>
       <c r="B6" s="23" t="s">
-        <v>312</v>
+        <v>306</v>
       </c>
       <c r="C6" s="5" t="s">
-        <v>321</v>
+        <v>315</v>
       </c>
       <c r="D6" s="24" t="s">
-        <v>42</v>
+        <v>36</v>
       </c>
       <c r="E6" s="6">
         <v>1</v>
@@ -6255,23 +6321,23 @@
         <v>0.5</v>
       </c>
       <c r="G6" s="6" t="s">
-        <v>43</v>
+        <v>37</v>
       </c>
       <c r="H6" s="5"/>
       <c r="I6" s="5"/>
     </row>
     <row r="7" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A7" s="15" t="s">
-        <v>322</v>
+        <v>316</v>
       </c>
       <c r="B7" s="25" t="s">
-        <v>312</v>
+        <v>306</v>
       </c>
       <c r="C7" s="9" t="s">
-        <v>323</v>
+        <v>317</v>
       </c>
       <c r="D7" s="24" t="s">
-        <v>42</v>
+        <v>36</v>
       </c>
       <c r="E7" s="10">
         <v>1</v>
@@ -6280,23 +6346,23 @@
         <v>1</v>
       </c>
       <c r="G7" s="10" t="s">
-        <v>43</v>
+        <v>37</v>
       </c>
       <c r="H7" s="9"/>
       <c r="I7" s="9"/>
     </row>
     <row r="8" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A8" s="22" t="s">
-        <v>324</v>
+        <v>318</v>
       </c>
       <c r="B8" s="23" t="s">
-        <v>325</v>
+        <v>319</v>
       </c>
       <c r="C8" s="5" t="s">
-        <v>326</v>
+        <v>320</v>
       </c>
       <c r="D8" s="24" t="s">
-        <v>42</v>
+        <v>36</v>
       </c>
       <c r="E8" s="6">
         <v>2</v>
@@ -6305,23 +6371,23 @@
         <v>0.5</v>
       </c>
       <c r="G8" s="6" t="s">
-        <v>77</v>
+        <v>71</v>
       </c>
       <c r="H8" s="5"/>
       <c r="I8" s="5"/>
     </row>
     <row r="9" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A9" s="15" t="s">
-        <v>327</v>
+        <v>321</v>
       </c>
       <c r="B9" s="25" t="s">
-        <v>325</v>
+        <v>319</v>
       </c>
       <c r="C9" s="9" t="s">
-        <v>328</v>
+        <v>322</v>
       </c>
       <c r="D9" s="24" t="s">
-        <v>42</v>
+        <v>36</v>
       </c>
       <c r="E9" s="10">
         <v>2</v>
@@ -6330,23 +6396,23 @@
         <v>0.5</v>
       </c>
       <c r="G9" s="10" t="s">
-        <v>77</v>
+        <v>71</v>
       </c>
       <c r="H9" s="9"/>
       <c r="I9" s="9"/>
     </row>
     <row r="10" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A10" s="22" t="s">
-        <v>329</v>
+        <v>323</v>
       </c>
       <c r="B10" s="23" t="s">
-        <v>325</v>
+        <v>319</v>
       </c>
       <c r="C10" s="5" t="s">
-        <v>330</v>
+        <v>324</v>
       </c>
       <c r="D10" s="24" t="s">
-        <v>42</v>
+        <v>36</v>
       </c>
       <c r="E10" s="6">
         <v>2</v>
@@ -6355,23 +6421,23 @@
         <v>1</v>
       </c>
       <c r="G10" s="6" t="s">
-        <v>77</v>
+        <v>71</v>
       </c>
       <c r="H10" s="5"/>
       <c r="I10" s="5"/>
     </row>
     <row r="11" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A11" s="15" t="s">
-        <v>331</v>
+        <v>325</v>
       </c>
       <c r="B11" s="25" t="s">
-        <v>325</v>
+        <v>319</v>
       </c>
       <c r="C11" s="9" t="s">
-        <v>332</v>
+        <v>326</v>
       </c>
       <c r="D11" s="24" t="s">
-        <v>42</v>
+        <v>36</v>
       </c>
       <c r="E11" s="10">
         <v>2</v>
@@ -6380,23 +6446,23 @@
         <v>1.5</v>
       </c>
       <c r="G11" s="10" t="s">
-        <v>77</v>
+        <v>71</v>
       </c>
       <c r="H11" s="9"/>
       <c r="I11" s="9"/>
     </row>
     <row r="12" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A12" s="22" t="s">
-        <v>333</v>
+        <v>327</v>
       </c>
       <c r="B12" s="23" t="s">
-        <v>325</v>
+        <v>319</v>
       </c>
       <c r="C12" s="5" t="s">
-        <v>334</v>
+        <v>328</v>
       </c>
       <c r="D12" s="24" t="s">
-        <v>42</v>
+        <v>36</v>
       </c>
       <c r="E12" s="6">
         <v>2</v>
@@ -6405,23 +6471,23 @@
         <v>1</v>
       </c>
       <c r="G12" s="6" t="s">
-        <v>77</v>
+        <v>71</v>
       </c>
       <c r="H12" s="5"/>
       <c r="I12" s="5"/>
     </row>
     <row r="13" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A13" s="15" t="s">
-        <v>335</v>
+        <v>329</v>
       </c>
       <c r="B13" s="25" t="s">
-        <v>325</v>
+        <v>319</v>
       </c>
       <c r="C13" s="9" t="s">
-        <v>336</v>
+        <v>330</v>
       </c>
       <c r="D13" s="24" t="s">
-        <v>42</v>
+        <v>36</v>
       </c>
       <c r="E13" s="10">
         <v>2</v>
@@ -6430,23 +6496,23 @@
         <v>1</v>
       </c>
       <c r="G13" s="10" t="s">
-        <v>77</v>
+        <v>71</v>
       </c>
       <c r="H13" s="9"/>
       <c r="I13" s="9"/>
     </row>
     <row r="14" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A14" s="22" t="s">
-        <v>337</v>
+        <v>331</v>
       </c>
       <c r="B14" s="23" t="s">
-        <v>338</v>
+        <v>332</v>
       </c>
       <c r="C14" s="5" t="s">
-        <v>339</v>
+        <v>333</v>
       </c>
       <c r="D14" s="24" t="s">
-        <v>42</v>
+        <v>36</v>
       </c>
       <c r="E14" s="6">
         <v>2</v>
@@ -6455,23 +6521,23 @@
         <v>1</v>
       </c>
       <c r="G14" s="6" t="s">
-        <v>77</v>
+        <v>71</v>
       </c>
       <c r="H14" s="5"/>
       <c r="I14" s="5"/>
     </row>
     <row r="15" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A15" s="15" t="s">
-        <v>340</v>
+        <v>334</v>
       </c>
       <c r="B15" s="25" t="s">
-        <v>338</v>
+        <v>332</v>
       </c>
       <c r="C15" s="9" t="s">
-        <v>341</v>
+        <v>335</v>
       </c>
       <c r="D15" s="24" t="s">
-        <v>42</v>
+        <v>36</v>
       </c>
       <c r="E15" s="10">
         <v>2</v>
@@ -6480,23 +6546,23 @@
         <v>1</v>
       </c>
       <c r="G15" s="10" t="s">
-        <v>77</v>
+        <v>71</v>
       </c>
       <c r="H15" s="9"/>
       <c r="I15" s="9"/>
     </row>
     <row r="16" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A16" s="22" t="s">
-        <v>342</v>
+        <v>336</v>
       </c>
       <c r="B16" s="23" t="s">
-        <v>338</v>
+        <v>332</v>
       </c>
       <c r="C16" s="5" t="s">
-        <v>343</v>
+        <v>337</v>
       </c>
       <c r="D16" s="24" t="s">
-        <v>42</v>
+        <v>36</v>
       </c>
       <c r="E16" s="6">
         <v>2</v>
@@ -6505,23 +6571,23 @@
         <v>1</v>
       </c>
       <c r="G16" s="6" t="s">
-        <v>77</v>
+        <v>71</v>
       </c>
       <c r="H16" s="5"/>
       <c r="I16" s="5"/>
     </row>
     <row r="17" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A17" s="15" t="s">
-        <v>344</v>
+        <v>338</v>
       </c>
       <c r="B17" s="25" t="s">
-        <v>345</v>
+        <v>339</v>
       </c>
       <c r="C17" s="9" t="s">
-        <v>346</v>
+        <v>340</v>
       </c>
       <c r="D17" s="24" t="s">
-        <v>42</v>
+        <v>36</v>
       </c>
       <c r="E17" s="10">
         <v>2</v>
@@ -6530,23 +6596,23 @@
         <v>0.5</v>
       </c>
       <c r="G17" s="10" t="s">
-        <v>77</v>
+        <v>71</v>
       </c>
       <c r="H17" s="9"/>
       <c r="I17" s="9"/>
     </row>
     <row r="18" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A18" s="22" t="s">
-        <v>347</v>
+        <v>341</v>
       </c>
       <c r="B18" s="23" t="s">
-        <v>345</v>
+        <v>339</v>
       </c>
       <c r="C18" s="5" t="s">
-        <v>348</v>
+        <v>342</v>
       </c>
       <c r="D18" s="24" t="s">
-        <v>42</v>
+        <v>36</v>
       </c>
       <c r="E18" s="6">
         <v>2</v>
@@ -6555,23 +6621,23 @@
         <v>1</v>
       </c>
       <c r="G18" s="6" t="s">
-        <v>77</v>
+        <v>71</v>
       </c>
       <c r="H18" s="5"/>
       <c r="I18" s="5"/>
     </row>
     <row r="19" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A19" s="15" t="s">
-        <v>349</v>
+        <v>343</v>
       </c>
       <c r="B19" s="25" t="s">
-        <v>350</v>
+        <v>344</v>
       </c>
       <c r="C19" s="9" t="s">
-        <v>351</v>
+        <v>345</v>
       </c>
       <c r="D19" s="24" t="s">
-        <v>42</v>
+        <v>36</v>
       </c>
       <c r="E19" s="10">
         <v>2</v>
@@ -6580,23 +6646,23 @@
         <v>1</v>
       </c>
       <c r="G19" s="10" t="s">
-        <v>77</v>
+        <v>71</v>
       </c>
       <c r="H19" s="9"/>
       <c r="I19" s="9"/>
     </row>
     <row r="20" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A20" s="22" t="s">
-        <v>352</v>
+        <v>346</v>
       </c>
       <c r="B20" s="23" t="s">
-        <v>350</v>
+        <v>344</v>
       </c>
       <c r="C20" s="5" t="s">
-        <v>353</v>
+        <v>347</v>
       </c>
       <c r="D20" s="24" t="s">
-        <v>42</v>
+        <v>36</v>
       </c>
       <c r="E20" s="6">
         <v>2</v>
@@ -6605,23 +6671,23 @@
         <v>1</v>
       </c>
       <c r="G20" s="6" t="s">
-        <v>77</v>
+        <v>71</v>
       </c>
       <c r="H20" s="5"/>
       <c r="I20" s="5"/>
     </row>
     <row r="21" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A21" s="15" t="s">
-        <v>354</v>
+        <v>348</v>
       </c>
       <c r="B21" s="25" t="s">
-        <v>350</v>
+        <v>344</v>
       </c>
       <c r="C21" s="9" t="s">
-        <v>355</v>
+        <v>349</v>
       </c>
       <c r="D21" s="24" t="s">
-        <v>42</v>
+        <v>36</v>
       </c>
       <c r="E21" s="10">
         <v>2</v>
@@ -6630,23 +6696,23 @@
         <v>1</v>
       </c>
       <c r="G21" s="10" t="s">
-        <v>77</v>
+        <v>71</v>
       </c>
       <c r="H21" s="9"/>
       <c r="I21" s="9"/>
     </row>
     <row r="22" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A22" s="22" t="s">
-        <v>356</v>
+        <v>350</v>
       </c>
       <c r="B22" s="23" t="s">
-        <v>350</v>
+        <v>344</v>
       </c>
       <c r="C22" s="5" t="s">
-        <v>357</v>
+        <v>351</v>
       </c>
       <c r="D22" s="24" t="s">
-        <v>42</v>
+        <v>36</v>
       </c>
       <c r="E22" s="6">
         <v>2</v>
@@ -6655,23 +6721,23 @@
         <v>1</v>
       </c>
       <c r="G22" s="6" t="s">
-        <v>77</v>
+        <v>71</v>
       </c>
       <c r="H22" s="5"/>
       <c r="I22" s="5"/>
     </row>
     <row r="23" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A23" s="15" t="s">
-        <v>358</v>
+        <v>352</v>
       </c>
       <c r="B23" s="25" t="s">
-        <v>350</v>
+        <v>344</v>
       </c>
       <c r="C23" s="9" t="s">
-        <v>359</v>
+        <v>353</v>
       </c>
       <c r="D23" s="24" t="s">
-        <v>42</v>
+        <v>36</v>
       </c>
       <c r="E23" s="10">
         <v>2</v>
@@ -6680,23 +6746,23 @@
         <v>0.5</v>
       </c>
       <c r="G23" s="10" t="s">
-        <v>77</v>
+        <v>71</v>
       </c>
       <c r="H23" s="9"/>
       <c r="I23" s="9"/>
     </row>
     <row r="24" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A24" s="22" t="s">
-        <v>360</v>
+        <v>354</v>
       </c>
       <c r="B24" s="23" t="s">
-        <v>361</v>
+        <v>355</v>
       </c>
       <c r="C24" s="5" t="s">
-        <v>362</v>
+        <v>356</v>
       </c>
       <c r="D24" s="24" t="s">
-        <v>42</v>
+        <v>36</v>
       </c>
       <c r="E24" s="6">
         <v>2</v>
@@ -6705,23 +6771,23 @@
         <v>1</v>
       </c>
       <c r="G24" s="6" t="s">
-        <v>77</v>
+        <v>71</v>
       </c>
       <c r="H24" s="5"/>
       <c r="I24" s="5"/>
     </row>
     <row r="25" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A25" s="15" t="s">
-        <v>363</v>
+        <v>357</v>
       </c>
       <c r="B25" s="25" t="s">
-        <v>361</v>
+        <v>355</v>
       </c>
       <c r="C25" s="9" t="s">
-        <v>364</v>
+        <v>358</v>
       </c>
       <c r="D25" s="24" t="s">
-        <v>42</v>
+        <v>36</v>
       </c>
       <c r="E25" s="10">
         <v>2</v>
@@ -6730,23 +6796,23 @@
         <v>1</v>
       </c>
       <c r="G25" s="10" t="s">
-        <v>77</v>
+        <v>71</v>
       </c>
       <c r="H25" s="9"/>
       <c r="I25" s="9"/>
     </row>
     <row r="26" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A26" s="22" t="s">
-        <v>365</v>
+        <v>359</v>
       </c>
       <c r="B26" s="23" t="s">
-        <v>366</v>
+        <v>360</v>
       </c>
       <c r="C26" s="5" t="s">
-        <v>367</v>
+        <v>361</v>
       </c>
       <c r="D26" s="26" t="s">
-        <v>118</v>
+        <v>112</v>
       </c>
       <c r="E26" s="6">
         <v>3</v>
@@ -6755,23 +6821,23 @@
         <v>1</v>
       </c>
       <c r="G26" s="6" t="s">
-        <v>77</v>
+        <v>71</v>
       </c>
       <c r="H26" s="5"/>
       <c r="I26" s="5"/>
     </row>
     <row r="27" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A27" s="15" t="s">
-        <v>368</v>
+        <v>362</v>
       </c>
       <c r="B27" s="25" t="s">
-        <v>366</v>
+        <v>360</v>
       </c>
       <c r="C27" s="9" t="s">
-        <v>369</v>
+        <v>363</v>
       </c>
       <c r="D27" s="26" t="s">
-        <v>118</v>
+        <v>112</v>
       </c>
       <c r="E27" s="10">
         <v>3</v>
@@ -6780,23 +6846,23 @@
         <v>1</v>
       </c>
       <c r="G27" s="10" t="s">
-        <v>77</v>
+        <v>71</v>
       </c>
       <c r="H27" s="9"/>
       <c r="I27" s="9"/>
     </row>
     <row r="28" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A28" s="22" t="s">
-        <v>370</v>
+        <v>364</v>
       </c>
       <c r="B28" s="23" t="s">
-        <v>366</v>
+        <v>360</v>
       </c>
       <c r="C28" s="5" t="s">
-        <v>371</v>
+        <v>365</v>
       </c>
       <c r="D28" s="26" t="s">
-        <v>118</v>
+        <v>112</v>
       </c>
       <c r="E28" s="6">
         <v>3</v>
@@ -6805,23 +6871,23 @@
         <v>0.5</v>
       </c>
       <c r="G28" s="6" t="s">
-        <v>77</v>
+        <v>71</v>
       </c>
       <c r="H28" s="5"/>
       <c r="I28" s="5"/>
     </row>
     <row r="29" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A29" s="15" t="s">
-        <v>372</v>
+        <v>366</v>
       </c>
       <c r="B29" s="25" t="s">
-        <v>373</v>
+        <v>367</v>
       </c>
       <c r="C29" s="9" t="s">
-        <v>294</v>
+        <v>288</v>
       </c>
       <c r="D29" s="26" t="s">
-        <v>118</v>
+        <v>112</v>
       </c>
       <c r="E29" s="10">
         <v>3</v>
@@ -6830,23 +6896,23 @@
         <v>0.5</v>
       </c>
       <c r="G29" s="10" t="s">
-        <v>77</v>
+        <v>71</v>
       </c>
       <c r="H29" s="9"/>
       <c r="I29" s="9"/>
     </row>
     <row r="30" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A30" s="22" t="s">
-        <v>374</v>
+        <v>368</v>
       </c>
       <c r="B30" s="23" t="s">
-        <v>373</v>
+        <v>367</v>
       </c>
       <c r="C30" s="5" t="s">
-        <v>375</v>
+        <v>369</v>
       </c>
       <c r="D30" s="26" t="s">
-        <v>118</v>
+        <v>112</v>
       </c>
       <c r="E30" s="6">
         <v>3</v>
@@ -6855,23 +6921,23 @@
         <v>1</v>
       </c>
       <c r="G30" s="6" t="s">
-        <v>77</v>
+        <v>71</v>
       </c>
       <c r="H30" s="5"/>
       <c r="I30" s="5"/>
     </row>
     <row r="31" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A31" s="15" t="s">
-        <v>376</v>
+        <v>370</v>
       </c>
       <c r="B31" s="25" t="s">
-        <v>373</v>
+        <v>367</v>
       </c>
       <c r="C31" s="9" t="s">
-        <v>377</v>
+        <v>371</v>
       </c>
       <c r="D31" s="26" t="s">
-        <v>118</v>
+        <v>112</v>
       </c>
       <c r="E31" s="10">
         <v>3</v>
@@ -6880,23 +6946,23 @@
         <v>0.5</v>
       </c>
       <c r="G31" s="10" t="s">
-        <v>77</v>
+        <v>71</v>
       </c>
       <c r="H31" s="9"/>
       <c r="I31" s="9"/>
     </row>
     <row r="32" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A32" s="22" t="s">
-        <v>378</v>
+        <v>372</v>
       </c>
       <c r="B32" s="23" t="s">
-        <v>379</v>
+        <v>373</v>
       </c>
       <c r="C32" s="5" t="s">
-        <v>380</v>
+        <v>374</v>
       </c>
       <c r="D32" s="26" t="s">
-        <v>118</v>
+        <v>112</v>
       </c>
       <c r="E32" s="6">
         <v>3</v>
@@ -6905,23 +6971,23 @@
         <v>1</v>
       </c>
       <c r="G32" s="6" t="s">
-        <v>77</v>
+        <v>71</v>
       </c>
       <c r="H32" s="5"/>
       <c r="I32" s="5"/>
     </row>
     <row r="33" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A33" s="15" t="s">
-        <v>381</v>
+        <v>375</v>
       </c>
       <c r="B33" s="25" t="s">
-        <v>379</v>
+        <v>373</v>
       </c>
       <c r="C33" s="9" t="s">
-        <v>382</v>
+        <v>376</v>
       </c>
       <c r="D33" s="26" t="s">
-        <v>118</v>
+        <v>112</v>
       </c>
       <c r="E33" s="10">
         <v>3</v>
@@ -6930,23 +6996,23 @@
         <v>0.5</v>
       </c>
       <c r="G33" s="10" t="s">
-        <v>77</v>
+        <v>71</v>
       </c>
       <c r="H33" s="9"/>
       <c r="I33" s="9"/>
     </row>
     <row r="34" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A34" s="22" t="s">
-        <v>383</v>
+        <v>377</v>
       </c>
       <c r="B34" s="23" t="s">
-        <v>379</v>
+        <v>373</v>
       </c>
       <c r="C34" s="5" t="s">
-        <v>127</v>
+        <v>121</v>
       </c>
       <c r="D34" s="26" t="s">
-        <v>118</v>
+        <v>112</v>
       </c>
       <c r="E34" s="6">
         <v>3</v>
@@ -6955,23 +7021,23 @@
         <v>0.5</v>
       </c>
       <c r="G34" s="6" t="s">
-        <v>77</v>
+        <v>71</v>
       </c>
       <c r="H34" s="5"/>
       <c r="I34" s="5"/>
     </row>
     <row r="35" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A35" s="15" t="s">
-        <v>384</v>
+        <v>378</v>
       </c>
       <c r="B35" s="25" t="s">
-        <v>136</v>
+        <v>130</v>
       </c>
       <c r="C35" s="9" t="s">
-        <v>137</v>
+        <v>131</v>
       </c>
       <c r="D35" s="24" t="s">
-        <v>42</v>
+        <v>36</v>
       </c>
       <c r="E35" s="10">
         <v>3</v>
@@ -6980,23 +7046,23 @@
         <v>1</v>
       </c>
       <c r="G35" s="10" t="s">
-        <v>77</v>
+        <v>71</v>
       </c>
       <c r="H35" s="9"/>
       <c r="I35" s="9"/>
     </row>
     <row r="36" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A36" s="22" t="s">
-        <v>385</v>
+        <v>379</v>
       </c>
       <c r="B36" s="23" t="s">
-        <v>136</v>
+        <v>130</v>
       </c>
       <c r="C36" s="5" t="s">
-        <v>139</v>
+        <v>133</v>
       </c>
       <c r="D36" s="24" t="s">
-        <v>42</v>
+        <v>36</v>
       </c>
       <c r="E36" s="6">
         <v>3</v>
@@ -7005,23 +7071,23 @@
         <v>2</v>
       </c>
       <c r="G36" s="6" t="s">
-        <v>77</v>
+        <v>71</v>
       </c>
       <c r="H36" s="5"/>
       <c r="I36" s="5"/>
     </row>
     <row r="37" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A37" s="15" t="s">
-        <v>386</v>
+        <v>380</v>
       </c>
       <c r="B37" s="25" t="s">
-        <v>136</v>
+        <v>130</v>
       </c>
       <c r="C37" s="9" t="s">
-        <v>387</v>
+        <v>381</v>
       </c>
       <c r="D37" s="24" t="s">
-        <v>42</v>
+        <v>36</v>
       </c>
       <c r="E37" s="10">
         <v>3</v>
@@ -7030,14 +7096,14 @@
         <v>0.5</v>
       </c>
       <c r="G37" s="10" t="s">
-        <v>77</v>
+        <v>71</v>
       </c>
       <c r="H37" s="9"/>
       <c r="I37" s="9"/>
     </row>
     <row r="39" spans="1:9" x14ac:dyDescent="0.3">
       <c r="C39" s="27" t="s">
-        <v>142</v>
+        <v>136</v>
       </c>
       <c r="F39" s="28">
         <f>SUM(F2:F37)</f>
@@ -7046,7 +7112,7 @@
     </row>
     <row r="40" spans="1:9" x14ac:dyDescent="0.3">
       <c r="C40" s="27" t="s">
-        <v>143</v>
+        <v>137</v>
       </c>
       <c r="F40" s="28">
         <f>SUMIF(G2:G37,"Feito",F2:F37)</f>
@@ -7063,6 +7129,18 @@
   </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{CCE6A557-97BC-4b89-ADB6-D9C93CAAB3DF}">
+      <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" count="1">
+        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{55C221EA-BD23-41F3-A04C-52C49795FAAE}">
+          <x14:formula1>
+            <xm:f>Equipes!$B$5:$G$5</xm:f>
+          </x14:formula1>
+          <xm:sqref>H2:H37</xm:sqref>
+        </x14:dataValidation>
+      </x14:dataValidations>
+    </ext>
+  </extLst>
 </worksheet>
 </file>
 
@@ -7084,45 +7162,45 @@
   <sheetData>
     <row r="1" spans="1:9" ht="26.4" x14ac:dyDescent="0.3">
       <c r="A1" s="32" t="s">
+        <v>24</v>
+      </c>
+      <c r="B1" s="32" t="s">
+        <v>25</v>
+      </c>
+      <c r="C1" s="32" t="s">
+        <v>26</v>
+      </c>
+      <c r="D1" s="32" t="s">
+        <v>27</v>
+      </c>
+      <c r="E1" s="32" t="s">
+        <v>28</v>
+      </c>
+      <c r="F1" s="32" t="s">
+        <v>29</v>
+      </c>
+      <c r="G1" s="32" t="s">
         <v>30</v>
       </c>
-      <c r="B1" s="32" t="s">
+      <c r="H1" s="32" t="s">
         <v>31</v>
       </c>
-      <c r="C1" s="32" t="s">
+      <c r="I1" s="32" t="s">
         <v>32</v>
-      </c>
-      <c r="D1" s="32" t="s">
-        <v>33</v>
-      </c>
-      <c r="E1" s="32" t="s">
-        <v>34</v>
-      </c>
-      <c r="F1" s="32" t="s">
-        <v>35</v>
-      </c>
-      <c r="G1" s="32" t="s">
-        <v>36</v>
-      </c>
-      <c r="H1" s="32" t="s">
-        <v>37</v>
-      </c>
-      <c r="I1" s="32" t="s">
-        <v>38</v>
       </c>
     </row>
     <row r="2" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A2" s="22" t="s">
-        <v>388</v>
+        <v>382</v>
       </c>
       <c r="B2" s="23" t="s">
-        <v>389</v>
+        <v>383</v>
       </c>
       <c r="C2" s="5" t="s">
-        <v>146</v>
+        <v>140</v>
       </c>
       <c r="D2" s="24" t="s">
-        <v>42</v>
+        <v>36</v>
       </c>
       <c r="E2" s="6">
         <v>1</v>
@@ -7131,23 +7209,23 @@
         <v>0.5</v>
       </c>
       <c r="G2" s="6" t="s">
-        <v>43</v>
+        <v>37</v>
       </c>
       <c r="H2" s="5"/>
       <c r="I2" s="5"/>
     </row>
     <row r="3" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A3" s="15" t="s">
-        <v>390</v>
+        <v>384</v>
       </c>
       <c r="B3" s="25" t="s">
-        <v>389</v>
+        <v>383</v>
       </c>
       <c r="C3" s="9" t="s">
-        <v>391</v>
+        <v>385</v>
       </c>
       <c r="D3" s="24" t="s">
-        <v>42</v>
+        <v>36</v>
       </c>
       <c r="E3" s="10">
         <v>1</v>
@@ -7156,23 +7234,23 @@
         <v>1.5</v>
       </c>
       <c r="G3" s="10" t="s">
-        <v>43</v>
+        <v>37</v>
       </c>
       <c r="H3" s="9"/>
       <c r="I3" s="9"/>
     </row>
     <row r="4" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A4" s="22" t="s">
-        <v>392</v>
+        <v>386</v>
       </c>
       <c r="B4" s="23" t="s">
-        <v>389</v>
+        <v>383</v>
       </c>
       <c r="C4" s="5" t="s">
-        <v>393</v>
+        <v>387</v>
       </c>
       <c r="D4" s="24" t="s">
-        <v>42</v>
+        <v>36</v>
       </c>
       <c r="E4" s="6">
         <v>1</v>
@@ -7181,23 +7259,23 @@
         <v>1</v>
       </c>
       <c r="G4" s="6" t="s">
-        <v>43</v>
+        <v>37</v>
       </c>
       <c r="H4" s="5"/>
       <c r="I4" s="5"/>
     </row>
     <row r="5" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A5" s="15" t="s">
-        <v>394</v>
+        <v>388</v>
       </c>
       <c r="B5" s="25" t="s">
+        <v>383</v>
+      </c>
+      <c r="C5" s="9" t="s">
         <v>389</v>
       </c>
-      <c r="C5" s="9" t="s">
-        <v>395</v>
-      </c>
       <c r="D5" s="24" t="s">
-        <v>42</v>
+        <v>36</v>
       </c>
       <c r="E5" s="10">
         <v>1</v>
@@ -7206,23 +7284,23 @@
         <v>1</v>
       </c>
       <c r="G5" s="10" t="s">
-        <v>43</v>
+        <v>37</v>
       </c>
       <c r="H5" s="9"/>
       <c r="I5" s="9"/>
     </row>
     <row r="6" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A6" s="22" t="s">
-        <v>396</v>
+        <v>390</v>
       </c>
       <c r="B6" s="23" t="s">
-        <v>389</v>
+        <v>383</v>
       </c>
       <c r="C6" s="5" t="s">
-        <v>397</v>
+        <v>391</v>
       </c>
       <c r="D6" s="24" t="s">
-        <v>42</v>
+        <v>36</v>
       </c>
       <c r="E6" s="6">
         <v>1</v>
@@ -7231,23 +7309,23 @@
         <v>1</v>
       </c>
       <c r="G6" s="6" t="s">
-        <v>43</v>
+        <v>37</v>
       </c>
       <c r="H6" s="5"/>
       <c r="I6" s="5"/>
     </row>
     <row r="7" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A7" s="15" t="s">
-        <v>398</v>
+        <v>392</v>
       </c>
       <c r="B7" s="25" t="s">
-        <v>399</v>
+        <v>393</v>
       </c>
       <c r="C7" s="9" t="s">
-        <v>400</v>
+        <v>394</v>
       </c>
       <c r="D7" s="24" t="s">
-        <v>42</v>
+        <v>36</v>
       </c>
       <c r="E7" s="10">
         <v>1</v>
@@ -7256,23 +7334,23 @@
         <v>1</v>
       </c>
       <c r="G7" s="10" t="s">
-        <v>43</v>
+        <v>37</v>
       </c>
       <c r="H7" s="9"/>
       <c r="I7" s="9"/>
     </row>
     <row r="8" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A8" s="22" t="s">
-        <v>401</v>
+        <v>395</v>
       </c>
       <c r="B8" s="23" t="s">
-        <v>399</v>
+        <v>393</v>
       </c>
       <c r="C8" s="5" t="s">
-        <v>402</v>
+        <v>396</v>
       </c>
       <c r="D8" s="24" t="s">
-        <v>42</v>
+        <v>36</v>
       </c>
       <c r="E8" s="6">
         <v>1</v>
@@ -7281,23 +7359,23 @@
         <v>1</v>
       </c>
       <c r="G8" s="6" t="s">
-        <v>43</v>
+        <v>37</v>
       </c>
       <c r="H8" s="5"/>
       <c r="I8" s="5"/>
     </row>
     <row r="9" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A9" s="15" t="s">
-        <v>403</v>
+        <v>397</v>
       </c>
       <c r="B9" s="25" t="s">
-        <v>399</v>
+        <v>393</v>
       </c>
       <c r="C9" s="9" t="s">
-        <v>404</v>
+        <v>398</v>
       </c>
       <c r="D9" s="24" t="s">
-        <v>42</v>
+        <v>36</v>
       </c>
       <c r="E9" s="10">
         <v>1</v>
@@ -7306,23 +7384,23 @@
         <v>0.5</v>
       </c>
       <c r="G9" s="10" t="s">
-        <v>43</v>
+        <v>37</v>
       </c>
       <c r="H9" s="9"/>
       <c r="I9" s="9"/>
     </row>
     <row r="10" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A10" s="22" t="s">
-        <v>405</v>
+        <v>399</v>
       </c>
       <c r="B10" s="23" t="s">
-        <v>406</v>
+        <v>400</v>
       </c>
       <c r="C10" s="5" t="s">
-        <v>407</v>
+        <v>401</v>
       </c>
       <c r="D10" s="24" t="s">
-        <v>42</v>
+        <v>36</v>
       </c>
       <c r="E10" s="6">
         <v>2</v>
@@ -7331,23 +7409,23 @@
         <v>0.5</v>
       </c>
       <c r="G10" s="6" t="s">
-        <v>77</v>
+        <v>71</v>
       </c>
       <c r="H10" s="5"/>
       <c r="I10" s="5"/>
     </row>
     <row r="11" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A11" s="15" t="s">
-        <v>408</v>
+        <v>402</v>
       </c>
       <c r="B11" s="25" t="s">
-        <v>406</v>
+        <v>400</v>
       </c>
       <c r="C11" s="9" t="s">
-        <v>409</v>
+        <v>403</v>
       </c>
       <c r="D11" s="24" t="s">
-        <v>42</v>
+        <v>36</v>
       </c>
       <c r="E11" s="10">
         <v>2</v>
@@ -7356,23 +7434,23 @@
         <v>1</v>
       </c>
       <c r="G11" s="10" t="s">
-        <v>77</v>
+        <v>71</v>
       </c>
       <c r="H11" s="9"/>
       <c r="I11" s="9"/>
     </row>
     <row r="12" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A12" s="22" t="s">
-        <v>410</v>
+        <v>404</v>
       </c>
       <c r="B12" s="23" t="s">
-        <v>406</v>
+        <v>400</v>
       </c>
       <c r="C12" s="5" t="s">
-        <v>411</v>
+        <v>405</v>
       </c>
       <c r="D12" s="24" t="s">
-        <v>42</v>
+        <v>36</v>
       </c>
       <c r="E12" s="6">
         <v>2</v>
@@ -7381,23 +7459,23 @@
         <v>1</v>
       </c>
       <c r="G12" s="6" t="s">
-        <v>77</v>
+        <v>71</v>
       </c>
       <c r="H12" s="5"/>
       <c r="I12" s="5"/>
     </row>
     <row r="13" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A13" s="15" t="s">
-        <v>412</v>
+        <v>406</v>
       </c>
       <c r="B13" s="25" t="s">
-        <v>406</v>
+        <v>400</v>
       </c>
       <c r="C13" s="9" t="s">
-        <v>413</v>
+        <v>407</v>
       </c>
       <c r="D13" s="24" t="s">
-        <v>42</v>
+        <v>36</v>
       </c>
       <c r="E13" s="10">
         <v>2</v>
@@ -7406,23 +7484,23 @@
         <v>1.5</v>
       </c>
       <c r="G13" s="10" t="s">
-        <v>77</v>
+        <v>71</v>
       </c>
       <c r="H13" s="9"/>
       <c r="I13" s="9"/>
     </row>
     <row r="14" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A14" s="22" t="s">
-        <v>414</v>
+        <v>408</v>
       </c>
       <c r="B14" s="23" t="s">
-        <v>406</v>
+        <v>400</v>
       </c>
       <c r="C14" s="5" t="s">
-        <v>415</v>
+        <v>409</v>
       </c>
       <c r="D14" s="24" t="s">
-        <v>42</v>
+        <v>36</v>
       </c>
       <c r="E14" s="6">
         <v>2</v>
@@ -7431,23 +7509,23 @@
         <v>0.5</v>
       </c>
       <c r="G14" s="6" t="s">
-        <v>77</v>
+        <v>71</v>
       </c>
       <c r="H14" s="5"/>
       <c r="I14" s="5"/>
     </row>
     <row r="15" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A15" s="15" t="s">
-        <v>416</v>
+        <v>410</v>
       </c>
       <c r="B15" s="25" t="s">
-        <v>417</v>
+        <v>411</v>
       </c>
       <c r="C15" s="9" t="s">
-        <v>418</v>
+        <v>412</v>
       </c>
       <c r="D15" s="24" t="s">
-        <v>42</v>
+        <v>36</v>
       </c>
       <c r="E15" s="10">
         <v>2</v>
@@ -7456,23 +7534,23 @@
         <v>1</v>
       </c>
       <c r="G15" s="10" t="s">
-        <v>77</v>
+        <v>71</v>
       </c>
       <c r="H15" s="9"/>
       <c r="I15" s="9"/>
     </row>
     <row r="16" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A16" s="22" t="s">
-        <v>419</v>
+        <v>413</v>
       </c>
       <c r="B16" s="23" t="s">
-        <v>417</v>
+        <v>411</v>
       </c>
       <c r="C16" s="5" t="s">
-        <v>420</v>
+        <v>414</v>
       </c>
       <c r="D16" s="24" t="s">
-        <v>42</v>
+        <v>36</v>
       </c>
       <c r="E16" s="6">
         <v>2</v>
@@ -7481,23 +7559,23 @@
         <v>1</v>
       </c>
       <c r="G16" s="6" t="s">
-        <v>77</v>
+        <v>71</v>
       </c>
       <c r="H16" s="5"/>
       <c r="I16" s="5"/>
     </row>
     <row r="17" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A17" s="15" t="s">
-        <v>421</v>
+        <v>415</v>
       </c>
       <c r="B17" s="25" t="s">
-        <v>417</v>
+        <v>411</v>
       </c>
       <c r="C17" s="9" t="s">
-        <v>422</v>
+        <v>416</v>
       </c>
       <c r="D17" s="24" t="s">
-        <v>42</v>
+        <v>36</v>
       </c>
       <c r="E17" s="10">
         <v>2</v>
@@ -7506,23 +7584,23 @@
         <v>1</v>
       </c>
       <c r="G17" s="10" t="s">
-        <v>77</v>
+        <v>71</v>
       </c>
       <c r="H17" s="9"/>
       <c r="I17" s="9"/>
     </row>
     <row r="18" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A18" s="22" t="s">
-        <v>423</v>
+        <v>417</v>
       </c>
       <c r="B18" s="23" t="s">
-        <v>417</v>
+        <v>411</v>
       </c>
       <c r="C18" s="5" t="s">
-        <v>424</v>
+        <v>418</v>
       </c>
       <c r="D18" s="24" t="s">
-        <v>42</v>
+        <v>36</v>
       </c>
       <c r="E18" s="6">
         <v>2</v>
@@ -7531,23 +7609,23 @@
         <v>1</v>
       </c>
       <c r="G18" s="6" t="s">
-        <v>77</v>
+        <v>71</v>
       </c>
       <c r="H18" s="5"/>
       <c r="I18" s="5"/>
     </row>
     <row r="19" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A19" s="15" t="s">
-        <v>425</v>
+        <v>419</v>
       </c>
       <c r="B19" s="25" t="s">
-        <v>426</v>
+        <v>420</v>
       </c>
       <c r="C19" s="9" t="s">
-        <v>427</v>
+        <v>421</v>
       </c>
       <c r="D19" s="24" t="s">
-        <v>42</v>
+        <v>36</v>
       </c>
       <c r="E19" s="10">
         <v>2</v>
@@ -7556,23 +7634,23 @@
         <v>1</v>
       </c>
       <c r="G19" s="10" t="s">
-        <v>77</v>
+        <v>71</v>
       </c>
       <c r="H19" s="9"/>
       <c r="I19" s="9"/>
     </row>
     <row r="20" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A20" s="22" t="s">
-        <v>428</v>
+        <v>422</v>
       </c>
       <c r="B20" s="23" t="s">
-        <v>426</v>
+        <v>420</v>
       </c>
       <c r="C20" s="5" t="s">
-        <v>429</v>
+        <v>423</v>
       </c>
       <c r="D20" s="24" t="s">
-        <v>42</v>
+        <v>36</v>
       </c>
       <c r="E20" s="6">
         <v>2</v>
@@ -7581,23 +7659,23 @@
         <v>0.5</v>
       </c>
       <c r="G20" s="6" t="s">
-        <v>77</v>
+        <v>71</v>
       </c>
       <c r="H20" s="5"/>
       <c r="I20" s="5"/>
     </row>
     <row r="21" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A21" s="15" t="s">
-        <v>430</v>
+        <v>424</v>
       </c>
       <c r="B21" s="25" t="s">
-        <v>426</v>
+        <v>420</v>
       </c>
       <c r="C21" s="9" t="s">
-        <v>431</v>
+        <v>425</v>
       </c>
       <c r="D21" s="24" t="s">
-        <v>42</v>
+        <v>36</v>
       </c>
       <c r="E21" s="10">
         <v>2</v>
@@ -7606,23 +7684,23 @@
         <v>1</v>
       </c>
       <c r="G21" s="10" t="s">
-        <v>77</v>
+        <v>71</v>
       </c>
       <c r="H21" s="9"/>
       <c r="I21" s="9"/>
     </row>
     <row r="22" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A22" s="22" t="s">
-        <v>432</v>
+        <v>426</v>
       </c>
       <c r="B22" s="23" t="s">
-        <v>426</v>
+        <v>420</v>
       </c>
       <c r="C22" s="5" t="s">
-        <v>433</v>
+        <v>427</v>
       </c>
       <c r="D22" s="24" t="s">
-        <v>42</v>
+        <v>36</v>
       </c>
       <c r="E22" s="6">
         <v>2</v>
@@ -7631,23 +7709,23 @@
         <v>1</v>
       </c>
       <c r="G22" s="6" t="s">
-        <v>77</v>
+        <v>71</v>
       </c>
       <c r="H22" s="5"/>
       <c r="I22" s="5"/>
     </row>
     <row r="23" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A23" s="15" t="s">
-        <v>434</v>
+        <v>428</v>
       </c>
       <c r="B23" s="25" t="s">
-        <v>435</v>
+        <v>429</v>
       </c>
       <c r="C23" s="9" t="s">
-        <v>436</v>
+        <v>430</v>
       </c>
       <c r="D23" s="24" t="s">
-        <v>42</v>
+        <v>36</v>
       </c>
       <c r="E23" s="10">
         <v>2</v>
@@ -7656,23 +7734,23 @@
         <v>1</v>
       </c>
       <c r="G23" s="10" t="s">
-        <v>77</v>
+        <v>71</v>
       </c>
       <c r="H23" s="9"/>
       <c r="I23" s="9"/>
     </row>
     <row r="24" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A24" s="22" t="s">
-        <v>437</v>
+        <v>431</v>
       </c>
       <c r="B24" s="23" t="s">
-        <v>435</v>
+        <v>429</v>
       </c>
       <c r="C24" s="5" t="s">
-        <v>438</v>
+        <v>432</v>
       </c>
       <c r="D24" s="24" t="s">
-        <v>42</v>
+        <v>36</v>
       </c>
       <c r="E24" s="6">
         <v>2</v>
@@ -7681,23 +7759,23 @@
         <v>0.5</v>
       </c>
       <c r="G24" s="6" t="s">
-        <v>77</v>
+        <v>71</v>
       </c>
       <c r="H24" s="5"/>
       <c r="I24" s="5"/>
     </row>
     <row r="25" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A25" s="15" t="s">
-        <v>439</v>
+        <v>433</v>
       </c>
       <c r="B25" s="25" t="s">
-        <v>435</v>
+        <v>429</v>
       </c>
       <c r="C25" s="9" t="s">
-        <v>96</v>
+        <v>90</v>
       </c>
       <c r="D25" s="24" t="s">
-        <v>42</v>
+        <v>36</v>
       </c>
       <c r="E25" s="10">
         <v>2</v>
@@ -7706,23 +7784,23 @@
         <v>0.5</v>
       </c>
       <c r="G25" s="10" t="s">
-        <v>77</v>
+        <v>71</v>
       </c>
       <c r="H25" s="9"/>
       <c r="I25" s="9"/>
     </row>
     <row r="26" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A26" s="22" t="s">
-        <v>440</v>
+        <v>434</v>
       </c>
       <c r="B26" s="23" t="s">
-        <v>441</v>
+        <v>435</v>
       </c>
       <c r="C26" s="5" t="s">
-        <v>442</v>
+        <v>436</v>
       </c>
       <c r="D26" s="24" t="s">
-        <v>42</v>
+        <v>36</v>
       </c>
       <c r="E26" s="6">
         <v>2</v>
@@ -7731,23 +7809,23 @@
         <v>1</v>
       </c>
       <c r="G26" s="6" t="s">
-        <v>77</v>
+        <v>71</v>
       </c>
       <c r="H26" s="5"/>
       <c r="I26" s="5"/>
     </row>
     <row r="27" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A27" s="15" t="s">
-        <v>443</v>
+        <v>437</v>
       </c>
       <c r="B27" s="25" t="s">
-        <v>441</v>
+        <v>435</v>
       </c>
       <c r="C27" s="9" t="s">
-        <v>444</v>
+        <v>438</v>
       </c>
       <c r="D27" s="24" t="s">
-        <v>42</v>
+        <v>36</v>
       </c>
       <c r="E27" s="10">
         <v>2</v>
@@ -7756,23 +7834,23 @@
         <v>1</v>
       </c>
       <c r="G27" s="10" t="s">
-        <v>77</v>
+        <v>71</v>
       </c>
       <c r="H27" s="9"/>
       <c r="I27" s="9"/>
     </row>
     <row r="28" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A28" s="22" t="s">
-        <v>445</v>
+        <v>439</v>
       </c>
       <c r="B28" s="23" t="s">
-        <v>446</v>
+        <v>440</v>
       </c>
       <c r="C28" s="5" t="s">
-        <v>447</v>
+        <v>441</v>
       </c>
       <c r="D28" s="26" t="s">
-        <v>118</v>
+        <v>112</v>
       </c>
       <c r="E28" s="6">
         <v>3</v>
@@ -7781,23 +7859,23 @@
         <v>1</v>
       </c>
       <c r="G28" s="6" t="s">
-        <v>77</v>
+        <v>71</v>
       </c>
       <c r="H28" s="5"/>
       <c r="I28" s="5"/>
     </row>
     <row r="29" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A29" s="15" t="s">
-        <v>448</v>
+        <v>442</v>
       </c>
       <c r="B29" s="25" t="s">
-        <v>446</v>
+        <v>440</v>
       </c>
       <c r="C29" s="9" t="s">
-        <v>291</v>
+        <v>285</v>
       </c>
       <c r="D29" s="26" t="s">
-        <v>118</v>
+        <v>112</v>
       </c>
       <c r="E29" s="10">
         <v>3</v>
@@ -7806,23 +7884,23 @@
         <v>0.5</v>
       </c>
       <c r="G29" s="10" t="s">
-        <v>77</v>
+        <v>71</v>
       </c>
       <c r="H29" s="9"/>
       <c r="I29" s="9"/>
     </row>
     <row r="30" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A30" s="22" t="s">
-        <v>449</v>
+        <v>443</v>
       </c>
       <c r="B30" s="23" t="s">
-        <v>450</v>
+        <v>444</v>
       </c>
       <c r="C30" s="5" t="s">
-        <v>294</v>
+        <v>288</v>
       </c>
       <c r="D30" s="26" t="s">
-        <v>118</v>
+        <v>112</v>
       </c>
       <c r="E30" s="6">
         <v>3</v>
@@ -7831,23 +7909,23 @@
         <v>0.5</v>
       </c>
       <c r="G30" s="6" t="s">
-        <v>77</v>
+        <v>71</v>
       </c>
       <c r="H30" s="5"/>
       <c r="I30" s="5"/>
     </row>
     <row r="31" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A31" s="15" t="s">
-        <v>451</v>
+        <v>445</v>
       </c>
       <c r="B31" s="25" t="s">
-        <v>450</v>
+        <v>444</v>
       </c>
       <c r="C31" s="9" t="s">
-        <v>452</v>
+        <v>446</v>
       </c>
       <c r="D31" s="26" t="s">
-        <v>118</v>
+        <v>112</v>
       </c>
       <c r="E31" s="10">
         <v>3</v>
@@ -7856,23 +7934,23 @@
         <v>1</v>
       </c>
       <c r="G31" s="10" t="s">
-        <v>77</v>
+        <v>71</v>
       </c>
       <c r="H31" s="9"/>
       <c r="I31" s="9"/>
     </row>
     <row r="32" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A32" s="22" t="s">
-        <v>453</v>
+        <v>447</v>
       </c>
       <c r="B32" s="23" t="s">
-        <v>450</v>
+        <v>444</v>
       </c>
       <c r="C32" s="5" t="s">
-        <v>454</v>
+        <v>448</v>
       </c>
       <c r="D32" s="26" t="s">
-        <v>118</v>
+        <v>112</v>
       </c>
       <c r="E32" s="6">
         <v>3</v>
@@ -7881,23 +7959,23 @@
         <v>0.5</v>
       </c>
       <c r="G32" s="6" t="s">
-        <v>77</v>
+        <v>71</v>
       </c>
       <c r="H32" s="5"/>
       <c r="I32" s="5"/>
     </row>
     <row r="33" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A33" s="15" t="s">
-        <v>455</v>
+        <v>449</v>
       </c>
       <c r="B33" s="25" t="s">
-        <v>136</v>
+        <v>130</v>
       </c>
       <c r="C33" s="9" t="s">
-        <v>137</v>
+        <v>131</v>
       </c>
       <c r="D33" s="24" t="s">
-        <v>42</v>
+        <v>36</v>
       </c>
       <c r="E33" s="10">
         <v>3</v>
@@ -7906,23 +7984,23 @@
         <v>1</v>
       </c>
       <c r="G33" s="10" t="s">
-        <v>77</v>
+        <v>71</v>
       </c>
       <c r="H33" s="9"/>
       <c r="I33" s="9"/>
     </row>
     <row r="34" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A34" s="22" t="s">
-        <v>456</v>
+        <v>450</v>
       </c>
       <c r="B34" s="23" t="s">
-        <v>136</v>
+        <v>130</v>
       </c>
       <c r="C34" s="5" t="s">
-        <v>139</v>
+        <v>133</v>
       </c>
       <c r="D34" s="24" t="s">
-        <v>42</v>
+        <v>36</v>
       </c>
       <c r="E34" s="6">
         <v>3</v>
@@ -7931,23 +8009,23 @@
         <v>2</v>
       </c>
       <c r="G34" s="6" t="s">
-        <v>77</v>
+        <v>71</v>
       </c>
       <c r="H34" s="5"/>
       <c r="I34" s="5"/>
     </row>
     <row r="35" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A35" s="15" t="s">
-        <v>457</v>
+        <v>451</v>
       </c>
       <c r="B35" s="25" t="s">
-        <v>136</v>
+        <v>130</v>
       </c>
       <c r="C35" s="9" t="s">
-        <v>458</v>
+        <v>452</v>
       </c>
       <c r="D35" s="24" t="s">
-        <v>42</v>
+        <v>36</v>
       </c>
       <c r="E35" s="10">
         <v>3</v>
@@ -7956,14 +8034,14 @@
         <v>1</v>
       </c>
       <c r="G35" s="10" t="s">
-        <v>77</v>
+        <v>71</v>
       </c>
       <c r="H35" s="9"/>
       <c r="I35" s="9"/>
     </row>
     <row r="37" spans="1:9" x14ac:dyDescent="0.3">
       <c r="C37" s="27" t="s">
-        <v>142</v>
+        <v>136</v>
       </c>
       <c r="F37" s="28">
         <f>SUM(F2:F35)</f>
@@ -7972,7 +8050,7 @@
     </row>
     <row r="38" spans="1:9" x14ac:dyDescent="0.3">
       <c r="C38" s="27" t="s">
-        <v>143</v>
+        <v>137</v>
       </c>
       <c r="F38" s="28">
         <f>SUMIF(G2:G35,"Feito",F2:F35)</f>
@@ -7989,6 +8067,18 @@
   </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{CCE6A557-97BC-4b89-ADB6-D9C93CAAB3DF}">
+      <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" count="1">
+        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{CCC53191-A2DA-4F5C-B99F-427F9B11E8AA}">
+          <x14:formula1>
+            <xm:f>Equipes!$B$6:$G$6</xm:f>
+          </x14:formula1>
+          <xm:sqref>H2:H35</xm:sqref>
+        </x14:dataValidation>
+      </x14:dataValidations>
+    </ext>
+  </extLst>
 </worksheet>
 </file>
 
@@ -8010,45 +8100,45 @@
   <sheetData>
     <row r="1" spans="1:9" ht="26.4" x14ac:dyDescent="0.3">
       <c r="A1" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="B1" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="C1" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="D1" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="E1" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="F1" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="G1" s="3" t="s">
         <v>30</v>
       </c>
-      <c r="B1" s="3" t="s">
+      <c r="H1" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="C1" s="3" t="s">
+      <c r="I1" s="3" t="s">
         <v>32</v>
-      </c>
-      <c r="D1" s="3" t="s">
-        <v>33</v>
-      </c>
-      <c r="E1" s="3" t="s">
-        <v>34</v>
-      </c>
-      <c r="F1" s="3" t="s">
-        <v>35</v>
-      </c>
-      <c r="G1" s="3" t="s">
-        <v>36</v>
-      </c>
-      <c r="H1" s="3" t="s">
-        <v>37</v>
-      </c>
-      <c r="I1" s="3" t="s">
-        <v>38</v>
       </c>
     </row>
     <row r="2" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A2" s="22" t="s">
-        <v>459</v>
+        <v>453</v>
       </c>
       <c r="B2" s="23" t="s">
-        <v>460</v>
+        <v>454</v>
       </c>
       <c r="C2" s="5" t="s">
-        <v>146</v>
+        <v>140</v>
       </c>
       <c r="D2" s="24" t="s">
-        <v>42</v>
+        <v>36</v>
       </c>
       <c r="E2" s="6">
         <v>1</v>
@@ -8057,23 +8147,23 @@
         <v>0.5</v>
       </c>
       <c r="G2" s="6" t="s">
-        <v>43</v>
+        <v>37</v>
       </c>
       <c r="H2" s="5"/>
       <c r="I2" s="5"/>
     </row>
     <row r="3" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A3" s="15" t="s">
-        <v>461</v>
+        <v>455</v>
       </c>
       <c r="B3" s="25" t="s">
-        <v>460</v>
+        <v>454</v>
       </c>
       <c r="C3" s="9" t="s">
-        <v>391</v>
+        <v>385</v>
       </c>
       <c r="D3" s="24" t="s">
-        <v>42</v>
+        <v>36</v>
       </c>
       <c r="E3" s="10">
         <v>1</v>
@@ -8082,23 +8172,23 @@
         <v>1.5</v>
       </c>
       <c r="G3" s="10" t="s">
-        <v>43</v>
+        <v>37</v>
       </c>
       <c r="H3" s="9"/>
       <c r="I3" s="9"/>
     </row>
     <row r="4" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A4" s="22" t="s">
-        <v>462</v>
+        <v>456</v>
       </c>
       <c r="B4" s="23" t="s">
-        <v>460</v>
+        <v>454</v>
       </c>
       <c r="C4" s="5" t="s">
-        <v>393</v>
+        <v>387</v>
       </c>
       <c r="D4" s="24" t="s">
-        <v>42</v>
+        <v>36</v>
       </c>
       <c r="E4" s="6">
         <v>1</v>
@@ -8107,23 +8197,23 @@
         <v>1</v>
       </c>
       <c r="G4" s="6" t="s">
-        <v>43</v>
+        <v>37</v>
       </c>
       <c r="H4" s="5"/>
       <c r="I4" s="5"/>
     </row>
     <row r="5" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A5" s="15" t="s">
-        <v>463</v>
+        <v>457</v>
       </c>
       <c r="B5" s="25" t="s">
-        <v>460</v>
+        <v>454</v>
       </c>
       <c r="C5" s="9" t="s">
-        <v>236</v>
+        <v>230</v>
       </c>
       <c r="D5" s="24" t="s">
-        <v>42</v>
+        <v>36</v>
       </c>
       <c r="E5" s="10">
         <v>1</v>
@@ -8132,23 +8222,23 @@
         <v>1.5</v>
       </c>
       <c r="G5" s="10" t="s">
-        <v>43</v>
+        <v>37</v>
       </c>
       <c r="H5" s="9"/>
       <c r="I5" s="9"/>
     </row>
     <row r="6" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A6" s="22" t="s">
-        <v>464</v>
+        <v>458</v>
       </c>
       <c r="B6" s="23" t="s">
-        <v>465</v>
+        <v>459</v>
       </c>
       <c r="C6" s="5" t="s">
-        <v>466</v>
+        <v>460</v>
       </c>
       <c r="D6" s="24" t="s">
-        <v>42</v>
+        <v>36</v>
       </c>
       <c r="E6" s="6">
         <v>1</v>
@@ -8157,23 +8247,23 @@
         <v>0.5</v>
       </c>
       <c r="G6" s="6" t="s">
-        <v>43</v>
+        <v>37</v>
       </c>
       <c r="H6" s="5"/>
       <c r="I6" s="5"/>
     </row>
     <row r="7" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A7" s="15" t="s">
-        <v>467</v>
+        <v>461</v>
       </c>
       <c r="B7" s="25" t="s">
-        <v>465</v>
+        <v>459</v>
       </c>
       <c r="C7" s="9" t="s">
-        <v>468</v>
+        <v>462</v>
       </c>
       <c r="D7" s="24" t="s">
-        <v>42</v>
+        <v>36</v>
       </c>
       <c r="E7" s="10">
         <v>1</v>
@@ -8182,23 +8272,23 @@
         <v>1</v>
       </c>
       <c r="G7" s="10" t="s">
-        <v>43</v>
+        <v>37</v>
       </c>
       <c r="H7" s="9"/>
       <c r="I7" s="9"/>
     </row>
     <row r="8" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A8" s="22" t="s">
-        <v>469</v>
+        <v>463</v>
       </c>
       <c r="B8" s="23" t="s">
-        <v>465</v>
+        <v>459</v>
       </c>
       <c r="C8" s="5" t="s">
-        <v>470</v>
+        <v>464</v>
       </c>
       <c r="D8" s="24" t="s">
-        <v>42</v>
+        <v>36</v>
       </c>
       <c r="E8" s="6">
         <v>1</v>
@@ -8207,23 +8297,23 @@
         <v>1</v>
       </c>
       <c r="G8" s="6" t="s">
-        <v>43</v>
+        <v>37</v>
       </c>
       <c r="H8" s="5"/>
       <c r="I8" s="5"/>
     </row>
     <row r="9" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A9" s="15" t="s">
-        <v>471</v>
+        <v>465</v>
       </c>
       <c r="B9" s="25" t="s">
-        <v>465</v>
+        <v>459</v>
       </c>
       <c r="C9" s="9" t="s">
-        <v>472</v>
+        <v>466</v>
       </c>
       <c r="D9" s="24" t="s">
-        <v>42</v>
+        <v>36</v>
       </c>
       <c r="E9" s="10">
         <v>1</v>
@@ -8232,23 +8322,23 @@
         <v>0.5</v>
       </c>
       <c r="G9" s="10" t="s">
-        <v>43</v>
+        <v>37</v>
       </c>
       <c r="H9" s="9"/>
       <c r="I9" s="9"/>
     </row>
     <row r="10" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A10" s="22" t="s">
-        <v>473</v>
+        <v>467</v>
       </c>
       <c r="B10" s="23" t="s">
-        <v>474</v>
+        <v>468</v>
       </c>
       <c r="C10" s="5" t="s">
-        <v>475</v>
+        <v>469</v>
       </c>
       <c r="D10" s="24" t="s">
-        <v>42</v>
+        <v>36</v>
       </c>
       <c r="E10" s="6">
         <v>2</v>
@@ -8257,23 +8347,23 @@
         <v>0.5</v>
       </c>
       <c r="G10" s="6" t="s">
-        <v>77</v>
+        <v>71</v>
       </c>
       <c r="H10" s="5"/>
       <c r="I10" s="5"/>
     </row>
     <row r="11" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A11" s="15" t="s">
-        <v>476</v>
+        <v>470</v>
       </c>
       <c r="B11" s="25" t="s">
-        <v>474</v>
+        <v>468</v>
       </c>
       <c r="C11" s="9" t="s">
-        <v>477</v>
+        <v>471</v>
       </c>
       <c r="D11" s="24" t="s">
-        <v>42</v>
+        <v>36</v>
       </c>
       <c r="E11" s="10">
         <v>2</v>
@@ -8282,23 +8372,23 @@
         <v>1</v>
       </c>
       <c r="G11" s="10" t="s">
-        <v>77</v>
+        <v>71</v>
       </c>
       <c r="H11" s="9"/>
       <c r="I11" s="9"/>
     </row>
     <row r="12" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A12" s="22" t="s">
-        <v>478</v>
+        <v>472</v>
       </c>
       <c r="B12" s="23" t="s">
-        <v>474</v>
+        <v>468</v>
       </c>
       <c r="C12" s="5" t="s">
-        <v>479</v>
+        <v>473</v>
       </c>
       <c r="D12" s="24" t="s">
-        <v>42</v>
+        <v>36</v>
       </c>
       <c r="E12" s="6">
         <v>2</v>
@@ -8307,23 +8397,23 @@
         <v>1</v>
       </c>
       <c r="G12" s="6" t="s">
-        <v>77</v>
+        <v>71</v>
       </c>
       <c r="H12" s="5"/>
       <c r="I12" s="5"/>
     </row>
     <row r="13" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A13" s="15" t="s">
-        <v>480</v>
+        <v>474</v>
       </c>
       <c r="B13" s="25" t="s">
-        <v>474</v>
+        <v>468</v>
       </c>
       <c r="C13" s="9" t="s">
-        <v>481</v>
+        <v>475</v>
       </c>
       <c r="D13" s="24" t="s">
-        <v>42</v>
+        <v>36</v>
       </c>
       <c r="E13" s="10">
         <v>2</v>
@@ -8332,23 +8422,23 @@
         <v>1.5</v>
       </c>
       <c r="G13" s="10" t="s">
-        <v>77</v>
+        <v>71</v>
       </c>
       <c r="H13" s="9"/>
       <c r="I13" s="9"/>
     </row>
     <row r="14" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A14" s="22" t="s">
-        <v>482</v>
+        <v>476</v>
       </c>
       <c r="B14" s="23" t="s">
-        <v>474</v>
+        <v>468</v>
       </c>
       <c r="C14" s="5" t="s">
-        <v>483</v>
+        <v>477</v>
       </c>
       <c r="D14" s="24" t="s">
-        <v>42</v>
+        <v>36</v>
       </c>
       <c r="E14" s="6">
         <v>2</v>
@@ -8357,23 +8447,23 @@
         <v>0.5</v>
       </c>
       <c r="G14" s="6" t="s">
-        <v>77</v>
+        <v>71</v>
       </c>
       <c r="H14" s="5"/>
       <c r="I14" s="5"/>
     </row>
     <row r="15" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A15" s="15" t="s">
-        <v>484</v>
+        <v>478</v>
       </c>
       <c r="B15" s="25" t="s">
-        <v>474</v>
+        <v>468</v>
       </c>
       <c r="C15" s="9" t="s">
-        <v>485</v>
+        <v>479</v>
       </c>
       <c r="D15" s="24" t="s">
-        <v>42</v>
+        <v>36</v>
       </c>
       <c r="E15" s="10">
         <v>2</v>
@@ -8382,23 +8472,23 @@
         <v>1</v>
       </c>
       <c r="G15" s="10" t="s">
-        <v>77</v>
+        <v>71</v>
       </c>
       <c r="H15" s="9"/>
       <c r="I15" s="9"/>
     </row>
     <row r="16" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A16" s="22" t="s">
-        <v>486</v>
+        <v>480</v>
       </c>
       <c r="B16" s="23" t="s">
-        <v>487</v>
+        <v>481</v>
       </c>
       <c r="C16" s="5" t="s">
-        <v>488</v>
+        <v>482</v>
       </c>
       <c r="D16" s="24" t="s">
-        <v>42</v>
+        <v>36</v>
       </c>
       <c r="E16" s="6">
         <v>2</v>
@@ -8407,23 +8497,23 @@
         <v>1</v>
       </c>
       <c r="G16" s="6" t="s">
-        <v>77</v>
+        <v>71</v>
       </c>
       <c r="H16" s="5"/>
       <c r="I16" s="5"/>
     </row>
     <row r="17" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A17" s="15" t="s">
-        <v>489</v>
+        <v>483</v>
       </c>
       <c r="B17" s="25" t="s">
-        <v>487</v>
+        <v>481</v>
       </c>
       <c r="C17" s="9" t="s">
-        <v>490</v>
+        <v>484</v>
       </c>
       <c r="D17" s="24" t="s">
-        <v>42</v>
+        <v>36</v>
       </c>
       <c r="E17" s="10">
         <v>2</v>
@@ -8432,23 +8522,23 @@
         <v>1.5</v>
       </c>
       <c r="G17" s="10" t="s">
-        <v>77</v>
+        <v>71</v>
       </c>
       <c r="H17" s="9"/>
       <c r="I17" s="9"/>
     </row>
     <row r="18" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A18" s="22" t="s">
-        <v>491</v>
+        <v>485</v>
       </c>
       <c r="B18" s="23" t="s">
-        <v>487</v>
+        <v>481</v>
       </c>
       <c r="C18" s="5" t="s">
-        <v>492</v>
+        <v>486</v>
       </c>
       <c r="D18" s="24" t="s">
-        <v>42</v>
+        <v>36</v>
       </c>
       <c r="E18" s="6">
         <v>2</v>
@@ -8457,23 +8547,23 @@
         <v>1</v>
       </c>
       <c r="G18" s="6" t="s">
-        <v>77</v>
+        <v>71</v>
       </c>
       <c r="H18" s="5"/>
       <c r="I18" s="5"/>
     </row>
     <row r="19" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A19" s="15" t="s">
-        <v>493</v>
+        <v>487</v>
       </c>
       <c r="B19" s="25" t="s">
-        <v>487</v>
+        <v>481</v>
       </c>
       <c r="C19" s="9" t="s">
-        <v>494</v>
+        <v>488</v>
       </c>
       <c r="D19" s="24" t="s">
-        <v>42</v>
+        <v>36</v>
       </c>
       <c r="E19" s="10">
         <v>2</v>
@@ -8482,23 +8572,23 @@
         <v>1</v>
       </c>
       <c r="G19" s="10" t="s">
-        <v>77</v>
+        <v>71</v>
       </c>
       <c r="H19" s="9"/>
       <c r="I19" s="9"/>
     </row>
     <row r="20" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A20" s="22" t="s">
-        <v>495</v>
+        <v>489</v>
       </c>
       <c r="B20" s="23" t="s">
-        <v>487</v>
+        <v>481</v>
       </c>
       <c r="C20" s="5" t="s">
-        <v>496</v>
+        <v>490</v>
       </c>
       <c r="D20" s="24" t="s">
-        <v>42</v>
+        <v>36</v>
       </c>
       <c r="E20" s="6">
         <v>2</v>
@@ -8507,23 +8597,23 @@
         <v>0.5</v>
       </c>
       <c r="G20" s="6" t="s">
-        <v>77</v>
+        <v>71</v>
       </c>
       <c r="H20" s="5"/>
       <c r="I20" s="5"/>
     </row>
     <row r="21" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A21" s="15" t="s">
-        <v>497</v>
+        <v>491</v>
       </c>
       <c r="B21" s="25" t="s">
-        <v>498</v>
+        <v>492</v>
       </c>
       <c r="C21" s="9" t="s">
-        <v>499</v>
+        <v>493</v>
       </c>
       <c r="D21" s="24" t="s">
-        <v>42</v>
+        <v>36</v>
       </c>
       <c r="E21" s="10">
         <v>2</v>
@@ -8532,23 +8622,23 @@
         <v>1.5</v>
       </c>
       <c r="G21" s="10" t="s">
-        <v>77</v>
+        <v>71</v>
       </c>
       <c r="H21" s="9"/>
       <c r="I21" s="9"/>
     </row>
     <row r="22" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A22" s="22" t="s">
-        <v>500</v>
+        <v>494</v>
       </c>
       <c r="B22" s="23" t="s">
-        <v>498</v>
+        <v>492</v>
       </c>
       <c r="C22" s="5" t="s">
-        <v>501</v>
+        <v>495</v>
       </c>
       <c r="D22" s="24" t="s">
-        <v>42</v>
+        <v>36</v>
       </c>
       <c r="E22" s="6">
         <v>2</v>
@@ -8557,23 +8647,23 @@
         <v>0.5</v>
       </c>
       <c r="G22" s="6" t="s">
-        <v>77</v>
+        <v>71</v>
       </c>
       <c r="H22" s="5"/>
       <c r="I22" s="5"/>
     </row>
     <row r="23" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A23" s="15" t="s">
-        <v>502</v>
+        <v>496</v>
       </c>
       <c r="B23" s="25" t="s">
-        <v>498</v>
+        <v>492</v>
       </c>
       <c r="C23" s="9" t="s">
-        <v>503</v>
+        <v>497</v>
       </c>
       <c r="D23" s="24" t="s">
-        <v>42</v>
+        <v>36</v>
       </c>
       <c r="E23" s="10">
         <v>2</v>
@@ -8582,23 +8672,23 @@
         <v>1</v>
       </c>
       <c r="G23" s="10" t="s">
-        <v>77</v>
+        <v>71</v>
       </c>
       <c r="H23" s="9"/>
       <c r="I23" s="9"/>
     </row>
     <row r="24" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A24" s="22" t="s">
-        <v>504</v>
+        <v>498</v>
       </c>
       <c r="B24" s="23" t="s">
-        <v>498</v>
+        <v>492</v>
       </c>
       <c r="C24" s="5" t="s">
-        <v>505</v>
+        <v>499</v>
       </c>
       <c r="D24" s="24" t="s">
-        <v>42</v>
+        <v>36</v>
       </c>
       <c r="E24" s="6">
         <v>2</v>
@@ -8607,23 +8697,23 @@
         <v>1</v>
       </c>
       <c r="G24" s="6" t="s">
-        <v>77</v>
+        <v>71</v>
       </c>
       <c r="H24" s="5"/>
       <c r="I24" s="5"/>
     </row>
     <row r="25" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A25" s="15" t="s">
-        <v>506</v>
+        <v>500</v>
       </c>
       <c r="B25" s="25" t="s">
-        <v>498</v>
+        <v>492</v>
       </c>
       <c r="C25" s="9" t="s">
-        <v>507</v>
+        <v>501</v>
       </c>
       <c r="D25" s="24" t="s">
-        <v>42</v>
+        <v>36</v>
       </c>
       <c r="E25" s="10">
         <v>2</v>
@@ -8632,23 +8722,23 @@
         <v>1</v>
       </c>
       <c r="G25" s="10" t="s">
-        <v>77</v>
+        <v>71</v>
       </c>
       <c r="H25" s="9"/>
       <c r="I25" s="9"/>
     </row>
     <row r="26" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A26" s="22" t="s">
-        <v>508</v>
+        <v>502</v>
       </c>
       <c r="B26" s="23" t="s">
-        <v>509</v>
+        <v>503</v>
       </c>
       <c r="C26" s="5" t="s">
-        <v>510</v>
+        <v>504</v>
       </c>
       <c r="D26" s="24" t="s">
-        <v>42</v>
+        <v>36</v>
       </c>
       <c r="E26" s="6">
         <v>2</v>
@@ -8657,23 +8747,23 @@
         <v>1</v>
       </c>
       <c r="G26" s="6" t="s">
-        <v>77</v>
+        <v>71</v>
       </c>
       <c r="H26" s="5"/>
       <c r="I26" s="5"/>
     </row>
     <row r="27" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A27" s="15" t="s">
-        <v>511</v>
+        <v>505</v>
       </c>
       <c r="B27" s="25" t="s">
-        <v>509</v>
+        <v>503</v>
       </c>
       <c r="C27" s="9" t="s">
-        <v>512</v>
+        <v>506</v>
       </c>
       <c r="D27" s="24" t="s">
-        <v>42</v>
+        <v>36</v>
       </c>
       <c r="E27" s="10">
         <v>2</v>
@@ -8682,23 +8772,23 @@
         <v>1</v>
       </c>
       <c r="G27" s="10" t="s">
-        <v>77</v>
+        <v>71</v>
       </c>
       <c r="H27" s="9"/>
       <c r="I27" s="9"/>
     </row>
     <row r="28" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A28" s="22" t="s">
-        <v>513</v>
+        <v>507</v>
       </c>
       <c r="B28" s="23" t="s">
-        <v>514</v>
+        <v>508</v>
       </c>
       <c r="C28" s="5" t="s">
-        <v>515</v>
+        <v>509</v>
       </c>
       <c r="D28" s="26" t="s">
-        <v>118</v>
+        <v>112</v>
       </c>
       <c r="E28" s="6">
         <v>3</v>
@@ -8707,23 +8797,23 @@
         <v>1</v>
       </c>
       <c r="G28" s="6" t="s">
-        <v>77</v>
+        <v>71</v>
       </c>
       <c r="H28" s="5"/>
       <c r="I28" s="5"/>
     </row>
     <row r="29" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A29" s="15" t="s">
-        <v>516</v>
+        <v>510</v>
       </c>
       <c r="B29" s="25" t="s">
-        <v>514</v>
+        <v>508</v>
       </c>
       <c r="C29" s="9" t="s">
-        <v>517</v>
+        <v>511</v>
       </c>
       <c r="D29" s="26" t="s">
-        <v>118</v>
+        <v>112</v>
       </c>
       <c r="E29" s="10">
         <v>3</v>
@@ -8732,23 +8822,23 @@
         <v>1</v>
       </c>
       <c r="G29" s="10" t="s">
-        <v>77</v>
+        <v>71</v>
       </c>
       <c r="H29" s="9"/>
       <c r="I29" s="9"/>
     </row>
     <row r="30" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A30" s="22" t="s">
-        <v>518</v>
+        <v>512</v>
       </c>
       <c r="B30" s="23" t="s">
-        <v>519</v>
+        <v>513</v>
       </c>
       <c r="C30" s="5" t="s">
-        <v>294</v>
+        <v>288</v>
       </c>
       <c r="D30" s="33" t="s">
-        <v>520</v>
+        <v>514</v>
       </c>
       <c r="E30" s="6">
         <v>3</v>
@@ -8757,23 +8847,23 @@
         <v>0.5</v>
       </c>
       <c r="G30" s="6" t="s">
-        <v>77</v>
+        <v>71</v>
       </c>
       <c r="H30" s="5"/>
       <c r="I30" s="5"/>
     </row>
     <row r="31" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A31" s="15" t="s">
-        <v>521</v>
+        <v>515</v>
       </c>
       <c r="B31" s="25" t="s">
-        <v>519</v>
+        <v>513</v>
       </c>
       <c r="C31" s="9" t="s">
-        <v>522</v>
+        <v>516</v>
       </c>
       <c r="D31" s="33" t="s">
-        <v>520</v>
+        <v>514</v>
       </c>
       <c r="E31" s="10">
         <v>3</v>
@@ -8782,23 +8872,23 @@
         <v>1.5</v>
       </c>
       <c r="G31" s="10" t="s">
-        <v>77</v>
+        <v>71</v>
       </c>
       <c r="H31" s="9"/>
       <c r="I31" s="9"/>
     </row>
     <row r="32" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A32" s="22" t="s">
-        <v>523</v>
+        <v>517</v>
       </c>
       <c r="B32" s="23" t="s">
-        <v>519</v>
+        <v>513</v>
       </c>
       <c r="C32" s="5" t="s">
-        <v>377</v>
+        <v>371</v>
       </c>
       <c r="D32" s="33" t="s">
-        <v>520</v>
+        <v>514</v>
       </c>
       <c r="E32" s="6">
         <v>3</v>
@@ -8807,23 +8897,23 @@
         <v>0.5</v>
       </c>
       <c r="G32" s="6" t="s">
-        <v>77</v>
+        <v>71</v>
       </c>
       <c r="H32" s="5"/>
       <c r="I32" s="5"/>
     </row>
     <row r="33" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A33" s="15" t="s">
-        <v>524</v>
+        <v>518</v>
       </c>
       <c r="B33" s="25" t="s">
-        <v>136</v>
+        <v>130</v>
       </c>
       <c r="C33" s="9" t="s">
-        <v>137</v>
+        <v>131</v>
       </c>
       <c r="D33" s="24" t="s">
-        <v>42</v>
+        <v>36</v>
       </c>
       <c r="E33" s="10">
         <v>3</v>
@@ -8832,23 +8922,23 @@
         <v>1</v>
       </c>
       <c r="G33" s="10" t="s">
-        <v>77</v>
+        <v>71</v>
       </c>
       <c r="H33" s="9"/>
       <c r="I33" s="9"/>
     </row>
     <row r="34" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A34" s="22" t="s">
-        <v>525</v>
+        <v>519</v>
       </c>
       <c r="B34" s="23" t="s">
-        <v>136</v>
+        <v>130</v>
       </c>
       <c r="C34" s="5" t="s">
-        <v>139</v>
+        <v>133</v>
       </c>
       <c r="D34" s="24" t="s">
-        <v>42</v>
+        <v>36</v>
       </c>
       <c r="E34" s="6">
         <v>3</v>
@@ -8857,23 +8947,23 @@
         <v>2</v>
       </c>
       <c r="G34" s="6" t="s">
-        <v>77</v>
+        <v>71</v>
       </c>
       <c r="H34" s="5"/>
       <c r="I34" s="5"/>
     </row>
     <row r="35" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A35" s="15" t="s">
-        <v>526</v>
+        <v>520</v>
       </c>
       <c r="B35" s="25" t="s">
-        <v>136</v>
+        <v>130</v>
       </c>
       <c r="C35" s="9" t="s">
-        <v>527</v>
+        <v>521</v>
       </c>
       <c r="D35" s="24" t="s">
-        <v>42</v>
+        <v>36</v>
       </c>
       <c r="E35" s="10">
         <v>3</v>
@@ -8882,14 +8972,14 @@
         <v>1</v>
       </c>
       <c r="G35" s="10" t="s">
-        <v>77</v>
+        <v>71</v>
       </c>
       <c r="H35" s="9"/>
       <c r="I35" s="9"/>
     </row>
     <row r="37" spans="1:9" x14ac:dyDescent="0.3">
       <c r="C37" s="27" t="s">
-        <v>142</v>
+        <v>136</v>
       </c>
       <c r="F37" s="28">
         <f>SUM(F2:F35)</f>
@@ -8898,7 +8988,7 @@
     </row>
     <row r="38" spans="1:9" x14ac:dyDescent="0.3">
       <c r="C38" s="27" t="s">
-        <v>143</v>
+        <v>137</v>
       </c>
       <c r="F38" s="28">
         <f>SUMIF(G2:G35,"Feito",F2:F35)</f>
@@ -8915,5 +9005,17 @@
   </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{CCE6A557-97BC-4b89-ADB6-D9C93CAAB3DF}">
+      <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" count="1">
+        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{0C7D0904-8A93-461A-9D7B-64D62D75D3CD}">
+          <x14:formula1>
+            <xm:f>Equipes!$B$7:$G$7</xm:f>
+          </x14:formula1>
+          <xm:sqref>H2:H35</xm:sqref>
+        </x14:dataValidation>
+      </x14:dataValidations>
+    </ext>
+  </extLst>
 </worksheet>
 </file>
--- a/docs/3DSB_Acompanhamento_CampusApp.xlsx
+++ b/docs/3DSB_Acompanhamento_CampusApp.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\.github\docs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3979694D-AB44-4DAE-86D6-A00F1D5FE839}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{92961326-908F-46C6-A189-E52B49CF15C5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-16320" windowWidth="29040" windowHeight="15720" tabRatio="500" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-16320" windowWidth="29040" windowHeight="15720" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Dashboard" sheetId="1" r:id="rId1"/>
@@ -51,7 +51,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1257" uniqueCount="551">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1285" uniqueCount="551">
   <si>
     <t>Desenvolvimento de Dispositivos Móveis · IFTM Campus Uberlândia · Prof. Edson Angoti Júnior</t>
   </si>
@@ -1821,7 +1821,7 @@
       <charset val="1"/>
     </font>
   </fonts>
-  <fills count="14">
+  <fills count="16">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -1900,6 +1900,18 @@
         <bgColor rgb="FFFFFFFF"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="0"/>
+        <bgColor rgb="FFFFFFFF"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="0"/>
+        <bgColor rgb="FFF1F5F9"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="2">
     <border>
@@ -1928,7 +1940,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="35">
+  <cellXfs count="37">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -2022,6 +2034,12 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="13" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="14" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="15" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -2710,14 +2728,14 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B0FDFF74-CD3B-4BC2-985D-0CD9C1F9EF2A}">
-  <dimension ref="A1:G7"/>
+  <dimension ref="A1:G38"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="24.33203125" customWidth="1"/>
+    <col min="1" max="1" width="31.109375" customWidth="1"/>
     <col min="2" max="7" width="31.77734375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" ht="26.4" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A1" s="3" t="s">
         <v>1</v>
       </c>
@@ -2862,7 +2880,180 @@
       </c>
       <c r="G7" s="34"/>
     </row>
+    <row r="11" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A11" s="5" t="s">
+        <v>546</v>
+      </c>
+      <c r="B11" s="35"/>
+      <c r="C11" s="35"/>
+      <c r="D11" s="35"/>
+      <c r="E11" s="35"/>
+      <c r="F11" s="35"/>
+    </row>
+    <row r="12" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A12" s="5" t="s">
+        <v>523</v>
+      </c>
+      <c r="B12" s="36"/>
+      <c r="C12" s="36"/>
+      <c r="D12" s="36"/>
+      <c r="E12" s="36"/>
+      <c r="F12" s="35"/>
+    </row>
+    <row r="13" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A13" s="9" t="s">
+        <v>538</v>
+      </c>
+      <c r="B13" s="35"/>
+      <c r="C13" s="35"/>
+      <c r="D13" s="35"/>
+      <c r="E13" s="35"/>
+      <c r="F13" s="35"/>
+    </row>
+    <row r="14" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A14" s="9" t="s">
+        <v>539</v>
+      </c>
+      <c r="B14" s="36"/>
+      <c r="C14" s="36"/>
+      <c r="D14" s="36"/>
+      <c r="E14" s="35"/>
+      <c r="F14" s="35"/>
+    </row>
+    <row r="15" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A15" s="5" t="s">
+        <v>542</v>
+      </c>
+      <c r="B15" s="35"/>
+      <c r="C15" s="35"/>
+      <c r="D15" s="35"/>
+      <c r="E15" s="35"/>
+      <c r="F15" s="35"/>
+    </row>
+    <row r="16" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A16" s="9" t="s">
+        <v>527</v>
+      </c>
+      <c r="B16" s="36"/>
+      <c r="C16" s="36"/>
+      <c r="D16" s="36"/>
+      <c r="E16" s="36"/>
+      <c r="F16" s="35"/>
+    </row>
+    <row r="17" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A17" s="9" t="s">
+        <v>528</v>
+      </c>
+    </row>
+    <row r="18" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A18" s="5" t="s">
+        <v>532</v>
+      </c>
+    </row>
+    <row r="19" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A19" s="9" t="s">
+        <v>547</v>
+      </c>
+    </row>
+    <row r="20" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A20" s="9" t="s">
+        <v>529</v>
+      </c>
+    </row>
+    <row r="21" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A21" s="5" t="s">
+        <v>524</v>
+      </c>
+    </row>
+    <row r="22" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A22" s="5" t="s">
+        <v>543</v>
+      </c>
+    </row>
+    <row r="23" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A23" s="5" t="s">
+        <v>533</v>
+      </c>
+    </row>
+    <row r="24" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A24" s="9" t="s">
+        <v>548</v>
+      </c>
+    </row>
+    <row r="25" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A25" s="9" t="s">
+        <v>537</v>
+      </c>
+    </row>
+    <row r="26" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A26" s="9" t="s">
+        <v>540</v>
+      </c>
+    </row>
+    <row r="27" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A27" s="5" t="s">
+        <v>534</v>
+      </c>
+    </row>
+    <row r="28" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A28" s="5" t="s">
+        <v>525</v>
+      </c>
+    </row>
+    <row r="29" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A29" s="5" t="s">
+        <v>535</v>
+      </c>
+    </row>
+    <row r="30" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A30" s="5" t="s">
+        <v>541</v>
+      </c>
+    </row>
+    <row r="31" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A31" s="9" t="s">
+        <v>549</v>
+      </c>
+    </row>
+    <row r="32" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A32" s="5" t="s">
+        <v>544</v>
+      </c>
+    </row>
+    <row r="33" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A33" s="9" t="s">
+        <v>530</v>
+      </c>
+    </row>
+    <row r="34" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A34" s="9" t="s">
+        <v>545</v>
+      </c>
+    </row>
+    <row r="35" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A35" s="5" t="s">
+        <v>536</v>
+      </c>
+    </row>
+    <row r="36" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A36" s="5" t="s">
+        <v>526</v>
+      </c>
+    </row>
+    <row r="37" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A37" s="9" t="s">
+        <v>550</v>
+      </c>
+    </row>
+    <row r="38" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A38" s="9" t="s">
+        <v>531</v>
+      </c>
+    </row>
   </sheetData>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A11:A38">
+    <sortCondition ref="A11:A38"/>
+  </sortState>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
 </worksheet>
 </file>
